--- a/outputs/019f8417-e7f4-7bc3-aded-c62dfd1d1462/ShellStorm2_美术资产台账_v001.xlsx
+++ b/outputs/019f8417-e7f4-7bc3-aded-c62dfd1d1462/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R5fbb048e441f4596"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Ra3e1101e2eac4045"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R223e66e6fb724b88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R2486a64db6284474"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Ra200e32d1a904c4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rfe4a095bea01414a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R8b13e6d5bb8c450b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rdd4093ae2b4f4078"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R97459e44b4534c7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R14cc543c2d0b4973"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R7790dbc62de644e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R046ed2fbaaef4304"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R8573fe1a4d684450"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rb7a5b573dea048ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R99f70fcbf0544d95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rfc9fec22444b442f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -214,7 +214,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="63">
+  <x:cellXfs count="65">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -356,6 +356,12 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -711,35 +717,31 @@
       </x:c>
       <x:c r="H5" s="44" t="str"/>
       <x:c r="I5" s="44" t="str">
-        <x:v>当前原型</x:v>
+        <x:v>当前3D原型</x:v>
       </x:c>
       <x:c r="J5" s="44" t="str">
-        <x:v>胶囊防护体 v001</x:v>
+        <x:v>基地 + 四主题副本 + 独立靶场</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="45" t="n">
-        <x:f>COUNTA('资产主表'!$A$6:$A$200)</x:f>
-        <x:v>107</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B6" s="43"/>
       <x:c r="C6" s="45" t="n">
-        <x:f>COUNTIF('资产主表'!$K$6:$K$200,"已完成")+COUNTIF('资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>7</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D6" s="43"/>
       <x:c r="E6" s="45" t="n">
-        <x:f>COUNTIF('资产主表'!$K$6:$K$200,"待制作")+COUNTIF('资产主表'!$K$6:$K$200,"程序占位")</x:f>
         <x:v>99</x:v>
       </x:c>
       <x:c r="F6" s="43"/>
       <x:c r="G6" s="45" t="n">
-        <x:f>COUNTIF('资产主表'!$S$6:$S$200,"重复")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="43"/>
       <x:c r="I6" s="46" t="str">
-        <x:v>侧面 / 无腿 / 单手随向镜像 / 独立红围巾</x:v>
+        <x:v>全3D闭环 / 三档房间 / 七类怪 / 56枪弹组合 / 废土灯池</x:v>
       </x:c>
       <x:c r="J6" s="46"/>
     </x:row>
@@ -793,11 +795,11 @@
       </x:c>
       <x:c r="B10" s="50" t="n">
         <x:f>COUNTIF('资产主表'!$C$6:$C$200,A10)</x:f>
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C10" s="50" t="n">
         <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A10,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A10,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>6</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D10" s="43"/>
       <x:c r="E10" s="51" t="str">
@@ -818,12 +820,10 @@
         <x:v>敌人</x:v>
       </x:c>
       <x:c r="B11" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A11)</x:f>
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A11,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A11,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D11" s="43"/>
       <x:c r="E11" s="51" t="str">
@@ -844,12 +844,10 @@
         <x:v>枪械</x:v>
       </x:c>
       <x:c r="B12" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A12)</x:f>
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A12,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A12,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D12" s="43"/>
       <x:c r="E12" s="51" t="str">
@@ -870,11 +868,9 @@
         <x:v>道具</x:v>
       </x:c>
       <x:c r="B13" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A13)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="C13" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A13,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A13,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="43"/>
@@ -882,10 +878,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F13" s="52" t="str">
-        <x:v>角色先拆 head/body/hand/accessory；按设计决定是否需要第二只手</x:v>
+        <x:v>3D房间/家具/枪械/怪物/灯具先查共用根与尺寸类</x:v>
       </x:c>
       <x:c r="G13" s="52" t="str">
-        <x:v>枪械和 UI 也按挂点/组件拆分</x:v>
+        <x:v>主题差异进入资源或配置，禁止复制关卡局部目录</x:v>
       </x:c>
       <x:c r="H13" s="43"/>
       <x:c r="I13" s="43"/>
@@ -896,12 +892,10 @@
         <x:v>场景</x:v>
       </x:c>
       <x:c r="B14" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A14)</x:f>
-        <x:v>18</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C14" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A14,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A14,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D14" s="43"/>
       <x:c r="E14" s="51" t="str">
@@ -922,12 +916,10 @@
         <x:v>场景道具</x:v>
       </x:c>
       <x:c r="B15" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A15)</x:f>
-        <x:v>10</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C15" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A15,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A15,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D15" s="43"/>
       <x:c r="E15" s="43"/>
@@ -942,11 +934,9 @@
         <x:v>UI</x:v>
       </x:c>
       <x:c r="B16" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A16)</x:f>
         <x:v>13</x:v>
       </x:c>
       <x:c r="C16" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A16,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A16,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="43"/>
@@ -962,12 +952,10 @@
         <x:v>特效</x:v>
       </x:c>
       <x:c r="B17" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A17)</x:f>
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A17,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A17,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D17" s="43"/>
       <x:c r="E17" s="43"/>
@@ -982,11 +970,9 @@
         <x:v>音频</x:v>
       </x:c>
       <x:c r="B18" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A18)</x:f>
         <x:v>13</x:v>
       </x:c>
       <x:c r="C18" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A18,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A18,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D18" s="43"/>
@@ -1273,7 +1259,7 @@
         <x:v>角色|player|player_capsule01|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S6" s="36" t="str">
-        <x:f>IF(A6="","",IF(COUNTIF($R$6:$R$112,R6)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A6="","",IF(COUNTIF($R$6:$R$139,R6)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T6" s="36" t="str"/>
@@ -1347,7 +1333,7 @@
         <x:v>角色|player_component|player_capsule01|head|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S7" s="37" t="str">
-        <x:f>IF(A7="","",IF(COUNTIF($R$6:$R$112,R7)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A7="","",IF(COUNTIF($R$6:$R$139,R7)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T7" s="37" t="str">
@@ -1423,7 +1409,7 @@
         <x:v>角色|player_component|player_capsule01|body|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S8" s="37" t="str">
-        <x:f>IF(A8="","",IF(COUNTIF($R$6:$R$112,R8)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A8="","",IF(COUNTIF($R$6:$R$139,R8)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T8" s="37" t="str">
@@ -1499,7 +1485,7 @@
         <x:v>角色|player_component|player_capsule01|hand_l_source|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S9" s="37" t="str">
-        <x:f>IF(A9="","",IF(COUNTIF($R$6:$R$112,R9)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A9="","",IF(COUNTIF($R$6:$R$139,R9)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T9" s="37" t="str">
@@ -1575,7 +1561,7 @@
         <x:v>角色|player_component|player_capsule01|hand|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S10" s="37" t="str">
-        <x:f>IF(A10="","",IF(COUNTIF($R$6:$R$112,R10)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A10="","",IF(COUNTIF($R$6:$R$139,R10)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T10" s="37" t="str">
@@ -1651,7 +1637,7 @@
         <x:v>角色|player_accessory|player_capsule01|scarf|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S11" s="37" t="str">
-        <x:f>IF(A11="","",IF(COUNTIF($R$6:$R$112,R11)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A11="","",IF(COUNTIF($R$6:$R$139,R11)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T11" s="37" t="str">
@@ -1727,7 +1713,7 @@
         <x:v>角色|review_board|player_capsule01|preview|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S12" s="37" t="str">
-        <x:f>IF(A12="","",IF(COUNTIF($R$6:$R$112,R12)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A12="","",IF(COUNTIF($R$6:$R$139,R12)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T12" s="37" t="str"/>
@@ -1795,7 +1781,7 @@
         <x:v>特效|player_state|player_dash|root|侧面朝右（可水平翻转）|dashing</x:v>
       </x:c>
       <x:c r="S13" s="37" t="str">
-        <x:f>IF(A13="","",IF(COUNTIF($R$6:$R$112,R13)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A13="","",IF(COUNTIF($R$6:$R$139,R13)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T13" s="37" t="str"/>
@@ -1863,7 +1849,7 @@
         <x:v>特效|player_state|player_hurt|root|侧面朝右（可水平翻转）|hurt</x:v>
       </x:c>
       <x:c r="S14" s="37" t="str">
-        <x:f>IF(A14="","",IF(COUNTIF($R$6:$R$112,R14)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A14="","",IF(COUNTIF($R$6:$R$139,R14)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T14" s="37" t="str"/>
@@ -1929,7 +1915,7 @@
         <x:v>特效|player_overlay|player_low_hp|root|侧面朝右（可水平翻转）|low_health</x:v>
       </x:c>
       <x:c r="S15" s="37" t="str">
-        <x:f>IF(A15="","",IF(COUNTIF($R$6:$R$112,R15)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A15="","",IF(COUNTIF($R$6:$R$139,R15)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T15" s="37" t="str"/>
@@ -1995,7 +1981,7 @@
         <x:v>特效|player_overlay|player_silenced|root|侧面朝右（可水平翻转）|silenced</x:v>
       </x:c>
       <x:c r="S16" s="37" t="str">
-        <x:f>IF(A16="","",IF(COUNTIF($R$6:$R$112,R16)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A16="","",IF(COUNTIF($R$6:$R$139,R16)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T16" s="37" t="str"/>
@@ -2063,7 +2049,7 @@
         <x:v>敌人|normal_melee|melee_chaser|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S17" s="37" t="str">
-        <x:f>IF(A17="","",IF(COUNTIF($R$6:$R$112,R17)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A17="","",IF(COUNTIF($R$6:$R$139,R17)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T17" s="37" t="str"/>
@@ -2133,7 +2119,7 @@
         <x:v>敌人|normal_ranged|ranged_caster|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S18" s="37" t="str">
-        <x:f>IF(A18="","",IF(COUNTIF($R$6:$R$112,R18)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A18="","",IF(COUNTIF($R$6:$R$139,R18)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T18" s="37" t="str"/>
@@ -2201,7 +2187,7 @@
         <x:v>敌人|normal_summoner|summoner|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S19" s="37" t="str">
-        <x:f>IF(A19="","",IF(COUNTIF($R$6:$R$112,R19)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A19="","",IF(COUNTIF($R$6:$R$139,R19)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T19" s="37" t="str"/>
@@ -2269,7 +2255,7 @@
         <x:v>敌人|normal_tank|shielded|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S20" s="37" t="str">
-        <x:f>IF(A20="","",IF(COUNTIF($R$6:$R$112,R20)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A20="","",IF(COUNTIF($R$6:$R$139,R20)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T20" s="37" t="str"/>
@@ -2337,7 +2323,7 @@
         <x:v>敌人|normal_bomber|exploder|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S21" s="37" t="str">
-        <x:f>IF(A21="","",IF(COUNTIF($R$6:$R$112,R21)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A21="","",IF(COUNTIF($R$6:$R$139,R21)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T21" s="37" t="str"/>
@@ -2405,7 +2391,7 @@
         <x:v>敌人|normal_ambusher|ambusher|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S22" s="37" t="str">
-        <x:f>IF(A22="","",IF(COUNTIF($R$6:$R$112,R22)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A22="","",IF(COUNTIF($R$6:$R$139,R22)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T22" s="37" t="str"/>
@@ -2473,7 +2459,7 @@
         <x:v>敌人|boss|boss|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S23" s="37" t="str">
-        <x:f>IF(A23="","",IF(COUNTIF($R$6:$R$112,R23)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A23="","",IF(COUNTIF($R$6:$R$139,R23)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T23" s="37" t="str"/>
@@ -2543,7 +2529,7 @@
         <x:v>枪械|gunbody|bp_pistol|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S24" s="37" t="str">
-        <x:f>IF(A24="","",IF(COUNTIF($R$6:$R$112,R24)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A24="","",IF(COUNTIF($R$6:$R$139,R24)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T24" s="37" t="str"/>
@@ -2613,7 +2599,7 @@
         <x:v>枪械|gunbody|bp_shotgun|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S25" s="37" t="str">
-        <x:f>IF(A25="","",IF(COUNTIF($R$6:$R$112,R25)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A25="","",IF(COUNTIF($R$6:$R$139,R25)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T25" s="37" t="str"/>
@@ -2683,7 +2669,7 @@
         <x:v>枪械|gunbody|bp_rifle|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S26" s="37" t="str">
-        <x:f>IF(A26="","",IF(COUNTIF($R$6:$R$112,R26)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A26="","",IF(COUNTIF($R$6:$R$139,R26)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T26" s="37" t="str"/>
@@ -2753,7 +2739,7 @@
         <x:v>枪械|gunbody|bp_machinegun|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S27" s="37" t="str">
-        <x:f>IF(A27="","",IF(COUNTIF($R$6:$R$112,R27)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A27="","",IF(COUNTIF($R$6:$R$139,R27)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T27" s="37" t="str"/>
@@ -2823,7 +2809,7 @@
         <x:v>枪械|gunbody|bp_sniper|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S28" s="37" t="str">
-        <x:f>IF(A28="","",IF(COUNTIF($R$6:$R$112,R28)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A28="","",IF(COUNTIF($R$6:$R$139,R28)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T28" s="37" t="str"/>
@@ -2893,7 +2879,7 @@
         <x:v>枪械|gunbody|bp_launcher|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S29" s="37" t="str">
-        <x:f>IF(A29="","",IF(COUNTIF($R$6:$R$112,R29)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A29="","",IF(COUNTIF($R$6:$R$139,R29)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T29" s="37" t="str"/>
@@ -2963,7 +2949,7 @@
         <x:v>枪械|gunbody|bp_charge|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S30" s="37" t="str">
-        <x:f>IF(A30="","",IF(COUNTIF($R$6:$R$112,R30)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A30="","",IF(COUNTIF($R$6:$R$139,R30)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T30" s="37" t="str"/>
@@ -3031,7 +3017,7 @@
         <x:v>枪械|bullet_module|mod_bullet_standard|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S31" s="37" t="str">
-        <x:f>IF(A31="","",IF(COUNTIF($R$6:$R$112,R31)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A31="","",IF(COUNTIF($R$6:$R$139,R31)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T31" s="37" t="str"/>
@@ -3099,7 +3085,7 @@
         <x:v>枪械|bullet_module|mod_bullet_sticky|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S32" s="37" t="str">
-        <x:f>IF(A32="","",IF(COUNTIF($R$6:$R$112,R32)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A32="","",IF(COUNTIF($R$6:$R$139,R32)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T32" s="37" t="str"/>
@@ -3167,7 +3153,7 @@
         <x:v>枪械|bullet_module|mod_bullet_bounce|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S33" s="37" t="str">
-        <x:f>IF(A33="","",IF(COUNTIF($R$6:$R$112,R33)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A33="","",IF(COUNTIF($R$6:$R$139,R33)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T33" s="37" t="str"/>
@@ -3235,7 +3221,7 @@
         <x:v>枪械|bullet_module|mod_bullet_piercing|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S34" s="37" t="str">
-        <x:f>IF(A34="","",IF(COUNTIF($R$6:$R$112,R34)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A34="","",IF(COUNTIF($R$6:$R$139,R34)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T34" s="37" t="str"/>
@@ -3303,7 +3289,7 @@
         <x:v>枪械|bullet_module|mod_bullet_explosive|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S35" s="37" t="str">
-        <x:f>IF(A35="","",IF(COUNTIF($R$6:$R$112,R35)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A35="","",IF(COUNTIF($R$6:$R$139,R35)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T35" s="37" t="str"/>
@@ -3371,7 +3357,7 @@
         <x:v>枪械|bullet_module|mod_bullet_homing|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S36" s="37" t="str">
-        <x:f>IF(A36="","",IF(COUNTIF($R$6:$R$112,R36)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A36="","",IF(COUNTIF($R$6:$R$139,R36)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T36" s="37" t="str"/>
@@ -3439,7 +3425,7 @@
         <x:v>枪械|bullet_module|mod_bullet_blackhole|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S37" s="37" t="str">
-        <x:f>IF(A37="","",IF(COUNTIF($R$6:$R$112,R37)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A37="","",IF(COUNTIF($R$6:$R$139,R37)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T37" s="37" t="str"/>
@@ -3507,7 +3493,7 @@
         <x:v>枪械|bullet_module|mod_bullet_balloon|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S38" s="37" t="str">
-        <x:f>IF(A38="","",IF(COUNTIF($R$6:$R$112,R38)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A38="","",IF(COUNTIF($R$6:$R$139,R38)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T38" s="37" t="str"/>
@@ -3575,7 +3561,7 @@
         <x:v>枪械|attachment|attach_triple_muzzle|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S39" s="37" t="str">
-        <x:f>IF(A39="","",IF(COUNTIF($R$6:$R$112,R39)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A39="","",IF(COUNTIF($R$6:$R$139,R39)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T39" s="37" t="str"/>
@@ -3643,7 +3629,7 @@
         <x:v>枪械|attachment|attach_rubber_stock|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S40" s="37" t="str">
-        <x:f>IF(A40="","",IF(COUNTIF($R$6:$R$112,R40)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A40="","",IF(COUNTIF($R$6:$R$139,R40)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T40" s="37" t="str"/>
@@ -3711,7 +3697,7 @@
         <x:v>枪械|attachment|attach_scope|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S41" s="37" t="str">
-        <x:f>IF(A41="","",IF(COUNTIF($R$6:$R$112,R41)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A41="","",IF(COUNTIF($R$6:$R$139,R41)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T41" s="37" t="str"/>
@@ -3779,7 +3765,7 @@
         <x:v>枪械|attachment|attach_big_mag|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S42" s="37" t="str">
-        <x:f>IF(A42="","",IF(COUNTIF($R$6:$R$112,R42)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A42="","",IF(COUNTIF($R$6:$R$139,R42)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T42" s="37" t="str"/>
@@ -3847,7 +3833,7 @@
         <x:v>枪械|attachment|attach_fan|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S43" s="37" t="str">
-        <x:f>IF(A43="","",IF(COUNTIF($R$6:$R$112,R43)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A43="","",IF(COUNTIF($R$6:$R$139,R43)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T43" s="37" t="str"/>
@@ -3915,7 +3901,7 @@
         <x:v>枪械|attachment|attach_copy_sticker|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S44" s="37" t="str">
-        <x:f>IF(A44="","",IF(COUNTIF($R$6:$R$112,R44)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A44="","",IF(COUNTIF($R$6:$R$139,R44)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T44" s="37" t="str"/>
@@ -3983,7 +3969,7 @@
         <x:v>道具|consumable|item_beacon|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S45" s="37" t="str">
-        <x:f>IF(A45="","",IF(COUNTIF($R$6:$R$112,R45)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A45="","",IF(COUNTIF($R$6:$R$139,R45)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T45" s="37" t="str"/>
@@ -4049,7 +4035,7 @@
         <x:v>道具|key|item_room_key|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S46" s="37" t="str">
-        <x:f>IF(A46="","",IF(COUNTIF($R$6:$R$112,R46)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A46="","",IF(COUNTIF($R$6:$R$139,R46)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T46" s="37" t="str"/>
@@ -4115,7 +4101,7 @@
         <x:v>道具|pickup|soul_orb|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S47" s="37" t="str">
-        <x:f>IF(A47="","",IF(COUNTIF($R$6:$R$112,R47)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A47="","",IF(COUNTIF($R$6:$R$139,R47)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T47" s="37" t="str"/>
@@ -4181,7 +4167,7 @@
         <x:v>道具|container|container|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S48" s="37" t="str">
-        <x:f>IF(A48="","",IF(COUNTIF($R$6:$R$112,R48)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A48="","",IF(COUNTIF($R$6:$R$139,R48)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T48" s="37" t="str"/>
@@ -4247,7 +4233,7 @@
         <x:v>道具|pickup|room_key_pickup|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S49" s="37" t="str">
-        <x:f>IF(A49="","",IF(COUNTIF($R$6:$R$112,R49)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A49="","",IF(COUNTIF($R$6:$R$139,R49)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T49" s="37" t="str"/>
@@ -4313,7 +4299,7 @@
         <x:v>道具|pickup_base|ground_item|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S50" s="37" t="str">
-        <x:f>IF(A50="","",IF(COUNTIF($R$6:$R$112,R50)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A50="","",IF(COUNTIF($R$6:$R$139,R50)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T50" s="37" t="str"/>
@@ -4379,7 +4365,7 @@
         <x:v>场景|biome_kit|base_world|root|顶视|default</x:v>
       </x:c>
       <x:c r="S51" s="37" t="str">
-        <x:f>IF(A51="","",IF(COUNTIF($R$6:$R$112,R51)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A51="","",IF(COUNTIF($R$6:$R$139,R51)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T51" s="37" t="str"/>
@@ -4447,7 +4433,7 @@
         <x:v>场景|biome_kit|iron_frontier|root|顶视|default</x:v>
       </x:c>
       <x:c r="S52" s="37" t="str">
-        <x:f>IF(A52="","",IF(COUNTIF($R$6:$R$112,R52)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A52="","",IF(COUNTIF($R$6:$R$139,R52)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T52" s="37" t="str"/>
@@ -4515,7 +4501,7 @@
         <x:v>场景|biome_kit|rust_foundry|root|顶视|default</x:v>
       </x:c>
       <x:c r="S53" s="37" t="str">
-        <x:f>IF(A53="","",IF(COUNTIF($R$6:$R$112,R53)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A53="","",IF(COUNTIF($R$6:$R$139,R53)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T53" s="37" t="str"/>
@@ -4583,7 +4569,7 @@
         <x:v>场景|biome_kit|spore_depths|root|顶视|default</x:v>
       </x:c>
       <x:c r="S54" s="37" t="str">
-        <x:f>IF(A54="","",IF(COUNTIF($R$6:$R$112,R54)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A54="","",IF(COUNTIF($R$6:$R$139,R54)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T54" s="37" t="str"/>
@@ -4651,7 +4637,7 @@
         <x:v>场景|biome_kit|abyss_archive|root|顶视|default</x:v>
       </x:c>
       <x:c r="S55" s="37" t="str">
-        <x:f>IF(A55="","",IF(COUNTIF($R$6:$R$112,R55)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A55="","",IF(COUNTIF($R$6:$R$139,R55)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T55" s="37" t="str"/>
@@ -4719,7 +4705,7 @@
         <x:v>场景|biome_kit|training_range|root|顶视|default</x:v>
       </x:c>
       <x:c r="S56" s="37" t="str">
-        <x:f>IF(A56="","",IF(COUNTIF($R$6:$R$112,R56)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A56="","",IF(COUNTIF($R$6:$R$139,R56)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T56" s="37" t="str"/>
@@ -4787,7 +4773,7 @@
         <x:v>场景|room_dressing|room_combat|root|顶视|default</x:v>
       </x:c>
       <x:c r="S57" s="37" t="str">
-        <x:f>IF(A57="","",IF(COUNTIF($R$6:$R$112,R57)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A57="","",IF(COUNTIF($R$6:$R$139,R57)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T57" s="37" t="str"/>
@@ -4855,7 +4841,7 @@
         <x:v>场景|room_dressing|room_elite|root|顶视|default</x:v>
       </x:c>
       <x:c r="S58" s="37" t="str">
-        <x:f>IF(A58="","",IF(COUNTIF($R$6:$R$112,R58)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A58="","",IF(COUNTIF($R$6:$R$139,R58)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T58" s="37" t="str"/>
@@ -4923,7 +4909,7 @@
         <x:v>场景|room_dressing|room_boss|root|顶视|default</x:v>
       </x:c>
       <x:c r="S59" s="37" t="str">
-        <x:f>IF(A59="","",IF(COUNTIF($R$6:$R$112,R59)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A59="","",IF(COUNTIF($R$6:$R$139,R59)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T59" s="37" t="str"/>
@@ -4991,7 +4977,7 @@
         <x:v>场景|room_dressing|room_event|root|顶视|default</x:v>
       </x:c>
       <x:c r="S60" s="37" t="str">
-        <x:f>IF(A60="","",IF(COUNTIF($R$6:$R$112,R60)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A60="","",IF(COUNTIF($R$6:$R$139,R60)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T60" s="37" t="str"/>
@@ -5059,7 +5045,7 @@
         <x:v>场景|room_dressing|room_extraction|root|顶视|default</x:v>
       </x:c>
       <x:c r="S61" s="37" t="str">
-        <x:f>IF(A61="","",IF(COUNTIF($R$6:$R$112,R61)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A61="","",IF(COUNTIF($R$6:$R$139,R61)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T61" s="37" t="str"/>
@@ -5127,7 +5113,7 @@
         <x:v>场景|room_dressing|room_merchant|root|顶视|default</x:v>
       </x:c>
       <x:c r="S62" s="37" t="str">
-        <x:f>IF(A62="","",IF(COUNTIF($R$6:$R$112,R62)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A62="","",IF(COUNTIF($R$6:$R$139,R62)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T62" s="37" t="str"/>
@@ -5195,7 +5181,7 @@
         <x:v>场景|room_dressing|room_scavenge|root|顶视|default</x:v>
       </x:c>
       <x:c r="S63" s="37" t="str">
-        <x:f>IF(A63="","",IF(COUNTIF($R$6:$R$112,R63)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A63="","",IF(COUNTIF($R$6:$R$139,R63)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T63" s="37" t="str"/>
@@ -5263,7 +5249,7 @@
         <x:v>场景|room_dressing|room_storage|root|顶视|default</x:v>
       </x:c>
       <x:c r="S64" s="37" t="str">
-        <x:f>IF(A64="","",IF(COUNTIF($R$6:$R$112,R64)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A64="","",IF(COUNTIF($R$6:$R$139,R64)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T64" s="37" t="str"/>
@@ -5331,7 +5317,7 @@
         <x:v>场景|room_dressing|room_trap|root|顶视|default</x:v>
       </x:c>
       <x:c r="S65" s="37" t="str">
-        <x:f>IF(A65="","",IF(COUNTIF($R$6:$R$112,R65)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A65="","",IF(COUNTIF($R$6:$R$139,R65)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T65" s="37" t="str"/>
@@ -5399,7 +5385,7 @@
         <x:v>场景|room_dressing|room_upgrade|root|顶视|default</x:v>
       </x:c>
       <x:c r="S66" s="37" t="str">
-        <x:f>IF(A66="","",IF(COUNTIF($R$6:$R$112,R66)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A66="","",IF(COUNTIF($R$6:$R$139,R66)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T66" s="37" t="str"/>
@@ -5467,7 +5453,7 @@
         <x:v>场景|room_dressing|room_spawn|root|顶视|default</x:v>
       </x:c>
       <x:c r="S67" s="37" t="str">
-        <x:f>IF(A67="","",IF(COUNTIF($R$6:$R$112,R67)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A67="","",IF(COUNTIF($R$6:$R$139,R67)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T67" s="37" t="str"/>
@@ -5535,7 +5521,7 @@
         <x:v>场景|room_dressing|room_stairs|root|顶视|default</x:v>
       </x:c>
       <x:c r="S68" s="37" t="str">
-        <x:f>IF(A68="","",IF(COUNTIF($R$6:$R$112,R68)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A68="","",IF(COUNTIF($R$6:$R$139,R68)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T68" s="37" t="str"/>
@@ -5603,7 +5589,7 @@
         <x:v>场景道具|facility|base_briefing|root|顶视|default</x:v>
       </x:c>
       <x:c r="S69" s="37" t="str">
-        <x:f>IF(A69="","",IF(COUNTIF($R$6:$R$112,R69)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A69="","",IF(COUNTIF($R$6:$R$139,R69)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T69" s="37" t="str"/>
@@ -5671,7 +5657,7 @@
         <x:v>场景道具|facility|base_workshop|root|顶视|default</x:v>
       </x:c>
       <x:c r="S70" s="37" t="str">
-        <x:f>IF(A70="","",IF(COUNTIF($R$6:$R$112,R70)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A70="","",IF(COUNTIF($R$6:$R$139,R70)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T70" s="37" t="str"/>
@@ -5739,7 +5725,7 @@
         <x:v>场景道具|facility|base_divination|root|顶视|default</x:v>
       </x:c>
       <x:c r="S71" s="37" t="str">
-        <x:f>IF(A71="","",IF(COUNTIF($R$6:$R$112,R71)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A71="","",IF(COUNTIF($R$6:$R$139,R71)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T71" s="37" t="str"/>
@@ -5807,7 +5793,7 @@
         <x:v>场景道具|facility|base_vault|root|顶视|default</x:v>
       </x:c>
       <x:c r="S72" s="37" t="str">
-        <x:f>IF(A72="","",IF(COUNTIF($R$6:$R$112,R72)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A72="","",IF(COUNTIF($R$6:$R$139,R72)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T72" s="37" t="str"/>
@@ -5875,7 +5861,7 @@
         <x:v>场景道具|facility|base_monster_archive|root|顶视|default</x:v>
       </x:c>
       <x:c r="S73" s="37" t="str">
-        <x:f>IF(A73="","",IF(COUNTIF($R$6:$R$112,R73)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A73="","",IF(COUNTIF($R$6:$R$139,R73)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T73" s="37" t="str"/>
@@ -5943,7 +5929,7 @@
         <x:v>场景道具|facility|base_card_collection|root|顶视|default</x:v>
       </x:c>
       <x:c r="S74" s="37" t="str">
-        <x:f>IF(A74="","",IF(COUNTIF($R$6:$R$112,R74)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A74="","",IF(COUNTIF($R$6:$R$139,R74)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T74" s="37" t="str"/>
@@ -6011,7 +5997,7 @@
         <x:v>场景道具|facility|base_terminal|root|顶视|default</x:v>
       </x:c>
       <x:c r="S75" s="37" t="str">
-        <x:f>IF(A75="","",IF(COUNTIF($R$6:$R$112,R75)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A75="","",IF(COUNTIF($R$6:$R$139,R75)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T75" s="37" t="str"/>
@@ -6079,7 +6065,7 @@
         <x:v>场景道具|facility|dungeon_gate|root|顶视|default</x:v>
       </x:c>
       <x:c r="S76" s="37" t="str">
-        <x:f>IF(A76="","",IF(COUNTIF($R$6:$R$112,R76)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A76="","",IF(COUNTIF($R$6:$R$139,R76)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T76" s="37" t="str"/>
@@ -6147,7 +6133,7 @@
         <x:v>场景道具|facility|workbench|root|顶视|default</x:v>
       </x:c>
       <x:c r="S77" s="37" t="str">
-        <x:f>IF(A77="","",IF(COUNTIF($R$6:$R$112,R77)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A77="","",IF(COUNTIF($R$6:$R$139,R77)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T77" s="37" t="str"/>
@@ -6215,7 +6201,7 @@
         <x:v>场景道具|facility|door|root|顶视|default</x:v>
       </x:c>
       <x:c r="S78" s="37" t="str">
-        <x:f>IF(A78="","",IF(COUNTIF($R$6:$R$112,R78)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A78="","",IF(COUNTIF($R$6:$R$139,R78)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T78" s="37" t="str"/>
@@ -6283,7 +6269,7 @@
         <x:v>ui|screen|hud|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S79" s="37" t="str">
-        <x:f>IF(A79="","",IF(COUNTIF($R$6:$R$112,R79)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A79="","",IF(COUNTIF($R$6:$R$139,R79)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T79" s="37" t="str"/>
@@ -6351,7 +6337,7 @@
         <x:v>ui|screen|inventory|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S80" s="37" t="str">
-        <x:f>IF(A80="","",IF(COUNTIF($R$6:$R$112,R80)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A80="","",IF(COUNTIF($R$6:$R$139,R80)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T80" s="37" t="str"/>
@@ -6419,7 +6405,7 @@
         <x:v>ui|screen|merchant|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S81" s="37" t="str">
-        <x:f>IF(A81="","",IF(COUNTIF($R$6:$R$112,R81)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A81="","",IF(COUNTIF($R$6:$R$139,R81)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T81" s="37" t="str"/>
@@ -6487,7 +6473,7 @@
         <x:v>ui|screen|workshop|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S82" s="37" t="str">
-        <x:f>IF(A82="","",IF(COUNTIF($R$6:$R$112,R82)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A82="","",IF(COUNTIF($R$6:$R$139,R82)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T82" s="37" t="str"/>
@@ -6555,7 +6541,7 @@
         <x:v>ui|screen|workbench|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S83" s="37" t="str">
-        <x:f>IF(A83="","",IF(COUNTIF($R$6:$R$112,R83)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A83="","",IF(COUNTIF($R$6:$R$139,R83)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T83" s="37" t="str"/>
@@ -6623,7 +6609,7 @@
         <x:v>ui|screen|weapon_tree|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S84" s="37" t="str">
-        <x:f>IF(A84="","",IF(COUNTIF($R$6:$R$112,R84)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A84="","",IF(COUNTIF($R$6:$R$139,R84)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T84" s="37" t="str"/>
@@ -6691,7 +6677,7 @@
         <x:v>ui|screen|fate_select|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S85" s="37" t="str">
-        <x:f>IF(A85="","",IF(COUNTIF($R$6:$R$112,R85)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A85="","",IF(COUNTIF($R$6:$R$139,R85)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T85" s="37" t="str"/>
@@ -6759,7 +6745,7 @@
         <x:v>ui|screen|fate_collection|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S86" s="37" t="str">
-        <x:f>IF(A86="","",IF(COUNTIF($R$6:$R$112,R86)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A86="","",IF(COUNTIF($R$6:$R$139,R86)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T86" s="37" t="str"/>
@@ -6827,7 +6813,7 @@
         <x:v>ui|screen|level_select|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S87" s="37" t="str">
-        <x:f>IF(A87="","",IF(COUNTIF($R$6:$R$112,R87)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A87="","",IF(COUNTIF($R$6:$R$139,R87)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T87" s="37" t="str"/>
@@ -6895,7 +6881,7 @@
         <x:v>ui|screen|vault|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S88" s="37" t="str">
-        <x:f>IF(A88="","",IF(COUNTIF($R$6:$R$112,R88)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A88="","",IF(COUNTIF($R$6:$R$139,R88)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T88" s="37" t="str"/>
@@ -6963,7 +6949,7 @@
         <x:v>ui|screen|monster_archive|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S89" s="37" t="str">
-        <x:f>IF(A89="","",IF(COUNTIF($R$6:$R$112,R89)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A89="","",IF(COUNTIF($R$6:$R$139,R89)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T89" s="37" t="str"/>
@@ -7031,7 +7017,7 @@
         <x:v>ui|screen|base_menu|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S90" s="37" t="str">
-        <x:f>IF(A90="","",IF(COUNTIF($R$6:$R$112,R90)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A90="","",IF(COUNTIF($R$6:$R$139,R90)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T90" s="37" t="str"/>
@@ -7099,7 +7085,7 @@
         <x:v>ui|screen|mobile_controls|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S91" s="37" t="str">
-        <x:f>IF(A91="","",IF(COUNTIF($R$6:$R$112,R91)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A91="","",IF(COUNTIF($R$6:$R$139,R91)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T91" s="37" t="str"/>
@@ -7167,7 +7153,7 @@
         <x:v>特效|gameplay_vfx|explosion|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S92" s="37" t="str">
-        <x:f>IF(A92="","",IF(COUNTIF($R$6:$R$112,R92)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A92="","",IF(COUNTIF($R$6:$R$139,R92)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T92" s="37" t="str"/>
@@ -7235,7 +7221,7 @@
         <x:v>特效|gameplay_vfx|muzzle_flash|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S93" s="37" t="str">
-        <x:f>IF(A93="","",IF(COUNTIF($R$6:$R$112,R93)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A93="","",IF(COUNTIF($R$6:$R$139,R93)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T93" s="37" t="str"/>
@@ -7303,7 +7289,7 @@
         <x:v>特效|gameplay_vfx|damage_number|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S94" s="37" t="str">
-        <x:f>IF(A94="","",IF(COUNTIF($R$6:$R$112,R94)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A94="","",IF(COUNTIF($R$6:$R$139,R94)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T94" s="37" t="str"/>
@@ -7371,7 +7357,7 @@
         <x:v>特效|gameplay_vfx|spark|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S95" s="37" t="str">
-        <x:f>IF(A95="","",IF(COUNTIF($R$6:$R$112,R95)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A95="","",IF(COUNTIF($R$6:$R$139,R95)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T95" s="37" t="str"/>
@@ -7439,7 +7425,7 @@
         <x:v>特效|gameplay_vfx|room_transition|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S96" s="37" t="str">
-        <x:f>IF(A96="","",IF(COUNTIF($R$6:$R$112,R96)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A96="","",IF(COUNTIF($R$6:$R$139,R96)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T96" s="37" t="str"/>
@@ -7507,7 +7493,7 @@
         <x:v>特效|gameplay_vfx|health_vignette|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S97" s="37" t="str">
-        <x:f>IF(A97="","",IF(COUNTIF($R$6:$R$112,R97)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A97="","",IF(COUNTIF($R$6:$R$139,R97)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T97" s="37" t="str"/>
@@ -7575,7 +7561,7 @@
         <x:v>特效|gameplay_vfx|visibility_light|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S98" s="37" t="str">
-        <x:f>IF(A98="","",IF(COUNTIF($R$6:$R$112,R98)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A98="","",IF(COUNTIF($R$6:$R$139,R98)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T98" s="37" t="str"/>
@@ -7643,7 +7629,7 @@
         <x:v>特效|gameplay_vfx|extraction_beacon|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S99" s="37" t="str">
-        <x:f>IF(A99="","",IF(COUNTIF($R$6:$R$112,R99)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A99="","",IF(COUNTIF($R$6:$R$139,R99)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T99" s="37" t="str"/>
@@ -7711,7 +7697,7 @@
         <x:v>音频|bgm|bgm_wasteland|root|不适用|default</x:v>
       </x:c>
       <x:c r="S100" s="37" t="str">
-        <x:f>IF(A100="","",IF(COUNTIF($R$6:$R$112,R100)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A100="","",IF(COUNTIF($R$6:$R$139,R100)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T100" s="37" t="str"/>
@@ -7777,7 +7763,7 @@
         <x:v>音频|sfx|pistol_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S101" s="37" t="str">
-        <x:f>IF(A101="","",IF(COUNTIF($R$6:$R$112,R101)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A101="","",IF(COUNTIF($R$6:$R$139,R101)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T101" s="37" t="str"/>
@@ -7843,7 +7829,7 @@
         <x:v>音频|sfx|rifle_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S102" s="37" t="str">
-        <x:f>IF(A102="","",IF(COUNTIF($R$6:$R$112,R102)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A102="","",IF(COUNTIF($R$6:$R$139,R102)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T102" s="37" t="str"/>
@@ -7909,7 +7895,7 @@
         <x:v>音频|sfx|shotgun_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S103" s="37" t="str">
-        <x:f>IF(A103="","",IF(COUNTIF($R$6:$R$112,R103)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A103="","",IF(COUNTIF($R$6:$R$139,R103)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T103" s="37" t="str"/>
@@ -7975,7 +7961,7 @@
         <x:v>音频|sfx|smg_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S104" s="37" t="str">
-        <x:f>IF(A104="","",IF(COUNTIF($R$6:$R$112,R104)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A104="","",IF(COUNTIF($R$6:$R$139,R104)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T104" s="37" t="str"/>
@@ -8041,7 +8027,7 @@
         <x:v>音频|sfx|sniper_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S105" s="37" t="str">
-        <x:f>IF(A105="","",IF(COUNTIF($R$6:$R$112,R105)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A105="","",IF(COUNTIF($R$6:$R$139,R105)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T105" s="37" t="str"/>
@@ -8107,7 +8093,7 @@
         <x:v>音频|sfx|player_hit|root|不适用|default</x:v>
       </x:c>
       <x:c r="S106" s="37" t="str">
-        <x:f>IF(A106="","",IF(COUNTIF($R$6:$R$112,R106)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A106="","",IF(COUNTIF($R$6:$R$139,R106)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T106" s="37" t="str"/>
@@ -8173,7 +8159,7 @@
         <x:v>音频|sfx|player_dash|root|不适用|default</x:v>
       </x:c>
       <x:c r="S107" s="37" t="str">
-        <x:f>IF(A107="","",IF(COUNTIF($R$6:$R$112,R107)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A107="","",IF(COUNTIF($R$6:$R$139,R107)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T107" s="37" t="str"/>
@@ -8239,7 +8225,7 @@
         <x:v>音频|sfx|enemy_hit|root|不适用|default</x:v>
       </x:c>
       <x:c r="S108" s="37" t="str">
-        <x:f>IF(A108="","",IF(COUNTIF($R$6:$R$112,R108)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A108="","",IF(COUNTIF($R$6:$R$139,R108)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T108" s="37" t="str"/>
@@ -8305,7 +8291,7 @@
         <x:v>音频|sfx|enemy_die|root|不适用|default</x:v>
       </x:c>
       <x:c r="S109" s="37" t="str">
-        <x:f>IF(A109="","",IF(COUNTIF($R$6:$R$112,R109)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A109="","",IF(COUNTIF($R$6:$R$139,R109)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T109" s="37" t="str"/>
@@ -8371,7 +8357,7 @@
         <x:v>音频|sfx|reload|root|不适用|default</x:v>
       </x:c>
       <x:c r="S110" s="37" t="str">
-        <x:f>IF(A110="","",IF(COUNTIF($R$6:$R$112,R110)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A110="","",IF(COUNTIF($R$6:$R$139,R110)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T110" s="37" t="str"/>
@@ -8437,7 +8423,7 @@
         <x:v>音频|sfx|extraction_start|root|不适用|default</x:v>
       </x:c>
       <x:c r="S111" s="37" t="str">
-        <x:f>IF(A111="","",IF(COUNTIF($R$6:$R$112,R111)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A111="","",IF(COUNTIF($R$6:$R$139,R111)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T111" s="37" t="str"/>
@@ -8503,7 +8489,7 @@
         <x:v>音频|sfx|extraction_done|root|不适用|default</x:v>
       </x:c>
       <x:c r="S112" s="37" t="str">
-        <x:f>IF(A112="","",IF(COUNTIF($R$6:$R$112,R112)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A112="","",IF(COUNTIF($R$6:$R$139,R112)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T112" s="37" t="str"/>
@@ -8517,6 +8503,2048 @@
         <x:v>原创/待确认</x:v>
       </x:c>
       <x:c r="X112" s="37" t="str"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="B113" t="str">
+        <x:v>胶囊防护体3D根组件</x:v>
+      </x:c>
+      <x:c r="C113" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D113" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="E113" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F113" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G113" t="str">
+        <x:v>CHR-PLY-CAPSULE01</x:v>
+      </x:c>
+      <x:c r="H113" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I113" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J113" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K113" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L113" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M113" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N113" t="str">
+        <x:v>PackedScene/程序材质</x:v>
+      </x:c>
+      <x:c r="O113" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P113" t="str">
+        <x:v>scenes/Player3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q113" t="str">
+        <x:v>胶囊;防护服;3D;模块角色</x:v>
+      </x:c>
+      <x:c r="R113" t="str">
+        <x:f>LOWER(TRIM(C113)&amp;"|"&amp;TRIM(D113)&amp;"|"&amp;TRIM(E113)&amp;"|"&amp;TRIM(F113)&amp;"|"&amp;TRIM(H113)&amp;"|"&amp;TRIM(I113))</x:f>
+        <x:v>角色|player|player_capsule01|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S113" t="str">
+        <x:f>IF(A113="","",IF(COUNTIF($R$6:$R$139,R113)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T113" t="str">
+        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+      </x:c>
+      <x:c r="U113" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V113" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W113" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X113" t="str">
+        <x:v>2D逻辑资产的3D表现变体；无腿、单手、无手臂</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="str">
+        <x:v>CHR-PLY-CAPSULE01-BODY-3D</x:v>
+      </x:c>
+      <x:c r="B114" t="str">
+        <x:v>胶囊防护体3D身躯</x:v>
+      </x:c>
+      <x:c r="C114" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D114" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="E114" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F114" t="str">
+        <x:v>body_3d</x:v>
+      </x:c>
+      <x:c r="G114" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="H114" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I114" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J114" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K114" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L114" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M114" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N114" t="str">
+        <x:v>CapsuleMesh节点</x:v>
+      </x:c>
+      <x:c r="O114" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P114" t="str">
+        <x:v>VisualRoot/Body</x:v>
+      </x:c>
+      <x:c r="Q114" t="str">
+        <x:v>身躯;防护服;无腿;3D</x:v>
+      </x:c>
+      <x:c r="R114" t="str">
+        <x:f>LOWER(TRIM(C114)&amp;"|"&amp;TRIM(D114)&amp;"|"&amp;TRIM(E114)&amp;"|"&amp;TRIM(F114)&amp;"|"&amp;TRIM(H114)&amp;"|"&amp;TRIM(I114))</x:f>
+        <x:v>角色|player|player_capsule01|body_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S114" t="str">
+        <x:f>IF(A114="","",IF(COUNTIF($R$6:$R$139,R114)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T114" t="str">
+        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+      </x:c>
+      <x:c r="U114" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V114" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W114" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X114" t="str">
+        <x:v>PackedScene内独立Body节点；后续可替换GLB</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HEAD-3D</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>胶囊防护体3D头壳</x:v>
+      </x:c>
+      <x:c r="C115" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D115" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="E115" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F115" t="str">
+        <x:v>head_3d</x:v>
+      </x:c>
+      <x:c r="G115" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="H115" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I115" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J115" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K115" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L115" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M115" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N115" t="str">
+        <x:v>SphereMesh节点</x:v>
+      </x:c>
+      <x:c r="O115" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P115" t="str">
+        <x:v>VisualRoot/Head</x:v>
+      </x:c>
+      <x:c r="Q115" t="str">
+        <x:v>头壳;单传感器;3D</x:v>
+      </x:c>
+      <x:c r="R115" t="str">
+        <x:f>LOWER(TRIM(C115)&amp;"|"&amp;TRIM(D115)&amp;"|"&amp;TRIM(E115)&amp;"|"&amp;TRIM(F115)&amp;"|"&amp;TRIM(H115)&amp;"|"&amp;TRIM(I115))</x:f>
+        <x:v>角色|player|player_capsule01|head_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S115" t="str">
+        <x:f>IF(A115="","",IF(COUNTIF($R$6:$R$139,R115)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T115" t="str">
+        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+      </x:c>
+      <x:c r="U115" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V115" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W115" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X115" t="str">
+        <x:v>PackedScene内独立Head节点；无嘴无人脸</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HAND-3D</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>胶囊防护体3D唯一手部</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D116" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="E116" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F116" t="str">
+        <x:v>hand_3d</x:v>
+      </x:c>
+      <x:c r="G116" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="H116" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I116" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J116" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K116" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L116" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M116" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N116" t="str">
+        <x:v>SphereMesh节点</x:v>
+      </x:c>
+      <x:c r="O116" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P116" t="str">
+        <x:v>VisualRoot/Hand</x:v>
+      </x:c>
+      <x:c r="Q116" t="str">
+        <x:v>单手;悬浮手;握持;3D</x:v>
+      </x:c>
+      <x:c r="R116" t="str">
+        <x:f>LOWER(TRIM(C116)&amp;"|"&amp;TRIM(D116)&amp;"|"&amp;TRIM(E116)&amp;"|"&amp;TRIM(F116)&amp;"|"&amp;TRIM(H116)&amp;"|"&amp;TRIM(I116))</x:f>
+        <x:v>角色|player|player_capsule01|hand_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S116" t="str">
+        <x:f>IF(A116="","",IF(COUNTIF($R$6:$R$139,R116)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T116" t="str">
+        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+      </x:c>
+      <x:c r="U116" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V116" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W116" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X116" t="str">
+        <x:v>唯一可见手；随VisualRoot转向并保持身体局部位置</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="str">
+        <x:v>CHR-PLY-CAPSULE01-SCARF-3D</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>胶囊防护体3D红围巾</x:v>
+      </x:c>
+      <x:c r="C117" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D117" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="E117" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F117" t="str">
+        <x:v>scarf_3d</x:v>
+      </x:c>
+      <x:c r="G117" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="H117" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I117" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J117" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K117" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L117" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M117" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N117" t="str">
+        <x:v>Cylinder+Box节点</x:v>
+      </x:c>
+      <x:c r="O117" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P117" t="str">
+        <x:v>VisualRoot/Scarf</x:v>
+      </x:c>
+      <x:c r="Q117" t="str">
+        <x:v>红围巾;身份配件;3D</x:v>
+      </x:c>
+      <x:c r="R117" t="str">
+        <x:f>LOWER(TRIM(C117)&amp;"|"&amp;TRIM(D117)&amp;"|"&amp;TRIM(E117)&amp;"|"&amp;TRIM(F117)&amp;"|"&amp;TRIM(H117)&amp;"|"&amp;TRIM(I117))</x:f>
+        <x:v>角色|player|player_capsule01|scarf_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S117" t="str">
+        <x:f>IF(A117="","",IF(COUNTIF($R$6:$R$139,R117)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T117" t="str">
+        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+      </x:c>
+      <x:c r="U117" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V117" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W117" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X117" t="str">
+        <x:v>独立Scarf节点；保留移动与冲刺滞后动态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="str">
+        <x:v>CHR-PLY-CAPSULE01-WEAPON-SOCKET-3D</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>胶囊防护体3D武器挂点</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D118" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="E118" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F118" t="str">
+        <x:v>weapon_socket_3d</x:v>
+      </x:c>
+      <x:c r="G118" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="H118" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I118" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J118" t="str">
+        <x:v>武器系统</x:v>
+      </x:c>
+      <x:c r="K118" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L118" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M118" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N118" t="str">
+        <x:v>Marker3D</x:v>
+      </x:c>
+      <x:c r="O118" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P118" t="str">
+        <x:v>VisualRoot/WeaponSocket</x:v>
+      </x:c>
+      <x:c r="Q118" t="str">
+        <x:v>武器挂点;Marker3D;瞄准</x:v>
+      </x:c>
+      <x:c r="R118" t="str">
+        <x:f>LOWER(TRIM(C118)&amp;"|"&amp;TRIM(D118)&amp;"|"&amp;TRIM(E118)&amp;"|"&amp;TRIM(F118)&amp;"|"&amp;TRIM(H118)&amp;"|"&amp;TRIM(I118))</x:f>
+        <x:v>角色|player|player_capsule01|weapon_socket_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S118" t="str">
+        <x:f>IF(A118="","",IF(COUNTIF($R$6:$R$139,R118)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T118" t="str">
+        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+      </x:c>
+      <x:c r="U118" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V118" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W118" t="str">
+        <x:v>原创逻辑挂点</x:v>
+      </x:c>
+      <x:c r="X118" t="str">
+        <x:v>手和挂点保持局部关系；VisualRoot统一跟随准星转向</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="str">
+        <x:v>ENV-BASE-WORLD-KIT-3D</x:v>
+      </x:c>
+      <x:c r="B119" t="str">
+        <x:v>入口基地3D环境套件</x:v>
+      </x:c>
+      <x:c r="C119" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D119" t="str">
+        <x:v>base</x:v>
+      </x:c>
+      <x:c r="E119" t="str">
+        <x:v>base_world</x:v>
+      </x:c>
+      <x:c r="F119" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G119" t="str">
+        <x:v>ENV-BASE-WORLD-KIT</x:v>
+      </x:c>
+      <x:c r="H119" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I119" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J119" t="str">
+        <x:v>入口基地地图</x:v>
+      </x:c>
+      <x:c r="K119" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L119" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M119" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N119" t="str">
+        <x:v>约1:100迁移/程序几何</x:v>
+      </x:c>
+      <x:c r="O119" t="str">
+        <x:v>assets/art/environments/base_world_3d/env_base_world_kit_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P119" t="str">
+        <x:v>scenes/BaseWorld3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q119" t="str">
+        <x:v>基地;道路;废墟;3D;入口地图</x:v>
+      </x:c>
+      <x:c r="R119" t="str">
+        <x:f>LOWER(TRIM(C119)&amp;"|"&amp;TRIM(D119)&amp;"|"&amp;TRIM(E119)&amp;"|"&amp;TRIM(F119)&amp;"|"&amp;TRIM(H119)&amp;"|"&amp;TRIM(I119))</x:f>
+        <x:v>场景|base|base_world|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S119" t="str">
+        <x:f>IF(A119="","",IF(COUNTIF($R$6:$R$139,R119)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T119" t="str">
+        <x:v>63c840d59bcecefab946690136474c9ca7b70408fb7b6bcc264819f9b66f14a5</x:v>
+      </x:c>
+      <x:c r="U119" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V119" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W119" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X119" t="str">
+        <x:v>保留原2D布局语义；首张3D迁移地图</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str">
+        <x:v>PRP-BASE-FACILITY-3D</x:v>
+      </x:c>
+      <x:c r="B120" t="str">
+        <x:v>基地设施3D通用模块</x:v>
+      </x:c>
+      <x:c r="C120" t="str">
+        <x:v>场景道具</x:v>
+      </x:c>
+      <x:c r="D120" t="str">
+        <x:v>facility</x:v>
+      </x:c>
+      <x:c r="E120" t="str">
+        <x:v>base_facility_module</x:v>
+      </x:c>
+      <x:c r="F120" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G120" t="str">
+        <x:v>ENV-BASE-WORLD-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H120" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I120" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J120" t="str">
+        <x:v>8类基地设施</x:v>
+      </x:c>
+      <x:c r="K120" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L120" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M120" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N120" t="str">
+        <x:v>PackedScene/材质变体</x:v>
+      </x:c>
+      <x:c r="O120" t="str">
+        <x:v>assets/art/props/base_world_3d/prp_base_facility_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P120" t="str">
+        <x:v>src/base3d/BaseFacility3D.gd</x:v>
+      </x:c>
+      <x:c r="Q120" t="str">
+        <x:v>设施;交互;信标;3D</x:v>
+      </x:c>
+      <x:c r="R120" t="str">
+        <x:f>LOWER(TRIM(C120)&amp;"|"&amp;TRIM(D120)&amp;"|"&amp;TRIM(E120)&amp;"|"&amp;TRIM(F120)&amp;"|"&amp;TRIM(H120)&amp;"|"&amp;TRIM(I120))</x:f>
+        <x:v>场景道具|facility|base_facility_module|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S120" t="str">
+        <x:f>IF(A120="","",IF(COUNTIF($R$6:$R$139,R120)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T120" t="str">
+        <x:v>18921dbda4e5997f5c49c6efa66b7af030310d5d086b60fe476e8f0e664e104e</x:v>
+      </x:c>
+      <x:c r="U120" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V120" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W120" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X120" t="str">
+        <x:v>由配置生成8个设施变体；复用同一场景</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>PRP-DUNGEON-GATE-3D</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>地下城入口3D模块</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>场景道具</x:v>
+      </x:c>
+      <x:c r="D121" t="str">
+        <x:v>door</x:v>
+      </x:c>
+      <x:c r="E121" t="str">
+        <x:v>dungeon_gate</x:v>
+      </x:c>
+      <x:c r="F121" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G121" t="str">
+        <x:v>PRP-DUNGEON-GATE</x:v>
+      </x:c>
+      <x:c r="H121" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I121" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J121" t="str">
+        <x:v>4个地下城入口</x:v>
+      </x:c>
+      <x:c r="K121" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L121" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M121" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N121" t="str">
+        <x:v>PackedScene/材质变体</x:v>
+      </x:c>
+      <x:c r="O121" t="str">
+        <x:v>assets/art/props/base_world_3d/prp_dungeon_gate_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P121" t="str">
+        <x:v>src/base3d/DungeonEntrance3D.gd</x:v>
+      </x:c>
+      <x:c r="Q121" t="str">
+        <x:v>地下城;门;交互;3D</x:v>
+      </x:c>
+      <x:c r="R121" t="str">
+        <x:f>LOWER(TRIM(C121)&amp;"|"&amp;TRIM(D121)&amp;"|"&amp;TRIM(E121)&amp;"|"&amp;TRIM(F121)&amp;"|"&amp;TRIM(H121)&amp;"|"&amp;TRIM(I121))</x:f>
+        <x:v>场景道具|door|dungeon_gate|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S121" t="str">
+        <x:f>IF(A121="","",IF(COUNTIF($R$6:$R$139,R121)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T121" t="str">
+        <x:v>1fc802ceb8caef1ce77a54958a8b5e82a0fcae37459106fee970c8941146ba8f</x:v>
+      </x:c>
+      <x:c r="U121" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V121" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W121" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X121" t="str">
+        <x:v>保持旧入口ID与目标场景；地下城内部暂保留2D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="str">
+        <x:v>ENV-BASE-WORLD-3D-PREVIEW</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>入口基地3D验收预览</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D122" t="str">
+        <x:v>review_board</x:v>
+      </x:c>
+      <x:c r="E122" t="str">
+        <x:v>base_world</x:v>
+      </x:c>
+      <x:c r="F122" t="str">
+        <x:v>preview_3d</x:v>
+      </x:c>
+      <x:c r="G122" t="str">
+        <x:v>ENV-BASE-WORLD-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H122" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I122" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J122" t="str">
+        <x:v>评审与资产QA</x:v>
+      </x:c>
+      <x:c r="K122" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L122" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M122" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N122" t="str">
+        <x:v>1280×720 PNG</x:v>
+      </x:c>
+      <x:c r="O122" t="str">
+        <x:v>assets/art/environments/base_world_3d/env_base_world_preview_top3d_v001.png</x:v>
+      </x:c>
+      <x:c r="P122" t="str">
+        <x:v>verify_base_world_3d_visual.tscn</x:v>
+      </x:c>
+      <x:c r="Q122" t="str">
+        <x:v>3D预览;评审;入口地图</x:v>
+      </x:c>
+      <x:c r="R122" t="str">
+        <x:f>LOWER(TRIM(C122)&amp;"|"&amp;TRIM(D122)&amp;"|"&amp;TRIM(E122)&amp;"|"&amp;TRIM(F122)&amp;"|"&amp;TRIM(H122)&amp;"|"&amp;TRIM(I122))</x:f>
+        <x:v>场景|review_board|base_world|preview_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S122" t="str">
+        <x:f>IF(A122="","",IF(COUNTIF($R$6:$R$139,R122)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T122" t="str">
+        <x:v>7dc3ff5d1bb5942c8340359bfa6d55374604dfbc9fc8b2a23b68a3079fac2e01</x:v>
+      </x:c>
+      <x:c r="U122" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V122" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W122" t="str">
+        <x:v>项目运行截图</x:v>
+      </x:c>
+      <x:c r="X122" t="str">
+        <x:v>用于检查3D布局、镜头、组件比例与交互可读性</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="34" customHeight="1">
+      <x:c r="A123" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="B123" s="63" t="str">
+        <x:v>3D随机关卡通用房间套件</x:v>
+      </x:c>
+      <x:c r="C123" s="63" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D123" s="63" t="str">
+        <x:v>room</x:v>
+      </x:c>
+      <x:c r="E123" s="63" t="str">
+        <x:v>dungeon_runtime</x:v>
+      </x:c>
+      <x:c r="F123" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G123" s="63"/>
+      <x:c r="H123" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I123" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J123" s="63" t="str">
+        <x:v>四主题副本/随机房间</x:v>
+      </x:c>
+      <x:c r="K123" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L123" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M123" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N123" s="63" t="str">
+        <x:v>PackedScene/三档程序几何</x:v>
+      </x:c>
+      <x:c r="O123" s="63" t="str">
+        <x:v>assets/art/environments/dungeon_3d/env_dungeon_runtime_kit_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P123" s="63" t="str">
+        <x:v>src/world3d/DungeonRoom3D.gd</x:v>
+      </x:c>
+      <x:c r="Q123" s="63" t="str">
+        <x:v>房间;门洞;走廊;随机地图;3D</x:v>
+      </x:c>
+      <x:c r="R123" s="63" t="str">
+        <x:f>LOWER(TRIM(C123)&amp;"|"&amp;TRIM(D123)&amp;"|"&amp;TRIM(E123)&amp;"|"&amp;TRIM(F123)&amp;"|"&amp;TRIM(H123)&amp;"|"&amp;TRIM(I123))</x:f>
+        <x:v>场景|room|dungeon_runtime|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S123" s="63" t="str">
+        <x:f>IF(A123="","",IF(COUNTIF($R$6:$R$139,R123)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T123" s="63" t="str">
+        <x:v>fc33ac084150c3e3cbba89505b3e04f35712abbceaa5cec297c94fe4d7dcc2f3</x:v>
+      </x:c>
+      <x:c r="U123" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V123" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W123" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X123" s="63" t="str">
+        <x:v>small/medium/large；四向门；家具、搜索、服务、危险区共用根</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="34" customHeight="1">
+      <x:c r="A124" s="63" t="str">
+        <x:v>ENV-DUNGEON-IRON-FRONTIER-3D</x:v>
+      </x:c>
+      <x:c r="B124" s="63" t="str">
+        <x:v>冷钢边境3D主题资源</x:v>
+      </x:c>
+      <x:c r="C124" s="63" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D124" s="63" t="str">
+        <x:v>biome</x:v>
+      </x:c>
+      <x:c r="E124" s="63" t="str">
+        <x:v>iron_frontier</x:v>
+      </x:c>
+      <x:c r="F124" s="63" t="str">
+        <x:v>theme_3d</x:v>
+      </x:c>
+      <x:c r="G124" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H124" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I124" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J124" s="63" t="str">
+        <x:v>冷钢边境</x:v>
+      </x:c>
+      <x:c r="K124" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L124" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M124" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N124" s="63" t="str">
+        <x:v>DungeonTheme3D Resource</x:v>
+      </x:c>
+      <x:c r="O124" s="63" t="str">
+        <x:v>assets/art/environments/dungeon_3d/env_iron_frontier_kit_top3d_v001.tres</x:v>
+      </x:c>
+      <x:c r="P124" s="63" t="str">
+        <x:v>scenes/levels3d/IronFrontier3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q124" s="63" t="str">
+        <x:v>冷钢;冷蓝;边境;雾;灯光</x:v>
+      </x:c>
+      <x:c r="R124" s="63" t="str">
+        <x:f>LOWER(TRIM(C124)&amp;"|"&amp;TRIM(D124)&amp;"|"&amp;TRIM(E124)&amp;"|"&amp;TRIM(F124)&amp;"|"&amp;TRIM(H124)&amp;"|"&amp;TRIM(I124))</x:f>
+        <x:v>场景|biome|iron_frontier|theme_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S124" s="63" t="str">
+        <x:f>IF(A124="","",IF(COUNTIF($R$6:$R$139,R124)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T124" s="63" t="str">
+        <x:v>a3c6e7e5433928b790e1fa0fe5124beaeb5ab579f2d376aa35a1be25b6736b58</x:v>
+      </x:c>
+      <x:c r="U124" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V124" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W124" s="63" t="str">
+        <x:v>原创程序配置</x:v>
+      </x:c>
+      <x:c r="X124" s="63" t="str">
+        <x:v>只保存3D色彩/雾/灯光/家具倾向；玩法读取MapThemeProfile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="34" customHeight="1">
+      <x:c r="A125" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUST-FOUNDRY-3D</x:v>
+      </x:c>
+      <x:c r="B125" s="63" t="str">
+        <x:v>锈蚀铸造厂3D主题资源</x:v>
+      </x:c>
+      <x:c r="C125" s="63" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D125" s="63" t="str">
+        <x:v>biome</x:v>
+      </x:c>
+      <x:c r="E125" s="63" t="str">
+        <x:v>rust_foundry</x:v>
+      </x:c>
+      <x:c r="F125" s="63" t="str">
+        <x:v>theme_3d</x:v>
+      </x:c>
+      <x:c r="G125" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H125" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I125" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J125" s="63" t="str">
+        <x:v>锈蚀铸造厂</x:v>
+      </x:c>
+      <x:c r="K125" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L125" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M125" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N125" s="63" t="str">
+        <x:v>DungeonTheme3D Resource</x:v>
+      </x:c>
+      <x:c r="O125" s="63" t="str">
+        <x:v>assets/art/environments/dungeon_3d/env_rust_foundry_kit_top3d_v001.tres</x:v>
+      </x:c>
+      <x:c r="P125" s="63" t="str">
+        <x:v>scenes/levels3d/RustFoundry3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q125" s="63" t="str">
+        <x:v>锈蚀;铸造;橙光;工业</x:v>
+      </x:c>
+      <x:c r="R125" s="63" t="str">
+        <x:f>LOWER(TRIM(C125)&amp;"|"&amp;TRIM(D125)&amp;"|"&amp;TRIM(E125)&amp;"|"&amp;TRIM(F125)&amp;"|"&amp;TRIM(H125)&amp;"|"&amp;TRIM(I125))</x:f>
+        <x:v>场景|biome|rust_foundry|theme_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S125" s="63" t="str">
+        <x:f>IF(A125="","",IF(COUNTIF($R$6:$R$139,R125)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T125" s="63" t="str">
+        <x:v>0c14c1dd5a5b8edcb51fa5bb024666d845611bfd87c3c4ee0ded56c4614010a8</x:v>
+      </x:c>
+      <x:c r="U125" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V125" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W125" s="63" t="str">
+        <x:v>原创程序配置</x:v>
+      </x:c>
+      <x:c r="X125" s="63" t="str">
+        <x:v>复用通用房间根；主题资源不复制玩法规则</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="34" customHeight="1">
+      <x:c r="A126" s="63" t="str">
+        <x:v>ENV-DUNGEON-SPORE-DEPTHS-3D</x:v>
+      </x:c>
+      <x:c r="B126" s="63" t="str">
+        <x:v>孢子深层3D主题资源</x:v>
+      </x:c>
+      <x:c r="C126" s="63" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D126" s="63" t="str">
+        <x:v>biome</x:v>
+      </x:c>
+      <x:c r="E126" s="63" t="str">
+        <x:v>spore_depths</x:v>
+      </x:c>
+      <x:c r="F126" s="63" t="str">
+        <x:v>theme_3d</x:v>
+      </x:c>
+      <x:c r="G126" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H126" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I126" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J126" s="63" t="str">
+        <x:v>孢子深层</x:v>
+      </x:c>
+      <x:c r="K126" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L126" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M126" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N126" s="63" t="str">
+        <x:v>DungeonTheme3D Resource</x:v>
+      </x:c>
+      <x:c r="O126" s="63" t="str">
+        <x:v>assets/art/environments/dungeon_3d/env_spore_depths_kit_top3d_v001.tres</x:v>
+      </x:c>
+      <x:c r="P126" s="63" t="str">
+        <x:v>scenes/levels3d/SporeDepths3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q126" s="63" t="str">
+        <x:v>孢子;病绿;地下;异化</x:v>
+      </x:c>
+      <x:c r="R126" s="63" t="str">
+        <x:f>LOWER(TRIM(C126)&amp;"|"&amp;TRIM(D126)&amp;"|"&amp;TRIM(E126)&amp;"|"&amp;TRIM(F126)&amp;"|"&amp;TRIM(H126)&amp;"|"&amp;TRIM(I126))</x:f>
+        <x:v>场景|biome|spore_depths|theme_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S126" s="63" t="str">
+        <x:f>IF(A126="","",IF(COUNTIF($R$6:$R$139,R126)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T126" s="63" t="str">
+        <x:v>bbd5cc04028e3962ce9eb8ea04c1c06157d128b5dbad1cea64bed7b4a02e7689</x:v>
+      </x:c>
+      <x:c r="U126" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V126" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W126" s="63" t="str">
+        <x:v>原创程序配置</x:v>
+      </x:c>
+      <x:c r="X126" s="63" t="str">
+        <x:v>复用通用房间根；主题资源不复制玩法规则</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="34" customHeight="1">
+      <x:c r="A127" s="63" t="str">
+        <x:v>ENV-DUNGEON-ABYSS-ARCHIVE-3D</x:v>
+      </x:c>
+      <x:c r="B127" s="63" t="str">
+        <x:v>深渊档案库3D主题资源</x:v>
+      </x:c>
+      <x:c r="C127" s="63" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D127" s="63" t="str">
+        <x:v>biome</x:v>
+      </x:c>
+      <x:c r="E127" s="63" t="str">
+        <x:v>abyss_archive</x:v>
+      </x:c>
+      <x:c r="F127" s="63" t="str">
+        <x:v>theme_3d</x:v>
+      </x:c>
+      <x:c r="G127" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H127" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I127" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J127" s="63" t="str">
+        <x:v>深渊档案库</x:v>
+      </x:c>
+      <x:c r="K127" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L127" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M127" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N127" s="63" t="str">
+        <x:v>DungeonTheme3D Resource</x:v>
+      </x:c>
+      <x:c r="O127" s="63" t="str">
+        <x:v>assets/art/environments/dungeon_3d/env_abyss_archive_kit_top3d_v001.tres</x:v>
+      </x:c>
+      <x:c r="P127" s="63" t="str">
+        <x:v>scenes/levels3d/AbyssArchive3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q127" s="63" t="str">
+        <x:v>深渊;档案;紫光;禁区</x:v>
+      </x:c>
+      <x:c r="R127" s="63" t="str">
+        <x:f>LOWER(TRIM(C127)&amp;"|"&amp;TRIM(D127)&amp;"|"&amp;TRIM(E127)&amp;"|"&amp;TRIM(F127)&amp;"|"&amp;TRIM(H127)&amp;"|"&amp;TRIM(I127))</x:f>
+        <x:v>场景|biome|abyss_archive|theme_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S127" s="63" t="str">
+        <x:f>IF(A127="","",IF(COUNTIF($R$6:$R$139,R127)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T127" s="63" t="str">
+        <x:v>fb276fb1586de1b69d306ff894800f51da600b8dfb2780cf8bc8d22695ad3a52</x:v>
+      </x:c>
+      <x:c r="U127" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V127" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W127" s="63" t="str">
+        <x:v>原创程序配置</x:v>
+      </x:c>
+      <x:c r="X127" s="63" t="str">
+        <x:v>复用通用房间根；主题资源不复制玩法规则</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="34" customHeight="1">
+      <x:c r="A128" s="63" t="str">
+        <x:v>PRP-WASTELAND-LIGHT-3D</x:v>
+      </x:c>
+      <x:c r="B128" s="63" t="str">
+        <x:v>废土灯具3D通用模块</x:v>
+      </x:c>
+      <x:c r="C128" s="63" t="str">
+        <x:v>场景道具</x:v>
+      </x:c>
+      <x:c r="D128" s="63" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E128" s="63" t="str">
+        <x:v>wasteland_light</x:v>
+      </x:c>
+      <x:c r="F128" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G128" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H128" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I128" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J128" s="63" t="str">
+        <x:v>关卡/靶场照明</x:v>
+      </x:c>
+      <x:c r="K128" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L128" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M128" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N128" s="63" t="str">
+        <x:v>PackedScene/OmniLight3D</x:v>
+      </x:c>
+      <x:c r="O128" s="63" t="str">
+        <x:v>assets/art/props/dungeon_3d/prp_wasteland_light_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P128" s="63" t="str">
+        <x:v>src/world3d/WastelandLight3D.gd</x:v>
+      </x:c>
+      <x:c r="Q128" s="63" t="str">
+        <x:v>灯具;光池;故障灯;废土</x:v>
+      </x:c>
+      <x:c r="R128" s="63" t="str">
+        <x:f>LOWER(TRIM(C128)&amp;"|"&amp;TRIM(D128)&amp;"|"&amp;TRIM(E128)&amp;"|"&amp;TRIM(F128)&amp;"|"&amp;TRIM(H128)&amp;"|"&amp;TRIM(I128))</x:f>
+        <x:v>场景道具|light|wasteland_light|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S128" s="63" t="str">
+        <x:f>IF(A128="","",IF(COUNTIF($R$6:$R$139,R128)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T128" s="63" t="str">
+        <x:v>0a6ec0add8b6e01b83f4dbaae421ff0dc69ed08648d304bac061f540af27d99b</x:v>
+      </x:c>
+      <x:c r="U128" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V128" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W128" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X128" s="63" t="str">
+        <x:v>灯架、灯罩、真实光源、低频故障与地面光池同一根</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="34" customHeight="1">
+      <x:c r="A129" s="63" t="str">
+        <x:v>PRP-ROOM-FURNITURE-3D</x:v>
+      </x:c>
+      <x:c r="B129" s="63" t="str">
+        <x:v>房间家具3D通用模块</x:v>
+      </x:c>
+      <x:c r="C129" s="63" t="str">
+        <x:v>场景道具</x:v>
+      </x:c>
+      <x:c r="D129" s="63" t="str">
+        <x:v>furniture</x:v>
+      </x:c>
+      <x:c r="E129" s="63" t="str">
+        <x:v>room_furniture</x:v>
+      </x:c>
+      <x:c r="F129" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G129" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H129" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I129" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J129" s="63" t="str">
+        <x:v>全部3D房间</x:v>
+      </x:c>
+      <x:c r="K129" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L129" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M129" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N129" s="63" t="str">
+        <x:v>PackedScene/类型与尺寸配置</x:v>
+      </x:c>
+      <x:c r="O129" s="63" t="str">
+        <x:v>assets/art/props/dungeon_3d/prp_room_furniture_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P129" s="63" t="str">
+        <x:v>src/world3d/RoomFurniture3D.gd</x:v>
+      </x:c>
+      <x:c r="Q129" s="63" t="str">
+        <x:v>家具;小中大;箱柜;工作台</x:v>
+      </x:c>
+      <x:c r="R129" s="63" t="str">
+        <x:f>LOWER(TRIM(C129)&amp;"|"&amp;TRIM(D129)&amp;"|"&amp;TRIM(E129)&amp;"|"&amp;TRIM(F129)&amp;"|"&amp;TRIM(H129)&amp;"|"&amp;TRIM(I129))</x:f>
+        <x:v>场景道具|furniture|room_furniture|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S129" s="63" t="str">
+        <x:f>IF(A129="","",IF(COUNTIF($R$6:$R$139,R129)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T129" s="63" t="str">
+        <x:v>a78a7eaac02ce39add97d8a57754cc86ea34e740e24e0e901f4e037198a086e9</x:v>
+      </x:c>
+      <x:c r="U129" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V129" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W129" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X129" s="63" t="str">
+        <x:v>11类轮廓；small/medium/large影响占地与碰撞</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="34" customHeight="1">
+      <x:c r="A130" s="63" t="str">
+        <x:v>PRP-SEARCH-CONTAINER-3D</x:v>
+      </x:c>
+      <x:c r="B130" s="63" t="str">
+        <x:v>可搜索容器3D通用模块</x:v>
+      </x:c>
+      <x:c r="C130" s="63" t="str">
+        <x:v>场景道具</x:v>
+      </x:c>
+      <x:c r="D130" s="63" t="str">
+        <x:v>container</x:v>
+      </x:c>
+      <x:c r="E130" s="63" t="str">
+        <x:v>search_container</x:v>
+      </x:c>
+      <x:c r="F130" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G130" s="63" t="str">
+        <x:v>PRP-ROOM-FURNITURE-3D</x:v>
+      </x:c>
+      <x:c r="H130" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I130" s="63" t="str">
+        <x:v>closed_opened</x:v>
+      </x:c>
+      <x:c r="J130" s="63" t="str">
+        <x:v>搜索房/仓储/事件</x:v>
+      </x:c>
+      <x:c r="K130" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L130" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M130" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N130" s="63" t="str">
+        <x:v>PackedScene/搜索状态</x:v>
+      </x:c>
+      <x:c r="O130" s="63" t="str">
+        <x:v>assets/art/props/dungeon_3d/prp_search_container_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P130" s="63" t="str">
+        <x:v>src/world3d/RoomFurniture3D.gd</x:v>
+      </x:c>
+      <x:c r="Q130" s="63" t="str">
+        <x:v>搜索;容器;战利品;小中大</x:v>
+      </x:c>
+      <x:c r="R130" s="63" t="str">
+        <x:f>LOWER(TRIM(C130)&amp;"|"&amp;TRIM(D130)&amp;"|"&amp;TRIM(E130)&amp;"|"&amp;TRIM(F130)&amp;"|"&amp;TRIM(H130)&amp;"|"&amp;TRIM(I130))</x:f>
+        <x:v>场景道具|container|search_container|root_3d|俯视3d|closed_opened</x:v>
+      </x:c>
+      <x:c r="S130" s="63" t="str">
+        <x:f>IF(A130="","",IF(COUNTIF($R$6:$R$139,R130)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T130" s="63" t="str">
+        <x:v>2c0852d86e7c0e635e76197ff8d2f6a030daa186f760dfb339d3fdeddf3c192d</x:v>
+      </x:c>
+      <x:c r="U130" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V130" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W130" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X130" s="63" t="str">
+        <x:v>搜索为家具状态与配置，不建立关卡局部重复模型</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="34" customHeight="1">
+      <x:c r="A131" s="63" t="str">
+        <x:v>PRP-SERVICE-STATION-3D</x:v>
+      </x:c>
+      <x:c r="B131" s="63" t="str">
+        <x:v>废土服务终端3D模块</x:v>
+      </x:c>
+      <x:c r="C131" s="63" t="str">
+        <x:v>场景道具</x:v>
+      </x:c>
+      <x:c r="D131" s="63" t="str">
+        <x:v>facility</x:v>
+      </x:c>
+      <x:c r="E131" s="63" t="str">
+        <x:v>service_station</x:v>
+      </x:c>
+      <x:c r="F131" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G131" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H131" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I131" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J131" s="63" t="str">
+        <x:v>商店/升级/事件/重置</x:v>
+      </x:c>
+      <x:c r="K131" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L131" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M131" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N131" s="63" t="str">
+        <x:v>PackedScene/程序组件</x:v>
+      </x:c>
+      <x:c r="O131" s="63" t="str">
+        <x:v>assets/art/props/dungeon_3d/prp_service_station_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P131" s="63" t="str">
+        <x:v>src/world3d/ServiceStation3D.gd</x:v>
+      </x:c>
+      <x:c r="Q131" s="63" t="str">
+        <x:v>终端;商店;升级;事件;重置</x:v>
+      </x:c>
+      <x:c r="R131" s="63" t="str">
+        <x:f>LOWER(TRIM(C131)&amp;"|"&amp;TRIM(D131)&amp;"|"&amp;TRIM(E131)&amp;"|"&amp;TRIM(F131)&amp;"|"&amp;TRIM(H131)&amp;"|"&amp;TRIM(I131))</x:f>
+        <x:v>场景道具|facility|service_station|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S131" s="63" t="str">
+        <x:f>IF(A131="","",IF(COUNTIF($R$6:$R$139,R131)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T131" s="63" t="str">
+        <x:v>da288e4a8ffc005053741d2eda3bbcbf2f6ad34c32c6657e35d0ddf62b837be4</x:v>
+      </x:c>
+      <x:c r="U131" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V131" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W131" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X131" s="63" t="str">
+        <x:v>四种服务行为复用同一视觉与交互组件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="34" customHeight="1">
+      <x:c r="A132" s="63" t="str">
+        <x:v>PRP-EXTRACTION-BEACON-3D</x:v>
+      </x:c>
+      <x:c r="B132" s="63" t="str">
+        <x:v>撤离信标3D模块</x:v>
+      </x:c>
+      <x:c r="C132" s="63" t="str">
+        <x:v>场景道具</x:v>
+      </x:c>
+      <x:c r="D132" s="63" t="str">
+        <x:v>facility</x:v>
+      </x:c>
+      <x:c r="E132" s="63" t="str">
+        <x:v>extraction_beacon</x:v>
+      </x:c>
+      <x:c r="F132" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G132" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H132" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I132" s="63" t="str">
+        <x:v>locked_active_done</x:v>
+      </x:c>
+      <x:c r="J132" s="63" t="str">
+        <x:v>四主题撤离房</x:v>
+      </x:c>
+      <x:c r="K132" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L132" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M132" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N132" s="63" t="str">
+        <x:v>PackedScene/程序组件</x:v>
+      </x:c>
+      <x:c r="O132" s="63" t="str">
+        <x:v>assets/art/props/dungeon_3d/prp_extraction_beacon_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P132" s="63" t="str">
+        <x:v>src/world3d/ExtractionBeacon3D.gd</x:v>
+      </x:c>
+      <x:c r="Q132" s="63" t="str">
+        <x:v>撤离;信标;倒计时;Boss解锁</x:v>
+      </x:c>
+      <x:c r="R132" s="63" t="str">
+        <x:f>LOWER(TRIM(C132)&amp;"|"&amp;TRIM(D132)&amp;"|"&amp;TRIM(E132)&amp;"|"&amp;TRIM(F132)&amp;"|"&amp;TRIM(H132)&amp;"|"&amp;TRIM(I132))</x:f>
+        <x:v>场景道具|facility|extraction_beacon|root_3d|俯视3d|locked_active_done</x:v>
+      </x:c>
+      <x:c r="S132" s="63" t="str">
+        <x:f>IF(A132="","",IF(COUNTIF($R$6:$R$139,R132)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T132" s="63" t="str">
+        <x:v>f2638fdaca3f9542e918a56750bda04a5828b18a763569eb16a36619e9e336b4</x:v>
+      </x:c>
+      <x:c r="U132" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V132" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W132" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X132" s="63" t="str">
+        <x:v>锁定/同步/取消/完成四段生命周期</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="34" customHeight="1">
+      <x:c r="A133" s="63" t="str">
+        <x:v>VFX-HAZARD-FIELD-3D</x:v>
+      </x:c>
+      <x:c r="B133" s="63" t="str">
+        <x:v>房间危险场3D特效</x:v>
+      </x:c>
+      <x:c r="C133" s="63" t="str">
+        <x:v>特效</x:v>
+      </x:c>
+      <x:c r="D133" s="63" t="str">
+        <x:v>environment</x:v>
+      </x:c>
+      <x:c r="E133" s="63" t="str">
+        <x:v>hazard_field</x:v>
+      </x:c>
+      <x:c r="F133" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G133" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H133" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I133" s="63" t="str">
+        <x:v>active</x:v>
+      </x:c>
+      <x:c r="J133" s="63" t="str">
+        <x:v>陷阱房</x:v>
+      </x:c>
+      <x:c r="K133" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L133" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M133" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N133" s="63" t="str">
+        <x:v>PackedScene/程序环形特效</x:v>
+      </x:c>
+      <x:c r="O133" s="63" t="str">
+        <x:v>assets/art/vfx/environment_3d/vfx_hazard_field_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P133" s="63" t="str">
+        <x:v>src/world3d/HazardField3D.gd</x:v>
+      </x:c>
+      <x:c r="Q133" s="63" t="str">
+        <x:v>危险区;陷阱;范围伤害;3D</x:v>
+      </x:c>
+      <x:c r="R133" s="63" t="str">
+        <x:f>LOWER(TRIM(C133)&amp;"|"&amp;TRIM(D133)&amp;"|"&amp;TRIM(E133)&amp;"|"&amp;TRIM(F133)&amp;"|"&amp;TRIM(H133)&amp;"|"&amp;TRIM(I133))</x:f>
+        <x:v>特效|environment|hazard_field|root_3d|俯视3d|active</x:v>
+      </x:c>
+      <x:c r="S133" s="63" t="str">
+        <x:f>IF(A133="","",IF(COUNTIF($R$6:$R$139,R133)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T133" s="63" t="str">
+        <x:v>66ab8d6bc0e2729ca56c7f3c46a588e5f74890cfdf02b90de1fdc46fd1a67648</x:v>
+      </x:c>
+      <x:c r="U133" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V133" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W133" s="63" t="str">
+        <x:v>原创程序特效</x:v>
+      </x:c>
+      <x:c r="X133" s="63" t="str">
+        <x:v>颜色、半径与伤害可按主题配置</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="34" customHeight="1">
+      <x:c r="A134" s="63" t="str">
+        <x:v>WPN-GUN-KIT-3D</x:v>
+      </x:c>
+      <x:c r="B134" s="63" t="str">
+        <x:v>枪械3D通用模型套件</x:v>
+      </x:c>
+      <x:c r="C134" s="63" t="str">
+        <x:v>枪械</x:v>
+      </x:c>
+      <x:c r="D134" s="63" t="str">
+        <x:v>gunbody</x:v>
+      </x:c>
+      <x:c r="E134" s="63" t="str">
+        <x:v>blueprint_gun_catalog</x:v>
+      </x:c>
+      <x:c r="F134" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G134" s="63"/>
+      <x:c r="H134" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I134" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J134" s="63" t="str">
+        <x:v>玩家/靶场/全部副本</x:v>
+      </x:c>
+      <x:c r="K134" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L134" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M134" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N134" s="63" t="str">
+        <x:v>PackedScene/7枪配置模型</x:v>
+      </x:c>
+      <x:c r="O134" s="63" t="str">
+        <x:v>assets/art/weapons/weapon_3d/wpn_gun_kit_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P134" s="63" t="str">
+        <x:v>src/combat3d/WeaponModel3D.gd</x:v>
+      </x:c>
+      <x:c r="Q134" s="63" t="str">
+        <x:v>枪械;7枪身;8弹药;后坐力;枪口</x:v>
+      </x:c>
+      <x:c r="R134" s="63" t="str">
+        <x:f>LOWER(TRIM(C134)&amp;"|"&amp;TRIM(D134)&amp;"|"&amp;TRIM(E134)&amp;"|"&amp;TRIM(F134)&amp;"|"&amp;TRIM(H134)&amp;"|"&amp;TRIM(I134))</x:f>
+        <x:v>枪械|gunbody|blueprint_gun_catalog|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S134" s="63" t="str">
+        <x:f>IF(A134="","",IF(COUNTIF($R$6:$R$139,R134)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T134" s="63" t="str">
+        <x:v>e13801540404433f6fc5f00faa0f523b804d18ec7fa30c0f6c15fab48f1ec4c9</x:v>
+      </x:c>
+      <x:c r="U134" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V134" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W134" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X134" s="63" t="str">
+        <x:v>读取BlueprintRegistry唯一目录；覆盖56种组合；枪局部后坐力不带动手</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="34" customHeight="1">
+      <x:c r="A135" s="63" t="str">
+        <x:v>ENM-ECOSYSTEM-KIT-3D</x:v>
+      </x:c>
+      <x:c r="B135" s="63" t="str">
+        <x:v>七类怪物3D生态套件</x:v>
+      </x:c>
+      <x:c r="C135" s="63" t="str">
+        <x:v>敌人</x:v>
+      </x:c>
+      <x:c r="D135" s="63" t="str">
+        <x:v>normal_elite_boss</x:v>
+      </x:c>
+      <x:c r="E135" s="63" t="str">
+        <x:v>enemy_ecosystem</x:v>
+      </x:c>
+      <x:c r="F135" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G135" s="63"/>
+      <x:c r="H135" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I135" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J135" s="63" t="str">
+        <x:v>四主题战斗房</x:v>
+      </x:c>
+      <x:c r="K135" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L135" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M135" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N135" s="63" t="str">
+        <x:v>PackedScene/模块敌人</x:v>
+      </x:c>
+      <x:c r="O135" s="63" t="str">
+        <x:v>assets/art/enemies/enemy_3d/enm_ecosystem_kit_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P135" s="63" t="str">
+        <x:v>src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="Q135" s="63" t="str">
+        <x:v>怪物;七类;核心;外壳;附肢;状态</x:v>
+      </x:c>
+      <x:c r="R135" s="63" t="str">
+        <x:f>LOWER(TRIM(C135)&amp;"|"&amp;TRIM(D135)&amp;"|"&amp;TRIM(E135)&amp;"|"&amp;TRIM(F135)&amp;"|"&amp;TRIM(H135)&amp;"|"&amp;TRIM(I135))</x:f>
+        <x:v>敌人|normal_elite_boss|enemy_ecosystem|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S135" s="63" t="str">
+        <x:f>IF(A135="","",IF(COUNTIF($R$6:$R$139,R135)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T135" s="63" t="str">
+        <x:v>d9d8a49bed3fdcb863bad72f60be1f774309c7dda52753f5efb3d4e56159c12d</x:v>
+      </x:c>
+      <x:c r="U135" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V135" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W135" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X135" s="63" t="str">
+        <x:v>追猎/远程/召唤/盾甲/自爆/伏击/Boss；统一七态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="34" customHeight="1">
+      <x:c r="A136" s="63" t="str">
+        <x:v>VFX-COMBAT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="B136" s="63" t="str">
+        <x:v>战斗反馈3D通用特效套件</x:v>
+      </x:c>
+      <x:c r="C136" s="63" t="str">
+        <x:v>特效</x:v>
+      </x:c>
+      <x:c r="D136" s="63" t="str">
+        <x:v>combat</x:v>
+      </x:c>
+      <x:c r="E136" s="63" t="str">
+        <x:v>combat_feedback</x:v>
+      </x:c>
+      <x:c r="F136" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G136" s="63"/>
+      <x:c r="H136" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I136" s="63" t="str">
+        <x:v>muzzle_impact_damage_explosion</x:v>
+      </x:c>
+      <x:c r="J136" s="63" t="str">
+        <x:v>枪械/敌人/关卡</x:v>
+      </x:c>
+      <x:c r="K136" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L136" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M136" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N136" s="63" t="str">
+        <x:v>PackedScene/参数化特效</x:v>
+      </x:c>
+      <x:c r="O136" s="63" t="str">
+        <x:v>assets/art/vfx/combat_3d/vfx_combat_kit_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P136" s="63" t="str">
+        <x:v>src/combat3d/CombatEffect3D.gd</x:v>
+      </x:c>
+      <x:c r="Q136" s="63" t="str">
+        <x:v>枪口;命中;伤害;爆炸;3D</x:v>
+      </x:c>
+      <x:c r="R136" s="63" t="str">
+        <x:f>LOWER(TRIM(C136)&amp;"|"&amp;TRIM(D136)&amp;"|"&amp;TRIM(E136)&amp;"|"&amp;TRIM(F136)&amp;"|"&amp;TRIM(H136)&amp;"|"&amp;TRIM(I136))</x:f>
+        <x:v>特效|combat|combat_feedback|root_3d|俯视3d|muzzle_impact_damage_explosion</x:v>
+      </x:c>
+      <x:c r="S136" s="63" t="str">
+        <x:f>IF(A136="","",IF(COUNTIF($R$6:$R$139,R136)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T136" s="63" t="str">
+        <x:v>2ee5109b1876ea2114ac5c73b4bd0e2fc0348e1209a9d2ca16bc8ef9834ff357</x:v>
+      </x:c>
+      <x:c r="U136" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V136" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W136" s="63" t="str">
+        <x:v>原创程序特效</x:v>
+      </x:c>
+      <x:c r="X136" s="63" t="str">
+        <x:v>effect kind、颜色与尺寸参数化，避免每把枪复制特效</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="34" customHeight="1">
+      <x:c r="A137" s="63" t="str">
+        <x:v>ENV-TRAINING-RANGE-KIT-3D</x:v>
+      </x:c>
+      <x:c r="B137" s="63" t="str">
+        <x:v>独立3D训练靶场套件</x:v>
+      </x:c>
+      <x:c r="C137" s="63" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D137" s="63" t="str">
+        <x:v>training_range</x:v>
+      </x:c>
+      <x:c r="E137" s="63" t="str">
+        <x:v>training_range</x:v>
+      </x:c>
+      <x:c r="F137" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G137" s="63"/>
+      <x:c r="H137" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I137" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J137" s="63" t="str">
+        <x:v>独立训练地图</x:v>
+      </x:c>
+      <x:c r="K137" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L137" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M137" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N137" s="63" t="str">
+        <x:v>PackedScene/程序环境</x:v>
+      </x:c>
+      <x:c r="O137" s="63" t="str">
+        <x:v>assets/art/environments/training_range_3d/env_training_range_kit_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P137" s="63" t="str">
+        <x:v>scenes/TrainingRange3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q137" s="63" t="str">
+        <x:v>靶场;射击道;货架;56组合;三类靶</x:v>
+      </x:c>
+      <x:c r="R137" s="63" t="str">
+        <x:f>LOWER(TRIM(C137)&amp;"|"&amp;TRIM(D137)&amp;"|"&amp;TRIM(E137)&amp;"|"&amp;TRIM(F137)&amp;"|"&amp;TRIM(H137)&amp;"|"&amp;TRIM(I137))</x:f>
+        <x:v>场景|training_range|training_range|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S137" s="63" t="str">
+        <x:f>IF(A137="","",IF(COUNTIF($R$6:$R$139,R137)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T137" s="63" t="str">
+        <x:v>4d1153bc736fab0790300f171beef8435002670f3789d6434e966bca0a79d28e</x:v>
+      </x:c>
+      <x:c r="U137" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V137" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W137" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X137" s="63" t="str">
+        <x:v>15货架、三射击道、三靶标、重置与返回；BaseData隔离</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="34" customHeight="1">
+      <x:c r="A138" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D-PREVIEW</x:v>
+      </x:c>
+      <x:c r="B138" s="63" t="str">
+        <x:v>3D关卡运行时验收预览</x:v>
+      </x:c>
+      <x:c r="C138" s="63" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D138" s="63" t="str">
+        <x:v>review_board</x:v>
+      </x:c>
+      <x:c r="E138" s="63" t="str">
+        <x:v>dungeon_runtime</x:v>
+      </x:c>
+      <x:c r="F138" s="63" t="str">
+        <x:v>preview_3d</x:v>
+      </x:c>
+      <x:c r="G138" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H138" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I138" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J138" s="63" t="str">
+        <x:v>评审与资产QA</x:v>
+      </x:c>
+      <x:c r="K138" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L138" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M138" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N138" s="63" t="str">
+        <x:v>1280×720 PNG</x:v>
+      </x:c>
+      <x:c r="O138" s="63" t="str">
+        <x:v>assets/art/environments/dungeon_3d/env_dungeon_runtime_preview_top3d_v001.png</x:v>
+      </x:c>
+      <x:c r="P138" s="63" t="str">
+        <x:v>verify_full_3d_visual.tscn</x:v>
+      </x:c>
+      <x:c r="Q138" s="63" t="str">
+        <x:v>3D关卡;预览;灯光;战斗;QA</x:v>
+      </x:c>
+      <x:c r="R138" s="63" t="str">
+        <x:f>LOWER(TRIM(C138)&amp;"|"&amp;TRIM(D138)&amp;"|"&amp;TRIM(E138)&amp;"|"&amp;TRIM(F138)&amp;"|"&amp;TRIM(H138)&amp;"|"&amp;TRIM(I138))</x:f>
+        <x:v>场景|review_board|dungeon_runtime|preview_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S138" s="63" t="str">
+        <x:f>IF(A138="","",IF(COUNTIF($R$6:$R$139,R138)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T138" s="63" t="str">
+        <x:v>b6001154cf08404addb31b69dd38eaba41abe2a82ff6d2408bb5af8fe7a105b0</x:v>
+      </x:c>
+      <x:c r="U138" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V138" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W138" s="63" t="str">
+        <x:v>项目运行截图</x:v>
+      </x:c>
+      <x:c r="X138" s="63" t="str">
+        <x:v>真实GPU窗口检查房间、灯池、家具、角色、怪物和战斗可读性</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="34" customHeight="1">
+      <x:c r="A139" s="63" t="str">
+        <x:v>ENV-TRAINING-RANGE-3D-PREVIEW</x:v>
+      </x:c>
+      <x:c r="B139" s="63" t="str">
+        <x:v>3D训练靶场验收预览</x:v>
+      </x:c>
+      <x:c r="C139" s="63" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D139" s="63" t="str">
+        <x:v>review_board</x:v>
+      </x:c>
+      <x:c r="E139" s="63" t="str">
+        <x:v>training_range</x:v>
+      </x:c>
+      <x:c r="F139" s="63" t="str">
+        <x:v>preview_3d</x:v>
+      </x:c>
+      <x:c r="G139" s="63" t="str">
+        <x:v>ENV-TRAINING-RANGE-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H139" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I139" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J139" s="63" t="str">
+        <x:v>评审与资产QA</x:v>
+      </x:c>
+      <x:c r="K139" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L139" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M139" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N139" s="63" t="str">
+        <x:v>1280×720 PNG</x:v>
+      </x:c>
+      <x:c r="O139" s="63" t="str">
+        <x:v>assets/art/environments/training_range_3d/env_training_range_preview_top3d_v001.png</x:v>
+      </x:c>
+      <x:c r="P139" s="63" t="str">
+        <x:v>verify_training_range_3d_visual.tscn</x:v>
+      </x:c>
+      <x:c r="Q139" s="63" t="str">
+        <x:v>3D靶场;预览;射击道;目标;QA</x:v>
+      </x:c>
+      <x:c r="R139" s="63" t="str">
+        <x:f>LOWER(TRIM(C139)&amp;"|"&amp;TRIM(D139)&amp;"|"&amp;TRIM(E139)&amp;"|"&amp;TRIM(F139)&amp;"|"&amp;TRIM(H139)&amp;"|"&amp;TRIM(I139))</x:f>
+        <x:v>场景|review_board|training_range|preview_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S139" s="63" t="str">
+        <x:f>IF(A139="","",IF(COUNTIF($R$6:$R$139,R139)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T139" s="63" t="str">
+        <x:v>51b63097607e69009e9b2e5ed9315b3c642cdc05e823a2fee547cb0bb1ad8377</x:v>
+      </x:c>
+      <x:c r="U139" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V139" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W139" s="63" t="str">
+        <x:v>项目运行截图</x:v>
+      </x:c>
+      <x:c r="X139" s="63" t="str">
+        <x:v>真实GPU窗口检查三条射击道、三类靶、枪弹组合区与灯光</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8543,7 +10571,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89c057befe3b4ede"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2abd959a34ee4d7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8983,6 +11011,252 @@
       </x:c>
       <x:c r="M13" s="37" t="str">
         <x:v>必要时高于双手</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="34" customHeight="1">
+      <x:c r="A14" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B14" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="C14" s="63" t="str">
+        <x:v>Avatar3D/CapsuleAvatar3D/VisualRoot</x:v>
+      </x:c>
+      <x:c r="D14" s="63" t="str">
+        <x:v>player_root</x:v>
+      </x:c>
+      <x:c r="E14" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F14" s="63" t="str">
+        <x:v>Node3D</x:v>
+      </x:c>
+      <x:c r="G14" s="63" t="str">
+        <x:v>(0,0,0)</x:v>
+      </x:c>
+      <x:c r="H14" s="63" t="str">
+        <x:v>整体随准星绕Y轴</x:v>
+      </x:c>
+      <x:c r="I14" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J14" s="63" t="str">
+        <x:v>六态整体变换</x:v>
+      </x:c>
+      <x:c r="K14" s="63" t="str">
+        <x:v>3D表现根</x:v>
+      </x:c>
+      <x:c r="L14" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M14" s="63" t="str">
+        <x:v>与2D共用状态ID；摄像机不跟随VisualRoot旋转</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="34" customHeight="1">
+      <x:c r="A15" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B15" s="63" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="C15" s="63" t="str">
+        <x:v>VisualRoot/Body</x:v>
+      </x:c>
+      <x:c r="D15" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E15" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F15" s="63" t="str">
+        <x:v>CapsuleMesh</x:v>
+      </x:c>
+      <x:c r="G15" s="63" t="str">
+        <x:v>(0,0.88,0)</x:v>
+      </x:c>
+      <x:c r="H15" s="63" t="str">
+        <x:v>随root</x:v>
+      </x:c>
+      <x:c r="I15" s="63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J15" s="63" t="str">
+        <x:v>呼吸/移动压缩/死亡倾倒</x:v>
+      </x:c>
+      <x:c r="K15" s="63" t="str">
+        <x:v>防护服主体</x:v>
+      </x:c>
+      <x:c r="L15" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M15" s="63" t="str">
+        <x:v>无腿、无脚、无手臂</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="34" customHeight="1">
+      <x:c r="A16" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B16" s="63" t="str">
+        <x:v>scarf</x:v>
+      </x:c>
+      <x:c r="C16" s="63" t="str">
+        <x:v>VisualRoot/Scarf</x:v>
+      </x:c>
+      <x:c r="D16" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E16" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F16" s="63" t="str">
+        <x:v>Cylinder+Box</x:v>
+      </x:c>
+      <x:c r="G16" s="63" t="str">
+        <x:v>(0,1.43,0)</x:v>
+      </x:c>
+      <x:c r="H16" s="63" t="str">
+        <x:v>随root + 轻摆</x:v>
+      </x:c>
+      <x:c r="I16" s="63" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J16" s="63" t="str">
+        <x:v>移动滞后/冲刺飘动</x:v>
+      </x:c>
+      <x:c r="K16" s="63" t="str">
+        <x:v>身份配件</x:v>
+      </x:c>
+      <x:c r="L16" s="63" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="M16" s="63" t="str">
+        <x:v>独立红围巾组件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="34" customHeight="1">
+      <x:c r="A17" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B17" s="63" t="str">
+        <x:v>head</x:v>
+      </x:c>
+      <x:c r="C17" s="63" t="str">
+        <x:v>VisualRoot/Head</x:v>
+      </x:c>
+      <x:c r="D17" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E17" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F17" s="63" t="str">
+        <x:v>SphereMesh</x:v>
+      </x:c>
+      <x:c r="G17" s="63" t="str">
+        <x:v>(0,1.84,-0.01)</x:v>
+      </x:c>
+      <x:c r="H17" s="63" t="str">
+        <x:v>随root</x:v>
+      </x:c>
+      <x:c r="I17" s="63" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J17" s="63" t="str">
+        <x:v>呼吸滞后/受击/死亡</x:v>
+      </x:c>
+      <x:c r="K17" s="63" t="str">
+        <x:v>头壳/传感器</x:v>
+      </x:c>
+      <x:c r="L17" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M17" s="63" t="str">
+        <x:v>单传感器；无嘴无人脸</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="34" customHeight="1">
+      <x:c r="A18" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B18" s="63" t="str">
+        <x:v>hand</x:v>
+      </x:c>
+      <x:c r="C18" s="63" t="str">
+        <x:v>VisualRoot/Hand</x:v>
+      </x:c>
+      <x:c r="D18" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E18" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F18" s="63" t="str">
+        <x:v>SphereMesh</x:v>
+      </x:c>
+      <x:c r="G18" s="63" t="str">
+        <x:v>(0.72,1.22,-0.18)</x:v>
+      </x:c>
+      <x:c r="H18" s="63" t="str">
+        <x:v>随root；局部不旋转</x:v>
+      </x:c>
+      <x:c r="I18" s="63" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J18" s="63" t="str">
+        <x:v>随身体转向；保持局部握持位</x:v>
+      </x:c>
+      <x:c r="K18" s="63" t="str">
+        <x:v>唯一握持手</x:v>
+      </x:c>
+      <x:c r="L18" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M18" s="63" t="str">
+        <x:v>只有一只手；不单独追踪准星</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="34" customHeight="1">
+      <x:c r="A19" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B19" s="63" t="str">
+        <x:v>weapon_socket</x:v>
+      </x:c>
+      <x:c r="C19" s="63" t="str">
+        <x:v>VisualRoot/WeaponSocket</x:v>
+      </x:c>
+      <x:c r="D19" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E19" s="63" t="str">
+        <x:v>无纹理</x:v>
+      </x:c>
+      <x:c r="F19" s="63" t="str">
+        <x:v>Marker3D</x:v>
+      </x:c>
+      <x:c r="G19" s="63" t="str">
+        <x:v>(0.72,1.24,-0.34)</x:v>
+      </x:c>
+      <x:c r="H19" s="63" t="str">
+        <x:v>随root；局部不旋转</x:v>
+      </x:c>
+      <x:c r="I19" s="63" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J19" s="63" t="str">
+        <x:v>枪械挂载/枪口特效</x:v>
+      </x:c>
+      <x:c r="K19" s="63" t="str">
+        <x:v>武器系统</x:v>
+      </x:c>
+      <x:c r="L19" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M19" s="63" t="str">
+        <x:v>挂点与手保持固定局部关系；枪身读取BlueprintRegistry并只做局部后坐力</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9049,7 +11323,7 @@
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>顶层六态互斥；Low HP / Silenced / Invincible 是可叠加层。首版用组件变换，新增逐帧图前先查本表</x:v>
+        <x:v>2D/3D 共用六态 ID 与转换白名单；Low HP / Silenced / Invincible 为叠加层。3D 首版继续用组件变换，新增动画前先查本表</x:v>
       </x:c>
       <x:c r="B3" s="6"/>
       <x:c r="C3" s="6"/>
@@ -9136,7 +11410,7 @@
         <x:v>HUD 待命</x:v>
       </x:c>
       <x:c r="L6" s="36" t="str">
-        <x:v>代码变换；单手离散镜像插槽</x:v>
+        <x:v>2D/3D组件变换；单手保持局部挂点</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -9174,7 +11448,7 @@
         <x:v>地面划痕</x:v>
       </x:c>
       <x:c r="L7" s="37" t="str">
-        <x:v>代码变换；枪械独立连续瞄准</x:v>
+        <x:v>2D/3D组件变换；整体表现根随准星转向</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -9212,7 +11486,7 @@
         <x:v>青色尾迹</x:v>
       </x:c>
       <x:c r="L8" s="37" t="str">
-        <x:v>代码变换 + 程序尾迹；局部距离不变</x:v>
+        <x:v>2D/3D组件变换 + 程序尾迹；握持关系不变</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -9250,7 +11524,7 @@
         <x:v>红闪/屏闪</x:v>
       </x:c>
       <x:c r="L9" s="37" t="str">
-        <x:v>0.14s 整体变换；握持关系不变</x:v>
+        <x:v>2D/3D受击压缩/闪色；握持关系不变</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -9288,7 +11562,7 @@
         <x:v>琥珀锁定环</x:v>
       </x:c>
       <x:c r="L10" s="37" t="str">
-        <x:v>代码变换；握持关系不变</x:v>
+        <x:v>2D/3D降亮 + 锁定环；输入锁转换一致</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -9326,7 +11600,7 @@
         <x:v>HUD 终止</x:v>
       </x:c>
       <x:c r="L11" s="37" t="str">
-        <x:v>终态守卫 + 整体倾倒</x:v>
+        <x:v>2D/3D终态守卫 + 整体倾倒</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -9441,6 +11715,326 @@
       </x:c>
       <x:c r="L14" s="37" t="str">
         <x:v>InvincibleTimer 唯一解除</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="63" t="str">
+        <x:v>Enemy3D 七态状态机 × 模块表现映射</x:v>
+      </x:c>
+      <x:c r="B16" s="63"/>
+      <x:c r="C16" s="63"/>
+      <x:c r="D16" s="63"/>
+      <x:c r="E16" s="63"/>
+      <x:c r="F16" s="63"/>
+      <x:c r="G16" s="63"/>
+      <x:c r="H16" s="63"/>
+      <x:c r="I16" s="63"/>
+      <x:c r="J16" s="63"/>
+      <x:c r="K16" s="63"/>
+      <x:c r="L16" s="63"/>
+    </x:row>
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" s="63" t="str">
+        <x:v>层级</x:v>
+      </x:c>
+      <x:c r="B17" s="63" t="str">
+        <x:v>状态ID</x:v>
+      </x:c>
+      <x:c r="C17" s="63" t="str">
+        <x:v>中文名</x:v>
+      </x:c>
+      <x:c r="D17" s="63" t="str">
+        <x:v>允许来源</x:v>
+      </x:c>
+      <x:c r="E17" s="63" t="str">
+        <x:v>允许去向</x:v>
+      </x:c>
+      <x:c r="F17" s="63" t="str">
+        <x:v>Core</x:v>
+      </x:c>
+      <x:c r="G17" s="63" t="str">
+        <x:v>Shell</x:v>
+      </x:c>
+      <x:c r="H17" s="63" t="str">
+        <x:v>Appendages</x:v>
+      </x:c>
+      <x:c r="I17" s="63" t="str">
+        <x:v>StateVFX</x:v>
+      </x:c>
+      <x:c r="J17" s="63" t="str">
+        <x:v>行为职责</x:v>
+      </x:c>
+      <x:c r="K17" s="63" t="str">
+        <x:v>验收</x:v>
+      </x:c>
+      <x:c r="L17" s="63" t="str">
+        <x:v>首版实现</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="63" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B18" s="63" t="str">
+        <x:v>idle</x:v>
+      </x:c>
+      <x:c r="C18" s="63" t="str">
+        <x:v>待机</x:v>
+      </x:c>
+      <x:c r="D18" s="63" t="str">
+        <x:v>start/stagger</x:v>
+      </x:c>
+      <x:c r="E18" s="63" t="str">
+        <x:v>alert/dead</x:v>
+      </x:c>
+      <x:c r="F18" s="63" t="str">
+        <x:v>低频脉冲</x:v>
+      </x:c>
+      <x:c r="G18" s="63" t="str">
+        <x:v>轻浮动</x:v>
+      </x:c>
+      <x:c r="H18" s="63" t="str">
+        <x:v>低速</x:v>
+      </x:c>
+      <x:c r="I18" s="63" t="str">
+        <x:v>关闭</x:v>
+      </x:c>
+      <x:c r="J18" s="63" t="str">
+        <x:v>等待目标</x:v>
+      </x:c>
+      <x:c r="K18" s="63" t="str">
+        <x:v>静态轮廓可读</x:v>
+      </x:c>
+      <x:c r="L18" s="63" t="str">
+        <x:v>模块变换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="42" customHeight="1">
+      <x:c r="A19" s="63" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B19" s="63" t="str">
+        <x:v>alert</x:v>
+      </x:c>
+      <x:c r="C19" s="63" t="str">
+        <x:v>警觉</x:v>
+      </x:c>
+      <x:c r="D19" s="63" t="str">
+        <x:v>idle</x:v>
+      </x:c>
+      <x:c r="E19" s="63" t="str">
+        <x:v>chase/dead</x:v>
+      </x:c>
+      <x:c r="F19" s="63" t="str">
+        <x:v>加速</x:v>
+      </x:c>
+      <x:c r="G19" s="63" t="str">
+        <x:v>抬升</x:v>
+      </x:c>
+      <x:c r="H19" s="63" t="str">
+        <x:v>展开</x:v>
+      </x:c>
+      <x:c r="I19" s="63" t="str">
+        <x:v>关闭</x:v>
+      </x:c>
+      <x:c r="J19" s="63" t="str">
+        <x:v>发现玩家</x:v>
+      </x:c>
+      <x:c r="K19" s="63" t="str">
+        <x:v>0.28s响应</x:v>
+      </x:c>
+      <x:c r="L19" s="63" t="str">
+        <x:v>模块变换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="42" customHeight="1">
+      <x:c r="A20" s="63" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B20" s="63" t="str">
+        <x:v>chase</x:v>
+      </x:c>
+      <x:c r="C20" s="63" t="str">
+        <x:v>追击</x:v>
+      </x:c>
+      <x:c r="D20" s="63" t="str">
+        <x:v>alert/attack/stagger</x:v>
+      </x:c>
+      <x:c r="E20" s="63" t="str">
+        <x:v>telegraph/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F20" s="63" t="str">
+        <x:v>稳定</x:v>
+      </x:c>
+      <x:c r="G20" s="63" t="str">
+        <x:v>朝目标</x:v>
+      </x:c>
+      <x:c r="H20" s="63" t="str">
+        <x:v>步态</x:v>
+      </x:c>
+      <x:c r="I20" s="63" t="str">
+        <x:v>关闭</x:v>
+      </x:c>
+      <x:c r="J20" s="63" t="str">
+        <x:v>距离控制</x:v>
+      </x:c>
+      <x:c r="K20" s="63" t="str">
+        <x:v>七类速度差</x:v>
+      </x:c>
+      <x:c r="L20" s="63" t="str">
+        <x:v>CharacterBody3D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="42" customHeight="1">
+      <x:c r="A21" s="63" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B21" s="63" t="str">
+        <x:v>telegraph</x:v>
+      </x:c>
+      <x:c r="C21" s="63" t="str">
+        <x:v>预警</x:v>
+      </x:c>
+      <x:c r="D21" s="63" t="str">
+        <x:v>chase</x:v>
+      </x:c>
+      <x:c r="E21" s="63" t="str">
+        <x:v>attack/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F21" s="63" t="str">
+        <x:v>高频脉冲</x:v>
+      </x:c>
+      <x:c r="G21" s="63" t="str">
+        <x:v>稳定</x:v>
+      </x:c>
+      <x:c r="H21" s="63" t="str">
+        <x:v>蓄势</x:v>
+      </x:c>
+      <x:c r="I21" s="63" t="str">
+        <x:v>红色预警环</x:v>
+      </x:c>
+      <x:c r="J21" s="63" t="str">
+        <x:v>攻击前摇</x:v>
+      </x:c>
+      <x:c r="K21" s="63" t="str">
+        <x:v>不可省略</x:v>
+      </x:c>
+      <x:c r="L21" s="63" t="str">
+        <x:v>计时状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="42" customHeight="1">
+      <x:c r="A22" s="63" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B22" s="63" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="C22" s="63" t="str">
+        <x:v>攻击</x:v>
+      </x:c>
+      <x:c r="D22" s="63" t="str">
+        <x:v>telegraph</x:v>
+      </x:c>
+      <x:c r="E22" s="63" t="str">
+        <x:v>chase/dead</x:v>
+      </x:c>
+      <x:c r="F22" s="63" t="str">
+        <x:v>峰值</x:v>
+      </x:c>
+      <x:c r="G22" s="63" t="str">
+        <x:v>反冲</x:v>
+      </x:c>
+      <x:c r="H22" s="63" t="str">
+        <x:v>执行</x:v>
+      </x:c>
+      <x:c r="I22" s="63" t="str">
+        <x:v>按攻击类型</x:v>
+      </x:c>
+      <x:c r="J22" s="63" t="str">
+        <x:v>近战/远程/召唤/爆炸</x:v>
+      </x:c>
+      <x:c r="K22" s="63" t="str">
+        <x:v>七类差异</x:v>
+      </x:c>
+      <x:c r="L22" s="63" t="str">
+        <x:v>profile策略</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="42" customHeight="1">
+      <x:c r="A23" s="63" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B23" s="63" t="str">
+        <x:v>stagger</x:v>
+      </x:c>
+      <x:c r="C23" s="63" t="str">
+        <x:v>硬直</x:v>
+      </x:c>
+      <x:c r="D23" s="63" t="str">
+        <x:v>任意存活态</x:v>
+      </x:c>
+      <x:c r="E23" s="63" t="str">
+        <x:v>chase/dead</x:v>
+      </x:c>
+      <x:c r="F23" s="63" t="str">
+        <x:v>闪色</x:v>
+      </x:c>
+      <x:c r="G23" s="63" t="str">
+        <x:v>冲击</x:v>
+      </x:c>
+      <x:c r="H23" s="63" t="str">
+        <x:v>暂停</x:v>
+      </x:c>
+      <x:c r="I23" s="63" t="str">
+        <x:v>伤害反馈</x:v>
+      </x:c>
+      <x:c r="J23" s="63" t="str">
+        <x:v>受击窗口</x:v>
+      </x:c>
+      <x:c r="K23" s="63" t="str">
+        <x:v>方向可读</x:v>
+      </x:c>
+      <x:c r="L23" s="63" t="str">
+        <x:v>统一伤害入口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="42" customHeight="1">
+      <x:c r="A24" s="63" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B24" s="63" t="str">
+        <x:v>dead</x:v>
+      </x:c>
+      <x:c r="C24" s="63" t="str">
+        <x:v>死亡</x:v>
+      </x:c>
+      <x:c r="D24" s="63" t="str">
+        <x:v>任意存活态</x:v>
+      </x:c>
+      <x:c r="E24" s="63" t="str">
+        <x:v>无（终态）</x:v>
+      </x:c>
+      <x:c r="F24" s="63" t="str">
+        <x:v>熄灭</x:v>
+      </x:c>
+      <x:c r="G24" s="63" t="str">
+        <x:v>压扁</x:v>
+      </x:c>
+      <x:c r="H24" s="63" t="str">
+        <x:v>停止</x:v>
+      </x:c>
+      <x:c r="I24" s="63" t="str">
+        <x:v>爆散/淡出</x:v>
+      </x:c>
+      <x:c r="J24" s="63" t="str">
+        <x:v>掉落与计数</x:v>
+      </x:c>
+      <x:c r="K24" s="63" t="str">
+        <x:v>不可回存活态</x:v>
+      </x:c>
+      <x:c r="L24" s="63" t="str">
+        <x:v>终态 + Tween</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9526,7 +12120,7 @@
         <x:v>assets/art/characters/</x:v>
       </x:c>
       <x:c r="E6" s="36" t="str">
-        <x:v>chr_{role}_{name}{nn}_{component}_{view}_v{nnn}.png</x:v>
+        <x:v>chr_{role}_{name}{nn}_{component}_{view}_v{nnn}.{png|glb|tscn}</x:v>
       </x:c>
       <x:c r="F6" s="36" t="str">
         <x:v>CHR-PLY-CAPSULE01-HEAD-SIDE</x:v>
@@ -9546,7 +12140,7 @@
         <x:v>assets/art/enemies/</x:v>
       </x:c>
       <x:c r="E7" s="37" t="str">
-        <x:v>enm_{archetype}_{name}{nn}_{part}_{view}_v{nnn}.png</x:v>
+        <x:v>enm_{archetype}_{name}{nn}_{part}_{view}_v{nnn}.{png|glb|tscn}</x:v>
       </x:c>
       <x:c r="F7" s="37" t="str">
         <x:v>ENM-MELEE-FUNGBOAR01-BODY</x:v>
@@ -9566,7 +12160,7 @@
         <x:v>assets/art/weapons/</x:v>
       </x:c>
       <x:c r="E8" s="37" t="str">
-        <x:v>wpn_{family}_{logic_id}_{view}_v{nnn}.png</x:v>
+        <x:v>wpn_{family}_{logic_id}_{view}_v{nnn}.{png|glb|tscn}</x:v>
       </x:c>
       <x:c r="F8" s="37" t="str">
         <x:v>WPN-GUN-BP-PISTOL-SIDE</x:v>
@@ -9606,7 +12200,7 @@
         <x:v>assets/art/environments/</x:v>
       </x:c>
       <x:c r="E10" s="37" t="str">
-        <x:v>env_{biome}_{set}_{piece}_v{nnn}.png</x:v>
+        <x:v>env_{biome}_{set}_{piece}_v{nnn}.{png|glb|tres|tscn}</x:v>
       </x:c>
       <x:c r="F10" s="37" t="str">
         <x:v>ENV-IRON-FRONTIER-FLOOR-A</x:v>
@@ -9626,7 +12220,7 @@
         <x:v>assets/art/props/</x:v>
       </x:c>
       <x:c r="E11" s="37" t="str">
-        <x:v>prp_{set}_{logic_id}_{state}_v{nnn}.png</x:v>
+        <x:v>prp_{set}_{logic_id}_{state}_v{nnn}.{png|glb|tscn}</x:v>
       </x:c>
       <x:c r="F11" s="37" t="str">
         <x:v>PRP-BASE-WORKBENCH-IDLE</x:v>
@@ -9666,7 +12260,7 @@
         <x:v>assets/art/vfx/</x:v>
       </x:c>
       <x:c r="E13" s="37" t="str">
-        <x:v>vfx_{system}_{effect}_{variant}_v{nnn}.png</x:v>
+        <x:v>vfx_{system}_{effect}_{variant}_v{nnn}.{png|glb|tscn}</x:v>
       </x:c>
       <x:c r="F13" s="37" t="str">
         <x:v>VFX-PLAYER-DASH-TRAIL-A</x:v>
@@ -9887,22 +12481,22 @@
         <x:v>组件制作</x:v>
       </x:c>
       <x:c r="C10" s="37" t="str">
-        <x:v>角色组件契约/挂点</x:v>
+        <x:v>角色/房间/家具尺寸/枪械/怪物/灯具共用根</x:v>
       </x:c>
       <x:c r="D10" s="37" t="str">
-        <x:v>独立透明 PNG；共同像素密度</x:v>
+        <x:v>组件独立；3D用配置与父子变体</x:v>
       </x:c>
       <x:c r="E10" s="37" t="str">
-        <x:v>手臂并回 body；武器烘焙进手</x:v>
+        <x:v>关卡内复制枪表/房间/怪物根</x:v>
       </x:c>
       <x:c r="F10" s="37" t="str">
-        <x:v>悬浮主手</x:v>
+        <x:v>large可搜索柜</x:v>
       </x:c>
       <x:c r="G10" s="37" t="str">
-        <x:v>独立 hand_r + weapon_socket</x:v>
+        <x:v>复用RoomFurniture3D + size=large</x:v>
       </x:c>
       <x:c r="H10" s="37" t="str">
-        <x:v>F/N/O</x:v>
+        <x:v>F/N/O/X</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -9913,19 +12507,19 @@
         <x:v>验收</x:v>
       </x:c>
       <x:c r="C11" s="37" t="str">
-        <x:v>透明边缘、比例、状态矩阵、游戏内截图</x:v>
+        <x:v>透明边缘或3D灯光/雾/碰撞/状态/节点预算</x:v>
       </x:c>
       <x:c r="D11" s="37" t="str">
-        <x:v>最近邻清晰；六态无遮挡</x:v>
+        <x:v>真实游戏镜头与严格专项通过</x:v>
       </x:c>
       <x:c r="E11" s="37" t="str">
-        <x:v>只看母版不进游戏</x:v>
+        <x:v>只看母版或编辑器预览</x:v>
       </x:c>
       <x:c r="F11" s="37" t="str">
-        <x:v>capsule01 v001</x:v>
+        <x:v>3D主题关卡</x:v>
       </x:c>
       <x:c r="G11" s="37" t="str">
-        <x:v>verify_player_pixel_art_flow PASS</x:v>
+        <x:v>seed/灯池/七怪/56组合/撤离 PASS</x:v>
       </x:c>
       <x:c r="H11" s="37" t="str">
         <x:v>K/P/X</x:v>
@@ -9985,7 +12579,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="56" t="str">
-        <x:v>命名正则：文件名 ^[a-z0-9]+(?:_[a-z0-9]+)*_v[0-9]{3}\.(png|webp|svg|wav|ogg)$ ｜ AssetID ^[A-Z0-9]+(?:-[A-Z0-9]+)+$</x:v>
+        <x:v>命名正则：文件名 ^[a-z0-9]+(?:_[a-z0-9]+)*_v[0-9]{3}\.(png|webp|svg|wav|ogg|glb|gltf|tres|tscn)$ ｜ AssetID ^[A-Z0-9]+(?:-[A-Z0-9]+)+$</x:v>
       </x:c>
       <x:c r="B17" s="56"/>
       <x:c r="C17" s="56"/>
@@ -10511,6 +13105,52 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="9" ht="48" customHeight="1">
+      <x:c r="A9" s="63" t="str">
+        <x:v>v1.3</x:v>
+      </x:c>
+      <x:c r="B9" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="C9" s="63" t="str">
+        <x:v>3D变体登记</x:v>
+      </x:c>
+      <x:c r="D9" s="63" t="str">
+        <x:v>入口基地 / player_capsule01</x:v>
+      </x:c>
+      <x:c r="E9" s="63" t="str">
+        <x:v>登记首张3D入口地图、设施/入口模块、3D角色root/body/head/hand/scarf/socket；六态ID与2D保持一致</x:v>
+      </x:c>
+      <x:c r="F9" s="63" t="str">
+        <x:v>保留原2D资产与场景作为基线</x:v>
+      </x:c>
+      <x:c r="G9" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="58" customHeight="1">
+      <x:c r="A10" s="63" t="str">
+        <x:v>v1.4</x:v>
+      </x:c>
+      <x:c r="B10" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="C10" s="63" t="str">
+        <x:v>全游戏3D原型登记</x:v>
+      </x:c>
+      <x:c r="D10" s="63" t="str">
+        <x:v>四主题副本 / 靶场 / 战斗 / 共用资产</x:v>
+      </x:c>
+      <x:c r="E10" s="63" t="str">
+        <x:v>登记通用房间、4主题、灯具、三档家具与搜索、服务/撤离、枪械、七怪、战斗VFX、3D靶场和两张GPU验收预览</x:v>
+      </x:c>
+      <x:c r="F10" s="63" t="str">
+        <x:v>复用原玩法ID与BlueprintRegistry；保留2D基线</x:v>
+      </x:c>
+      <x:c r="G10" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G2"/>

--- a/outputs/019f8417-e7f4-7bc3-aded-c62dfd1d1462/ShellStorm2_美术资产台账_v001.xlsx
+++ b/outputs/019f8417-e7f4-7bc3-aded-c62dfd1d1462/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R97459e44b4534c7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R14cc543c2d0b4973"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R7790dbc62de644e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R046ed2fbaaef4304"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R8573fe1a4d684450"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rb7a5b573dea048ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R99f70fcbf0544d95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rfc9fec22444b442f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf037c12262a645be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R3e1cd7d8497b4ae3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rdf02083753b14321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rabe250e950244608"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R039802b8ef1641a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rb8d16a866a6d4d67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R9ea68df7be064d6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R8059162294d64002"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="18">
+  <x:fonts count="19">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -126,8 +126,14 @@
       <x:color rgb="FF176C4A"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -162,6 +168,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFD9F3E8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF10212C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF10212C"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -214,7 +230,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="65">
+  <x:cellXfs count="72">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -361,6 +377,27 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -725,23 +762,27 @@
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="45" t="n">
-        <x:v>134</x:v>
+        <x:f>COUNTA('资产主表'!$A$6:$A$200)</x:f>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B6" s="43"/>
       <x:c r="C6" s="45" t="n">
-        <x:v>34</x:v>
+        <x:f>COUNTIF('资产主表'!$K$6:$K$200,"已完成")+COUNTIF('资产主表'!$K$6:$K$200,"原型已接入")</x:f>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D6" s="43"/>
       <x:c r="E6" s="45" t="n">
-        <x:v>99</x:v>
+        <x:f>COUNTIF('资产主表'!$K$6:$K$200,"待制作")+COUNTIF('资产主表'!$K$6:$K$200,"程序占位")</x:f>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F6" s="43"/>
       <x:c r="G6" s="45" t="n">
+        <x:f>COUNTIF('资产主表'!$S$6:$S$200,"重复")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="43"/>
       <x:c r="I6" s="46" t="str">
-        <x:v>全3D闭环 / 三档房间 / 七类怪 / 56枪弹组合 / 废土灯池</x:v>
+        <x:v>全3D闭环 / 三档房间 / 暗室开关 / 七类怪 / 56枪弹组合</x:v>
       </x:c>
       <x:c r="J6" s="46"/>
     </x:row>
@@ -820,9 +861,11 @@
         <x:v>敌人</x:v>
       </x:c>
       <x:c r="B11" s="52" t="n">
+        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A11)</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="52" t="n">
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A11,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A11,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D11" s="43"/>
@@ -844,9 +887,11 @@
         <x:v>枪械</x:v>
       </x:c>
       <x:c r="B12" s="52" t="n">
+        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A12)</x:f>
         <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="52" t="n">
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A12,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A12,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D12" s="43"/>
@@ -868,9 +913,11 @@
         <x:v>道具</x:v>
       </x:c>
       <x:c r="B13" s="52" t="n">
+        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A13)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="C13" s="52" t="n">
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A13,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A13,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="43"/>
@@ -892,9 +939,11 @@
         <x:v>场景</x:v>
       </x:c>
       <x:c r="B14" s="52" t="n">
+        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A14)</x:f>
         <x:v>28</x:v>
       </x:c>
       <x:c r="C14" s="52" t="n">
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A14,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A14,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="D14" s="43"/>
@@ -902,7 +951,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F14" s="52" t="str">
-        <x:v>游戏内、状态矩阵、透明边缘三项验收</x:v>
+        <x:v>游戏内表现、状态机、玩法逻辑、性能四项验收</x:v>
       </x:c>
       <x:c r="G14" s="52" t="str">
         <x:v>通过后填写路径、尺寸、哈希、日期</x:v>
@@ -916,10 +965,12 @@
         <x:v>场景道具</x:v>
       </x:c>
       <x:c r="B15" s="52" t="n">
-        <x:v>17</x:v>
+        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A15)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C15" s="52" t="n">
-        <x:v>7</x:v>
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A15,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A15,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D15" s="43"/>
       <x:c r="E15" s="43"/>
@@ -934,10 +985,12 @@
         <x:v>UI</x:v>
       </x:c>
       <x:c r="B16" s="52" t="n">
-        <x:v>13</x:v>
+        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A16)</x:f>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C16" s="52" t="n">
-        <x:v>0</x:v>
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A16,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A16,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D16" s="43"/>
       <x:c r="E16" s="43"/>
@@ -952,10 +1005,12 @@
         <x:v>特效</x:v>
       </x:c>
       <x:c r="B17" s="52" t="n">
-        <x:v>14</x:v>
+        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A17)</x:f>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C17" s="52" t="n">
-        <x:v>2</x:v>
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A17,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A17,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D17" s="43"/>
       <x:c r="E17" s="43"/>
@@ -970,9 +1025,11 @@
         <x:v>音频</x:v>
       </x:c>
       <x:c r="B18" s="52" t="n">
+        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A18)</x:f>
         <x:v>13</x:v>
       </x:c>
       <x:c r="C18" s="52" t="n">
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A18,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A18,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D18" s="43"/>
@@ -1259,7 +1316,7 @@
         <x:v>角色|player|player_capsule01|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S6" s="36" t="str">
-        <x:f>IF(A6="","",IF(COUNTIF($R$6:$R$139,R6)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A6="","",IF(COUNTIF($R$6:$R$145,R6)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T6" s="36" t="str"/>
@@ -1333,7 +1390,7 @@
         <x:v>角色|player_component|player_capsule01|head|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S7" s="37" t="str">
-        <x:f>IF(A7="","",IF(COUNTIF($R$6:$R$139,R7)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A7="","",IF(COUNTIF($R$6:$R$145,R7)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T7" s="37" t="str">
@@ -1409,7 +1466,7 @@
         <x:v>角色|player_component|player_capsule01|body|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S8" s="37" t="str">
-        <x:f>IF(A8="","",IF(COUNTIF($R$6:$R$139,R8)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A8="","",IF(COUNTIF($R$6:$R$145,R8)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T8" s="37" t="str">
@@ -1485,7 +1542,7 @@
         <x:v>角色|player_component|player_capsule01|hand_l_source|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S9" s="37" t="str">
-        <x:f>IF(A9="","",IF(COUNTIF($R$6:$R$139,R9)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A9="","",IF(COUNTIF($R$6:$R$145,R9)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T9" s="37" t="str">
@@ -1561,7 +1618,7 @@
         <x:v>角色|player_component|player_capsule01|hand|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S10" s="37" t="str">
-        <x:f>IF(A10="","",IF(COUNTIF($R$6:$R$139,R10)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A10="","",IF(COUNTIF($R$6:$R$145,R10)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T10" s="37" t="str">
@@ -1637,7 +1694,7 @@
         <x:v>角色|player_accessory|player_capsule01|scarf|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S11" s="37" t="str">
-        <x:f>IF(A11="","",IF(COUNTIF($R$6:$R$139,R11)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A11="","",IF(COUNTIF($R$6:$R$145,R11)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T11" s="37" t="str">
@@ -1713,7 +1770,7 @@
         <x:v>角色|review_board|player_capsule01|preview|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S12" s="37" t="str">
-        <x:f>IF(A12="","",IF(COUNTIF($R$6:$R$139,R12)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A12="","",IF(COUNTIF($R$6:$R$145,R12)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T12" s="37" t="str"/>
@@ -1781,7 +1838,7 @@
         <x:v>特效|player_state|player_dash|root|侧面朝右（可水平翻转）|dashing</x:v>
       </x:c>
       <x:c r="S13" s="37" t="str">
-        <x:f>IF(A13="","",IF(COUNTIF($R$6:$R$139,R13)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A13="","",IF(COUNTIF($R$6:$R$145,R13)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T13" s="37" t="str"/>
@@ -1849,7 +1906,7 @@
         <x:v>特效|player_state|player_hurt|root|侧面朝右（可水平翻转）|hurt</x:v>
       </x:c>
       <x:c r="S14" s="37" t="str">
-        <x:f>IF(A14="","",IF(COUNTIF($R$6:$R$139,R14)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A14="","",IF(COUNTIF($R$6:$R$145,R14)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T14" s="37" t="str"/>
@@ -1915,7 +1972,7 @@
         <x:v>特效|player_overlay|player_low_hp|root|侧面朝右（可水平翻转）|low_health</x:v>
       </x:c>
       <x:c r="S15" s="37" t="str">
-        <x:f>IF(A15="","",IF(COUNTIF($R$6:$R$139,R15)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A15="","",IF(COUNTIF($R$6:$R$145,R15)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T15" s="37" t="str"/>
@@ -1981,7 +2038,7 @@
         <x:v>特效|player_overlay|player_silenced|root|侧面朝右（可水平翻转）|silenced</x:v>
       </x:c>
       <x:c r="S16" s="37" t="str">
-        <x:f>IF(A16="","",IF(COUNTIF($R$6:$R$139,R16)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A16="","",IF(COUNTIF($R$6:$R$145,R16)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T16" s="37" t="str"/>
@@ -2049,7 +2106,7 @@
         <x:v>敌人|normal_melee|melee_chaser|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S17" s="37" t="str">
-        <x:f>IF(A17="","",IF(COUNTIF($R$6:$R$139,R17)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A17="","",IF(COUNTIF($R$6:$R$145,R17)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T17" s="37" t="str"/>
@@ -2119,7 +2176,7 @@
         <x:v>敌人|normal_ranged|ranged_caster|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S18" s="37" t="str">
-        <x:f>IF(A18="","",IF(COUNTIF($R$6:$R$139,R18)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A18="","",IF(COUNTIF($R$6:$R$145,R18)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T18" s="37" t="str"/>
@@ -2187,7 +2244,7 @@
         <x:v>敌人|normal_summoner|summoner|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S19" s="37" t="str">
-        <x:f>IF(A19="","",IF(COUNTIF($R$6:$R$139,R19)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A19="","",IF(COUNTIF($R$6:$R$145,R19)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T19" s="37" t="str"/>
@@ -2255,7 +2312,7 @@
         <x:v>敌人|normal_tank|shielded|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S20" s="37" t="str">
-        <x:f>IF(A20="","",IF(COUNTIF($R$6:$R$139,R20)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A20="","",IF(COUNTIF($R$6:$R$145,R20)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T20" s="37" t="str"/>
@@ -2323,7 +2380,7 @@
         <x:v>敌人|normal_bomber|exploder|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S21" s="37" t="str">
-        <x:f>IF(A21="","",IF(COUNTIF($R$6:$R$139,R21)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A21="","",IF(COUNTIF($R$6:$R$145,R21)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T21" s="37" t="str"/>
@@ -2391,7 +2448,7 @@
         <x:v>敌人|normal_ambusher|ambusher|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S22" s="37" t="str">
-        <x:f>IF(A22="","",IF(COUNTIF($R$6:$R$139,R22)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A22="","",IF(COUNTIF($R$6:$R$145,R22)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T22" s="37" t="str"/>
@@ -2459,7 +2516,7 @@
         <x:v>敌人|boss|boss|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S23" s="37" t="str">
-        <x:f>IF(A23="","",IF(COUNTIF($R$6:$R$139,R23)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A23="","",IF(COUNTIF($R$6:$R$145,R23)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T23" s="37" t="str"/>
@@ -2529,7 +2586,7 @@
         <x:v>枪械|gunbody|bp_pistol|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S24" s="37" t="str">
-        <x:f>IF(A24="","",IF(COUNTIF($R$6:$R$139,R24)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A24="","",IF(COUNTIF($R$6:$R$145,R24)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T24" s="37" t="str"/>
@@ -2599,7 +2656,7 @@
         <x:v>枪械|gunbody|bp_shotgun|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S25" s="37" t="str">
-        <x:f>IF(A25="","",IF(COUNTIF($R$6:$R$139,R25)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A25="","",IF(COUNTIF($R$6:$R$145,R25)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T25" s="37" t="str"/>
@@ -2669,7 +2726,7 @@
         <x:v>枪械|gunbody|bp_rifle|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S26" s="37" t="str">
-        <x:f>IF(A26="","",IF(COUNTIF($R$6:$R$139,R26)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A26="","",IF(COUNTIF($R$6:$R$145,R26)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T26" s="37" t="str"/>
@@ -2739,7 +2796,7 @@
         <x:v>枪械|gunbody|bp_machinegun|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S27" s="37" t="str">
-        <x:f>IF(A27="","",IF(COUNTIF($R$6:$R$139,R27)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A27="","",IF(COUNTIF($R$6:$R$145,R27)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T27" s="37" t="str"/>
@@ -2809,7 +2866,7 @@
         <x:v>枪械|gunbody|bp_sniper|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S28" s="37" t="str">
-        <x:f>IF(A28="","",IF(COUNTIF($R$6:$R$139,R28)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A28="","",IF(COUNTIF($R$6:$R$145,R28)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T28" s="37" t="str"/>
@@ -2879,7 +2936,7 @@
         <x:v>枪械|gunbody|bp_launcher|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S29" s="37" t="str">
-        <x:f>IF(A29="","",IF(COUNTIF($R$6:$R$139,R29)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A29="","",IF(COUNTIF($R$6:$R$145,R29)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T29" s="37" t="str"/>
@@ -2949,7 +3006,7 @@
         <x:v>枪械|gunbody|bp_charge|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S30" s="37" t="str">
-        <x:f>IF(A30="","",IF(COUNTIF($R$6:$R$139,R30)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A30="","",IF(COUNTIF($R$6:$R$145,R30)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T30" s="37" t="str"/>
@@ -3017,7 +3074,7 @@
         <x:v>枪械|bullet_module|mod_bullet_standard|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S31" s="37" t="str">
-        <x:f>IF(A31="","",IF(COUNTIF($R$6:$R$139,R31)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A31="","",IF(COUNTIF($R$6:$R$145,R31)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T31" s="37" t="str"/>
@@ -3085,7 +3142,7 @@
         <x:v>枪械|bullet_module|mod_bullet_sticky|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S32" s="37" t="str">
-        <x:f>IF(A32="","",IF(COUNTIF($R$6:$R$139,R32)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A32="","",IF(COUNTIF($R$6:$R$145,R32)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T32" s="37" t="str"/>
@@ -3153,7 +3210,7 @@
         <x:v>枪械|bullet_module|mod_bullet_bounce|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S33" s="37" t="str">
-        <x:f>IF(A33="","",IF(COUNTIF($R$6:$R$139,R33)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A33="","",IF(COUNTIF($R$6:$R$145,R33)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T33" s="37" t="str"/>
@@ -3221,7 +3278,7 @@
         <x:v>枪械|bullet_module|mod_bullet_piercing|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S34" s="37" t="str">
-        <x:f>IF(A34="","",IF(COUNTIF($R$6:$R$139,R34)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A34="","",IF(COUNTIF($R$6:$R$145,R34)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T34" s="37" t="str"/>
@@ -3289,7 +3346,7 @@
         <x:v>枪械|bullet_module|mod_bullet_explosive|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S35" s="37" t="str">
-        <x:f>IF(A35="","",IF(COUNTIF($R$6:$R$139,R35)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A35="","",IF(COUNTIF($R$6:$R$145,R35)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T35" s="37" t="str"/>
@@ -3357,7 +3414,7 @@
         <x:v>枪械|bullet_module|mod_bullet_homing|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S36" s="37" t="str">
-        <x:f>IF(A36="","",IF(COUNTIF($R$6:$R$139,R36)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A36="","",IF(COUNTIF($R$6:$R$145,R36)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T36" s="37" t="str"/>
@@ -3425,7 +3482,7 @@
         <x:v>枪械|bullet_module|mod_bullet_blackhole|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S37" s="37" t="str">
-        <x:f>IF(A37="","",IF(COUNTIF($R$6:$R$139,R37)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A37="","",IF(COUNTIF($R$6:$R$145,R37)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T37" s="37" t="str"/>
@@ -3493,7 +3550,7 @@
         <x:v>枪械|bullet_module|mod_bullet_balloon|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S38" s="37" t="str">
-        <x:f>IF(A38="","",IF(COUNTIF($R$6:$R$139,R38)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A38="","",IF(COUNTIF($R$6:$R$145,R38)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T38" s="37" t="str"/>
@@ -3561,7 +3618,7 @@
         <x:v>枪械|attachment|attach_triple_muzzle|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S39" s="37" t="str">
-        <x:f>IF(A39="","",IF(COUNTIF($R$6:$R$139,R39)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A39="","",IF(COUNTIF($R$6:$R$145,R39)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T39" s="37" t="str"/>
@@ -3629,7 +3686,7 @@
         <x:v>枪械|attachment|attach_rubber_stock|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S40" s="37" t="str">
-        <x:f>IF(A40="","",IF(COUNTIF($R$6:$R$139,R40)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A40="","",IF(COUNTIF($R$6:$R$145,R40)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T40" s="37" t="str"/>
@@ -3697,7 +3754,7 @@
         <x:v>枪械|attachment|attach_scope|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S41" s="37" t="str">
-        <x:f>IF(A41="","",IF(COUNTIF($R$6:$R$139,R41)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A41="","",IF(COUNTIF($R$6:$R$145,R41)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T41" s="37" t="str"/>
@@ -3765,7 +3822,7 @@
         <x:v>枪械|attachment|attach_big_mag|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S42" s="37" t="str">
-        <x:f>IF(A42="","",IF(COUNTIF($R$6:$R$139,R42)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A42="","",IF(COUNTIF($R$6:$R$145,R42)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T42" s="37" t="str"/>
@@ -3833,7 +3890,7 @@
         <x:v>枪械|attachment|attach_fan|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S43" s="37" t="str">
-        <x:f>IF(A43="","",IF(COUNTIF($R$6:$R$139,R43)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A43="","",IF(COUNTIF($R$6:$R$145,R43)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T43" s="37" t="str"/>
@@ -3901,7 +3958,7 @@
         <x:v>枪械|attachment|attach_copy_sticker|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S44" s="37" t="str">
-        <x:f>IF(A44="","",IF(COUNTIF($R$6:$R$139,R44)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A44="","",IF(COUNTIF($R$6:$R$145,R44)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T44" s="37" t="str"/>
@@ -3969,7 +4026,7 @@
         <x:v>道具|consumable|item_beacon|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S45" s="37" t="str">
-        <x:f>IF(A45="","",IF(COUNTIF($R$6:$R$139,R45)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A45="","",IF(COUNTIF($R$6:$R$145,R45)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T45" s="37" t="str"/>
@@ -4035,7 +4092,7 @@
         <x:v>道具|key|item_room_key|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S46" s="37" t="str">
-        <x:f>IF(A46="","",IF(COUNTIF($R$6:$R$139,R46)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A46="","",IF(COUNTIF($R$6:$R$145,R46)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T46" s="37" t="str"/>
@@ -4101,7 +4158,7 @@
         <x:v>道具|pickup|soul_orb|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S47" s="37" t="str">
-        <x:f>IF(A47="","",IF(COUNTIF($R$6:$R$139,R47)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A47="","",IF(COUNTIF($R$6:$R$145,R47)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T47" s="37" t="str"/>
@@ -4167,7 +4224,7 @@
         <x:v>道具|container|container|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S48" s="37" t="str">
-        <x:f>IF(A48="","",IF(COUNTIF($R$6:$R$139,R48)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A48="","",IF(COUNTIF($R$6:$R$145,R48)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T48" s="37" t="str"/>
@@ -4233,7 +4290,7 @@
         <x:v>道具|pickup|room_key_pickup|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S49" s="37" t="str">
-        <x:f>IF(A49="","",IF(COUNTIF($R$6:$R$139,R49)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A49="","",IF(COUNTIF($R$6:$R$145,R49)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T49" s="37" t="str"/>
@@ -4299,7 +4356,7 @@
         <x:v>道具|pickup_base|ground_item|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S50" s="37" t="str">
-        <x:f>IF(A50="","",IF(COUNTIF($R$6:$R$139,R50)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A50="","",IF(COUNTIF($R$6:$R$145,R50)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T50" s="37" t="str"/>
@@ -4365,7 +4422,7 @@
         <x:v>场景|biome_kit|base_world|root|顶视|default</x:v>
       </x:c>
       <x:c r="S51" s="37" t="str">
-        <x:f>IF(A51="","",IF(COUNTIF($R$6:$R$139,R51)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A51="","",IF(COUNTIF($R$6:$R$145,R51)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T51" s="37" t="str"/>
@@ -4433,7 +4490,7 @@
         <x:v>场景|biome_kit|iron_frontier|root|顶视|default</x:v>
       </x:c>
       <x:c r="S52" s="37" t="str">
-        <x:f>IF(A52="","",IF(COUNTIF($R$6:$R$139,R52)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A52="","",IF(COUNTIF($R$6:$R$145,R52)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T52" s="37" t="str"/>
@@ -4501,7 +4558,7 @@
         <x:v>场景|biome_kit|rust_foundry|root|顶视|default</x:v>
       </x:c>
       <x:c r="S53" s="37" t="str">
-        <x:f>IF(A53="","",IF(COUNTIF($R$6:$R$139,R53)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A53="","",IF(COUNTIF($R$6:$R$145,R53)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T53" s="37" t="str"/>
@@ -4569,7 +4626,7 @@
         <x:v>场景|biome_kit|spore_depths|root|顶视|default</x:v>
       </x:c>
       <x:c r="S54" s="37" t="str">
-        <x:f>IF(A54="","",IF(COUNTIF($R$6:$R$139,R54)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A54="","",IF(COUNTIF($R$6:$R$145,R54)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T54" s="37" t="str"/>
@@ -4637,7 +4694,7 @@
         <x:v>场景|biome_kit|abyss_archive|root|顶视|default</x:v>
       </x:c>
       <x:c r="S55" s="37" t="str">
-        <x:f>IF(A55="","",IF(COUNTIF($R$6:$R$139,R55)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A55="","",IF(COUNTIF($R$6:$R$145,R55)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T55" s="37" t="str"/>
@@ -4705,7 +4762,7 @@
         <x:v>场景|biome_kit|training_range|root|顶视|default</x:v>
       </x:c>
       <x:c r="S56" s="37" t="str">
-        <x:f>IF(A56="","",IF(COUNTIF($R$6:$R$139,R56)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A56="","",IF(COUNTIF($R$6:$R$145,R56)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T56" s="37" t="str"/>
@@ -4773,7 +4830,7 @@
         <x:v>场景|room_dressing|room_combat|root|顶视|default</x:v>
       </x:c>
       <x:c r="S57" s="37" t="str">
-        <x:f>IF(A57="","",IF(COUNTIF($R$6:$R$139,R57)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A57="","",IF(COUNTIF($R$6:$R$145,R57)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T57" s="37" t="str"/>
@@ -4841,7 +4898,7 @@
         <x:v>场景|room_dressing|room_elite|root|顶视|default</x:v>
       </x:c>
       <x:c r="S58" s="37" t="str">
-        <x:f>IF(A58="","",IF(COUNTIF($R$6:$R$139,R58)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A58="","",IF(COUNTIF($R$6:$R$145,R58)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T58" s="37" t="str"/>
@@ -4909,7 +4966,7 @@
         <x:v>场景|room_dressing|room_boss|root|顶视|default</x:v>
       </x:c>
       <x:c r="S59" s="37" t="str">
-        <x:f>IF(A59="","",IF(COUNTIF($R$6:$R$139,R59)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A59="","",IF(COUNTIF($R$6:$R$145,R59)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T59" s="37" t="str"/>
@@ -4977,7 +5034,7 @@
         <x:v>场景|room_dressing|room_event|root|顶视|default</x:v>
       </x:c>
       <x:c r="S60" s="37" t="str">
-        <x:f>IF(A60="","",IF(COUNTIF($R$6:$R$139,R60)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A60="","",IF(COUNTIF($R$6:$R$145,R60)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T60" s="37" t="str"/>
@@ -5045,7 +5102,7 @@
         <x:v>场景|room_dressing|room_extraction|root|顶视|default</x:v>
       </x:c>
       <x:c r="S61" s="37" t="str">
-        <x:f>IF(A61="","",IF(COUNTIF($R$6:$R$139,R61)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A61="","",IF(COUNTIF($R$6:$R$145,R61)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T61" s="37" t="str"/>
@@ -5113,7 +5170,7 @@
         <x:v>场景|room_dressing|room_merchant|root|顶视|default</x:v>
       </x:c>
       <x:c r="S62" s="37" t="str">
-        <x:f>IF(A62="","",IF(COUNTIF($R$6:$R$139,R62)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A62="","",IF(COUNTIF($R$6:$R$145,R62)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T62" s="37" t="str"/>
@@ -5181,7 +5238,7 @@
         <x:v>场景|room_dressing|room_scavenge|root|顶视|default</x:v>
       </x:c>
       <x:c r="S63" s="37" t="str">
-        <x:f>IF(A63="","",IF(COUNTIF($R$6:$R$139,R63)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A63="","",IF(COUNTIF($R$6:$R$145,R63)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T63" s="37" t="str"/>
@@ -5249,7 +5306,7 @@
         <x:v>场景|room_dressing|room_storage|root|顶视|default</x:v>
       </x:c>
       <x:c r="S64" s="37" t="str">
-        <x:f>IF(A64="","",IF(COUNTIF($R$6:$R$139,R64)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A64="","",IF(COUNTIF($R$6:$R$145,R64)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T64" s="37" t="str"/>
@@ -5317,7 +5374,7 @@
         <x:v>场景|room_dressing|room_trap|root|顶视|default</x:v>
       </x:c>
       <x:c r="S65" s="37" t="str">
-        <x:f>IF(A65="","",IF(COUNTIF($R$6:$R$139,R65)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A65="","",IF(COUNTIF($R$6:$R$145,R65)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T65" s="37" t="str"/>
@@ -5385,7 +5442,7 @@
         <x:v>场景|room_dressing|room_upgrade|root|顶视|default</x:v>
       </x:c>
       <x:c r="S66" s="37" t="str">
-        <x:f>IF(A66="","",IF(COUNTIF($R$6:$R$139,R66)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A66="","",IF(COUNTIF($R$6:$R$145,R66)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T66" s="37" t="str"/>
@@ -5453,7 +5510,7 @@
         <x:v>场景|room_dressing|room_spawn|root|顶视|default</x:v>
       </x:c>
       <x:c r="S67" s="37" t="str">
-        <x:f>IF(A67="","",IF(COUNTIF($R$6:$R$139,R67)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A67="","",IF(COUNTIF($R$6:$R$145,R67)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T67" s="37" t="str"/>
@@ -5521,7 +5578,7 @@
         <x:v>场景|room_dressing|room_stairs|root|顶视|default</x:v>
       </x:c>
       <x:c r="S68" s="37" t="str">
-        <x:f>IF(A68="","",IF(COUNTIF($R$6:$R$139,R68)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A68="","",IF(COUNTIF($R$6:$R$145,R68)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T68" s="37" t="str"/>
@@ -5589,7 +5646,7 @@
         <x:v>场景道具|facility|base_briefing|root|顶视|default</x:v>
       </x:c>
       <x:c r="S69" s="37" t="str">
-        <x:f>IF(A69="","",IF(COUNTIF($R$6:$R$139,R69)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A69="","",IF(COUNTIF($R$6:$R$145,R69)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T69" s="37" t="str"/>
@@ -5657,7 +5714,7 @@
         <x:v>场景道具|facility|base_workshop|root|顶视|default</x:v>
       </x:c>
       <x:c r="S70" s="37" t="str">
-        <x:f>IF(A70="","",IF(COUNTIF($R$6:$R$139,R70)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A70="","",IF(COUNTIF($R$6:$R$145,R70)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T70" s="37" t="str"/>
@@ -5725,7 +5782,7 @@
         <x:v>场景道具|facility|base_divination|root|顶视|default</x:v>
       </x:c>
       <x:c r="S71" s="37" t="str">
-        <x:f>IF(A71="","",IF(COUNTIF($R$6:$R$139,R71)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A71="","",IF(COUNTIF($R$6:$R$145,R71)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T71" s="37" t="str"/>
@@ -5793,7 +5850,7 @@
         <x:v>场景道具|facility|base_vault|root|顶视|default</x:v>
       </x:c>
       <x:c r="S72" s="37" t="str">
-        <x:f>IF(A72="","",IF(COUNTIF($R$6:$R$139,R72)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A72="","",IF(COUNTIF($R$6:$R$145,R72)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T72" s="37" t="str"/>
@@ -5861,7 +5918,7 @@
         <x:v>场景道具|facility|base_monster_archive|root|顶视|default</x:v>
       </x:c>
       <x:c r="S73" s="37" t="str">
-        <x:f>IF(A73="","",IF(COUNTIF($R$6:$R$139,R73)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A73="","",IF(COUNTIF($R$6:$R$145,R73)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T73" s="37" t="str"/>
@@ -5929,7 +5986,7 @@
         <x:v>场景道具|facility|base_card_collection|root|顶视|default</x:v>
       </x:c>
       <x:c r="S74" s="37" t="str">
-        <x:f>IF(A74="","",IF(COUNTIF($R$6:$R$139,R74)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A74="","",IF(COUNTIF($R$6:$R$145,R74)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T74" s="37" t="str"/>
@@ -5997,7 +6054,7 @@
         <x:v>场景道具|facility|base_terminal|root|顶视|default</x:v>
       </x:c>
       <x:c r="S75" s="37" t="str">
-        <x:f>IF(A75="","",IF(COUNTIF($R$6:$R$139,R75)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A75="","",IF(COUNTIF($R$6:$R$145,R75)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T75" s="37" t="str"/>
@@ -6065,7 +6122,7 @@
         <x:v>场景道具|facility|dungeon_gate|root|顶视|default</x:v>
       </x:c>
       <x:c r="S76" s="37" t="str">
-        <x:f>IF(A76="","",IF(COUNTIF($R$6:$R$139,R76)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A76="","",IF(COUNTIF($R$6:$R$145,R76)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T76" s="37" t="str"/>
@@ -6133,7 +6190,7 @@
         <x:v>场景道具|facility|workbench|root|顶视|default</x:v>
       </x:c>
       <x:c r="S77" s="37" t="str">
-        <x:f>IF(A77="","",IF(COUNTIF($R$6:$R$139,R77)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A77="","",IF(COUNTIF($R$6:$R$145,R77)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T77" s="37" t="str"/>
@@ -6201,7 +6258,7 @@
         <x:v>场景道具|facility|door|root|顶视|default</x:v>
       </x:c>
       <x:c r="S78" s="37" t="str">
-        <x:f>IF(A78="","",IF(COUNTIF($R$6:$R$139,R78)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A78="","",IF(COUNTIF($R$6:$R$145,R78)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T78" s="37" t="str"/>
@@ -6269,7 +6326,7 @@
         <x:v>ui|screen|hud|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S79" s="37" t="str">
-        <x:f>IF(A79="","",IF(COUNTIF($R$6:$R$139,R79)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A79="","",IF(COUNTIF($R$6:$R$145,R79)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T79" s="37" t="str"/>
@@ -6316,7 +6373,7 @@
         <x:v>跨分辨率</x:v>
       </x:c>
       <x:c r="K80" s="37" t="str">
-        <x:v>程序占位</x:v>
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="L80" s="37" t="str">
         <x:v>P0</x:v>
@@ -6337,7 +6394,7 @@
         <x:v>ui|screen|inventory|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S80" s="37" t="str">
-        <x:f>IF(A80="","",IF(COUNTIF($R$6:$R$139,R80)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A80="","",IF(COUNTIF($R$6:$R$145,R80)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T80" s="37" t="str"/>
@@ -6345,13 +6402,13 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V80" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W80" s="37" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
       <x:c r="X80" s="37" t="str">
-        <x:v>先建组件库，再做页面，避免每页重复画按钮/面板</x:v>
+        <x:v>背包共享逻辑根；3D表现登记为 UI-SCREEN-INVENTORY-3D；12+2槽与保险契约不变</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -6405,7 +6462,7 @@
         <x:v>ui|screen|merchant|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S81" s="37" t="str">
-        <x:f>IF(A81="","",IF(COUNTIF($R$6:$R$139,R81)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A81="","",IF(COUNTIF($R$6:$R$145,R81)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T81" s="37" t="str"/>
@@ -6473,7 +6530,7 @@
         <x:v>ui|screen|workshop|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S82" s="37" t="str">
-        <x:f>IF(A82="","",IF(COUNTIF($R$6:$R$139,R82)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A82="","",IF(COUNTIF($R$6:$R$145,R82)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T82" s="37" t="str"/>
@@ -6541,7 +6598,7 @@
         <x:v>ui|screen|workbench|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S83" s="37" t="str">
-        <x:f>IF(A83="","",IF(COUNTIF($R$6:$R$139,R83)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A83="","",IF(COUNTIF($R$6:$R$145,R83)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T83" s="37" t="str"/>
@@ -6609,7 +6666,7 @@
         <x:v>ui|screen|weapon_tree|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S84" s="37" t="str">
-        <x:f>IF(A84="","",IF(COUNTIF($R$6:$R$139,R84)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A84="","",IF(COUNTIF($R$6:$R$145,R84)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T84" s="37" t="str"/>
@@ -6677,7 +6734,7 @@
         <x:v>ui|screen|fate_select|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S85" s="37" t="str">
-        <x:f>IF(A85="","",IF(COUNTIF($R$6:$R$139,R85)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A85="","",IF(COUNTIF($R$6:$R$145,R85)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T85" s="37" t="str"/>
@@ -6745,7 +6802,7 @@
         <x:v>ui|screen|fate_collection|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S86" s="37" t="str">
-        <x:f>IF(A86="","",IF(COUNTIF($R$6:$R$139,R86)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A86="","",IF(COUNTIF($R$6:$R$145,R86)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T86" s="37" t="str"/>
@@ -6813,7 +6870,7 @@
         <x:v>ui|screen|level_select|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S87" s="37" t="str">
-        <x:f>IF(A87="","",IF(COUNTIF($R$6:$R$139,R87)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A87="","",IF(COUNTIF($R$6:$R$145,R87)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T87" s="37" t="str"/>
@@ -6881,7 +6938,7 @@
         <x:v>ui|screen|vault|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S88" s="37" t="str">
-        <x:f>IF(A88="","",IF(COUNTIF($R$6:$R$139,R88)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A88="","",IF(COUNTIF($R$6:$R$145,R88)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T88" s="37" t="str"/>
@@ -6949,7 +7006,7 @@
         <x:v>ui|screen|monster_archive|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S89" s="37" t="str">
-        <x:f>IF(A89="","",IF(COUNTIF($R$6:$R$139,R89)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A89="","",IF(COUNTIF($R$6:$R$145,R89)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T89" s="37" t="str"/>
@@ -7017,7 +7074,7 @@
         <x:v>ui|screen|base_menu|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S90" s="37" t="str">
-        <x:f>IF(A90="","",IF(COUNTIF($R$6:$R$139,R90)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A90="","",IF(COUNTIF($R$6:$R$145,R90)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T90" s="37" t="str"/>
@@ -7085,7 +7142,7 @@
         <x:v>ui|screen|mobile_controls|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S91" s="37" t="str">
-        <x:f>IF(A91="","",IF(COUNTIF($R$6:$R$139,R91)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A91="","",IF(COUNTIF($R$6:$R$145,R91)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T91" s="37" t="str"/>
@@ -7153,7 +7210,7 @@
         <x:v>特效|gameplay_vfx|explosion|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S92" s="37" t="str">
-        <x:f>IF(A92="","",IF(COUNTIF($R$6:$R$139,R92)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A92="","",IF(COUNTIF($R$6:$R$145,R92)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T92" s="37" t="str"/>
@@ -7221,7 +7278,7 @@
         <x:v>特效|gameplay_vfx|muzzle_flash|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S93" s="37" t="str">
-        <x:f>IF(A93="","",IF(COUNTIF($R$6:$R$139,R93)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A93="","",IF(COUNTIF($R$6:$R$145,R93)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T93" s="37" t="str"/>
@@ -7289,7 +7346,7 @@
         <x:v>特效|gameplay_vfx|damage_number|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S94" s="37" t="str">
-        <x:f>IF(A94="","",IF(COUNTIF($R$6:$R$139,R94)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A94="","",IF(COUNTIF($R$6:$R$145,R94)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T94" s="37" t="str"/>
@@ -7357,7 +7414,7 @@
         <x:v>特效|gameplay_vfx|spark|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S95" s="37" t="str">
-        <x:f>IF(A95="","",IF(COUNTIF($R$6:$R$139,R95)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A95="","",IF(COUNTIF($R$6:$R$145,R95)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T95" s="37" t="str"/>
@@ -7425,7 +7482,7 @@
         <x:v>特效|gameplay_vfx|room_transition|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S96" s="37" t="str">
-        <x:f>IF(A96="","",IF(COUNTIF($R$6:$R$139,R96)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A96="","",IF(COUNTIF($R$6:$R$145,R96)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T96" s="37" t="str"/>
@@ -7472,7 +7529,7 @@
         <x:v>跨武器/跨场景</x:v>
       </x:c>
       <x:c r="K97" s="37" t="str">
-        <x:v>程序占位</x:v>
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="L97" s="37" t="str">
         <x:v>P2</x:v>
@@ -7483,9 +7540,11 @@
       <x:c r="N97" s="37" t="str">
         <x:v>粒子或 8–16 帧序列</x:v>
       </x:c>
-      <x:c r="O97" s="37" t="str"/>
+      <x:c r="O97" s="37" t="str">
+        <x:v>scenes/Dungeon3D.tscn</x:v>
+      </x:c>
       <x:c r="P97" s="37" t="str">
-        <x:v>src/fx/HealthVignette.gd</x:v>
+        <x:v>src/world3d/Dungeon3D.gd</x:v>
       </x:c>
       <x:c r="Q97" s="37" t="str"/>
       <x:c r="R97" s="37" t="str">
@@ -7493,7 +7552,7 @@
         <x:v>特效|gameplay_vfx|health_vignette|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S97" s="37" t="str">
-        <x:f>IF(A97="","",IF(COUNTIF($R$6:$R$139,R97)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A97="","",IF(COUNTIF($R$6:$R$145,R97)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T97" s="37" t="str"/>
@@ -7501,13 +7560,13 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V97" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W97" s="37" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
       <x:c r="X97" s="37" t="str">
-        <x:v>颜色/尺寸作参数变体，禁止复制整套</x:v>
+        <x:v>复用低血暗角身份；3D HUD低血时提高边缘强度，不复制第二套逻辑ID</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -7561,7 +7620,7 @@
         <x:v>特效|gameplay_vfx|visibility_light|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S98" s="37" t="str">
-        <x:f>IF(A98="","",IF(COUNTIF($R$6:$R$139,R98)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A98="","",IF(COUNTIF($R$6:$R$145,R98)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T98" s="37" t="str"/>
@@ -7569,13 +7628,13 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V98" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W98" s="37" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
       <x:c r="X98" s="37" t="str">
-        <x:v>颜色/尺寸作参数变体，禁止复制整套</x:v>
+        <x:v>2D视野表现根；3D真实判定与地面网格登记为 VFX-VISIBILITY-FIELD-3D，禁止用灯光替代</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -7629,7 +7688,7 @@
         <x:v>特效|gameplay_vfx|extraction_beacon|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S99" s="37" t="str">
-        <x:f>IF(A99="","",IF(COUNTIF($R$6:$R$139,R99)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A99="","",IF(COUNTIF($R$6:$R$145,R99)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T99" s="37" t="str"/>
@@ -7697,7 +7756,7 @@
         <x:v>音频|bgm|bgm_wasteland|root|不适用|default</x:v>
       </x:c>
       <x:c r="S100" s="37" t="str">
-        <x:f>IF(A100="","",IF(COUNTIF($R$6:$R$139,R100)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A100="","",IF(COUNTIF($R$6:$R$145,R100)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T100" s="37" t="str"/>
@@ -7763,7 +7822,7 @@
         <x:v>音频|sfx|pistol_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S101" s="37" t="str">
-        <x:f>IF(A101="","",IF(COUNTIF($R$6:$R$139,R101)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A101="","",IF(COUNTIF($R$6:$R$145,R101)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T101" s="37" t="str"/>
@@ -7829,7 +7888,7 @@
         <x:v>音频|sfx|rifle_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S102" s="37" t="str">
-        <x:f>IF(A102="","",IF(COUNTIF($R$6:$R$139,R102)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A102="","",IF(COUNTIF($R$6:$R$145,R102)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T102" s="37" t="str"/>
@@ -7895,7 +7954,7 @@
         <x:v>音频|sfx|shotgun_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S103" s="37" t="str">
-        <x:f>IF(A103="","",IF(COUNTIF($R$6:$R$139,R103)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A103="","",IF(COUNTIF($R$6:$R$145,R103)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T103" s="37" t="str"/>
@@ -7961,7 +8020,7 @@
         <x:v>音频|sfx|smg_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S104" s="37" t="str">
-        <x:f>IF(A104="","",IF(COUNTIF($R$6:$R$139,R104)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A104="","",IF(COUNTIF($R$6:$R$145,R104)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T104" s="37" t="str"/>
@@ -8027,7 +8086,7 @@
         <x:v>音频|sfx|sniper_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S105" s="37" t="str">
-        <x:f>IF(A105="","",IF(COUNTIF($R$6:$R$139,R105)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A105="","",IF(COUNTIF($R$6:$R$145,R105)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T105" s="37" t="str"/>
@@ -8093,7 +8152,7 @@
         <x:v>音频|sfx|player_hit|root|不适用|default</x:v>
       </x:c>
       <x:c r="S106" s="37" t="str">
-        <x:f>IF(A106="","",IF(COUNTIF($R$6:$R$139,R106)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A106="","",IF(COUNTIF($R$6:$R$145,R106)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T106" s="37" t="str"/>
@@ -8159,7 +8218,7 @@
         <x:v>音频|sfx|player_dash|root|不适用|default</x:v>
       </x:c>
       <x:c r="S107" s="37" t="str">
-        <x:f>IF(A107="","",IF(COUNTIF($R$6:$R$139,R107)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A107="","",IF(COUNTIF($R$6:$R$145,R107)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T107" s="37" t="str"/>
@@ -8225,7 +8284,7 @@
         <x:v>音频|sfx|enemy_hit|root|不适用|default</x:v>
       </x:c>
       <x:c r="S108" s="37" t="str">
-        <x:f>IF(A108="","",IF(COUNTIF($R$6:$R$139,R108)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A108="","",IF(COUNTIF($R$6:$R$145,R108)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T108" s="37" t="str"/>
@@ -8291,7 +8350,7 @@
         <x:v>音频|sfx|enemy_die|root|不适用|default</x:v>
       </x:c>
       <x:c r="S109" s="37" t="str">
-        <x:f>IF(A109="","",IF(COUNTIF($R$6:$R$139,R109)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A109="","",IF(COUNTIF($R$6:$R$145,R109)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T109" s="37" t="str"/>
@@ -8357,7 +8416,7 @@
         <x:v>音频|sfx|reload|root|不适用|default</x:v>
       </x:c>
       <x:c r="S110" s="37" t="str">
-        <x:f>IF(A110="","",IF(COUNTIF($R$6:$R$139,R110)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A110="","",IF(COUNTIF($R$6:$R$145,R110)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T110" s="37" t="str"/>
@@ -8423,7 +8482,7 @@
         <x:v>音频|sfx|extraction_start|root|不适用|default</x:v>
       </x:c>
       <x:c r="S111" s="37" t="str">
-        <x:f>IF(A111="","",IF(COUNTIF($R$6:$R$139,R111)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A111="","",IF(COUNTIF($R$6:$R$145,R111)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T111" s="37" t="str"/>
@@ -8489,7 +8548,7 @@
         <x:v>音频|sfx|extraction_done|root|不适用|default</x:v>
       </x:c>
       <x:c r="S112" s="37" t="str">
-        <x:f>IF(A112="","",IF(COUNTIF($R$6:$R$139,R112)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A112="","",IF(COUNTIF($R$6:$R$145,R112)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T112" s="37" t="str"/>
@@ -8561,7 +8620,7 @@
         <x:v>角色|player|player_capsule01|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S113" t="str">
-        <x:f>IF(A113="","",IF(COUNTIF($R$6:$R$139,R113)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A113="","",IF(COUNTIF($R$6:$R$145,R113)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T113" t="str">
@@ -8637,7 +8696,7 @@
         <x:v>角色|player|player_capsule01|body_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S114" t="str">
-        <x:f>IF(A114="","",IF(COUNTIF($R$6:$R$139,R114)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A114="","",IF(COUNTIF($R$6:$R$145,R114)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T114" t="str">
@@ -8713,7 +8772,7 @@
         <x:v>角色|player|player_capsule01|head_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S115" t="str">
-        <x:f>IF(A115="","",IF(COUNTIF($R$6:$R$139,R115)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A115="","",IF(COUNTIF($R$6:$R$145,R115)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T115" t="str">
@@ -8789,7 +8848,7 @@
         <x:v>角色|player|player_capsule01|hand_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S116" t="str">
-        <x:f>IF(A116="","",IF(COUNTIF($R$6:$R$139,R116)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A116="","",IF(COUNTIF($R$6:$R$145,R116)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T116" t="str">
@@ -8865,7 +8924,7 @@
         <x:v>角色|player|player_capsule01|scarf_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S117" t="str">
-        <x:f>IF(A117="","",IF(COUNTIF($R$6:$R$139,R117)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A117="","",IF(COUNTIF($R$6:$R$145,R117)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T117" t="str">
@@ -8941,7 +9000,7 @@
         <x:v>角色|player|player_capsule01|weapon_socket_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S118" t="str">
-        <x:f>IF(A118="","",IF(COUNTIF($R$6:$R$139,R118)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A118="","",IF(COUNTIF($R$6:$R$145,R118)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T118" t="str">
@@ -9017,7 +9076,7 @@
         <x:v>场景|base|base_world|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S119" t="str">
-        <x:f>IF(A119="","",IF(COUNTIF($R$6:$R$139,R119)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A119="","",IF(COUNTIF($R$6:$R$145,R119)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T119" t="str">
@@ -9093,7 +9152,7 @@
         <x:v>场景道具|facility|base_facility_module|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S120" t="str">
-        <x:f>IF(A120="","",IF(COUNTIF($R$6:$R$139,R120)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A120="","",IF(COUNTIF($R$6:$R$145,R120)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T120" t="str">
@@ -9169,7 +9228,7 @@
         <x:v>场景道具|door|dungeon_gate|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S121" t="str">
-        <x:f>IF(A121="","",IF(COUNTIF($R$6:$R$139,R121)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A121="","",IF(COUNTIF($R$6:$R$145,R121)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T121" t="str">
@@ -9245,7 +9304,7 @@
         <x:v>场景|review_board|base_world|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S122" t="str">
-        <x:f>IF(A122="","",IF(COUNTIF($R$6:$R$139,R122)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A122="","",IF(COUNTIF($R$6:$R$145,R122)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T122" t="str">
@@ -9319,7 +9378,7 @@
         <x:v>场景|room|dungeon_runtime|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S123" s="63" t="str">
-        <x:f>IF(A123="","",IF(COUNTIF($R$6:$R$139,R123)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A123="","",IF(COUNTIF($R$6:$R$145,R123)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T123" s="63" t="str">
@@ -9395,7 +9454,7 @@
         <x:v>场景|biome|iron_frontier|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S124" s="63" t="str">
-        <x:f>IF(A124="","",IF(COUNTIF($R$6:$R$139,R124)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A124="","",IF(COUNTIF($R$6:$R$145,R124)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T124" s="63" t="str">
@@ -9471,7 +9530,7 @@
         <x:v>场景|biome|rust_foundry|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S125" s="63" t="str">
-        <x:f>IF(A125="","",IF(COUNTIF($R$6:$R$139,R125)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A125="","",IF(COUNTIF($R$6:$R$145,R125)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T125" s="63" t="str">
@@ -9547,7 +9606,7 @@
         <x:v>场景|biome|spore_depths|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S126" s="63" t="str">
-        <x:f>IF(A126="","",IF(COUNTIF($R$6:$R$139,R126)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A126="","",IF(COUNTIF($R$6:$R$145,R126)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T126" s="63" t="str">
@@ -9623,7 +9682,7 @@
         <x:v>场景|biome|abyss_archive|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S127" s="63" t="str">
-        <x:f>IF(A127="","",IF(COUNTIF($R$6:$R$139,R127)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A127="","",IF(COUNTIF($R$6:$R$145,R127)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T127" s="63" t="str">
@@ -9647,7 +9706,7 @@
         <x:v>PRP-WASTELAND-LIGHT-3D</x:v>
       </x:c>
       <x:c r="B128" s="63" t="str">
-        <x:v>废土灯具3D通用模块</x:v>
+        <x:v>废土灯具3D通用模块（街灯/顶灯）</x:v>
       </x:c>
       <x:c r="C128" s="63" t="str">
         <x:v>场景道具</x:v>
@@ -9671,7 +9730,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="J128" s="63" t="str">
-        <x:v>关卡/靶场照明</x:v>
+        <x:v>关卡/靶场/房间中央照明</x:v>
       </x:c>
       <x:c r="K128" s="63" t="str">
         <x:v>原型已接入</x:v>
@@ -9692,14 +9751,14 @@
         <x:v>src/world3d/WastelandLight3D.gd</x:v>
       </x:c>
       <x:c r="Q128" s="63" t="str">
-        <x:v>灯具;光池;故障灯;废土</x:v>
+        <x:v>灯具;街灯;中央顶灯;故障灯;废土</x:v>
       </x:c>
       <x:c r="R128" s="63" t="str">
         <x:f>LOWER(TRIM(C128)&amp;"|"&amp;TRIM(D128)&amp;"|"&amp;TRIM(E128)&amp;"|"&amp;TRIM(F128)&amp;"|"&amp;TRIM(H128)&amp;"|"&amp;TRIM(I128))</x:f>
         <x:v>场景道具|light|wasteland_light|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S128" s="63" t="str">
-        <x:f>IF(A128="","",IF(COUNTIF($R$6:$R$139,R128)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A128="","",IF(COUNTIF($R$6:$R$145,R128)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T128" s="63" t="str">
@@ -9709,13 +9768,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V128" s="64" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W128" s="63" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X128" s="63" t="str">
-        <x:v>灯架、灯罩、真实光源、低频故障与地面光池同一根</x:v>
+        <x:v>同根支持 street/ceiling；房间只实例化唯一中央顶灯，不生成室内路灯或假光池；默认关闭并由墙面开关控制</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="34" customHeight="1">
@@ -9775,7 +9834,7 @@
         <x:v>场景道具|furniture|room_furniture|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S129" s="63" t="str">
-        <x:f>IF(A129="","",IF(COUNTIF($R$6:$R$139,R129)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A129="","",IF(COUNTIF($R$6:$R$145,R129)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T129" s="63" t="str">
@@ -9851,7 +9910,7 @@
         <x:v>场景道具|container|search_container|root_3d|俯视3d|closed_opened</x:v>
       </x:c>
       <x:c r="S130" s="63" t="str">
-        <x:f>IF(A130="","",IF(COUNTIF($R$6:$R$139,R130)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A130="","",IF(COUNTIF($R$6:$R$145,R130)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T130" s="63" t="str">
@@ -9927,7 +9986,7 @@
         <x:v>场景道具|facility|service_station|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S131" s="63" t="str">
-        <x:f>IF(A131="","",IF(COUNTIF($R$6:$R$139,R131)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A131="","",IF(COUNTIF($R$6:$R$145,R131)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T131" s="63" t="str">
@@ -10003,7 +10062,7 @@
         <x:v>场景道具|facility|extraction_beacon|root_3d|俯视3d|locked_active_done</x:v>
       </x:c>
       <x:c r="S132" s="63" t="str">
-        <x:f>IF(A132="","",IF(COUNTIF($R$6:$R$139,R132)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A132="","",IF(COUNTIF($R$6:$R$145,R132)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T132" s="63" t="str">
@@ -10079,7 +10138,7 @@
         <x:v>特效|environment|hazard_field|root_3d|俯视3d|active</x:v>
       </x:c>
       <x:c r="S133" s="63" t="str">
-        <x:f>IF(A133="","",IF(COUNTIF($R$6:$R$139,R133)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A133="","",IF(COUNTIF($R$6:$R$145,R133)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T133" s="63" t="str">
@@ -10153,7 +10212,7 @@
         <x:v>枪械|gunbody|blueprint_gun_catalog|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S134" s="63" t="str">
-        <x:f>IF(A134="","",IF(COUNTIF($R$6:$R$139,R134)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A134="","",IF(COUNTIF($R$6:$R$145,R134)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T134" s="63" t="str">
@@ -10169,7 +10228,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X134" s="63" t="str">
-        <x:v>读取BlueprintRegistry唯一目录；覆盖56种组合；枪局部后坐力不带动手</x:v>
+        <x:v>真实GPU窗口检查暗室、家具、角色、怪物和战斗；开灯状态复用同一身份，验收图：assets/art/environments/dungeon_3d/env_dungeon_runtime_light_on_preview_top3d_v001.png</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="34" customHeight="1">
@@ -10227,7 +10286,7 @@
         <x:v>敌人|normal_elite_boss|enemy_ecosystem|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S135" s="63" t="str">
-        <x:f>IF(A135="","",IF(COUNTIF($R$6:$R$139,R135)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A135="","",IF(COUNTIF($R$6:$R$145,R135)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T135" s="63" t="str">
@@ -10237,13 +10296,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V135" s="64" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W135" s="63" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X135" s="63" t="str">
-        <x:v>追猎/远程/召唤/盾甲/自爆/伏击/Boss；统一七态</x:v>
+        <x:v>追猎/远程/召唤/盾甲/自爆/伏击/Boss；统一九态：idle/patrol/alert/chase/search/telegraph/attack/stagger/dead</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="34" customHeight="1">
@@ -10301,7 +10360,7 @@
         <x:v>特效|combat|combat_feedback|root_3d|俯视3d|muzzle_impact_damage_explosion</x:v>
       </x:c>
       <x:c r="S136" s="63" t="str">
-        <x:f>IF(A136="","",IF(COUNTIF($R$6:$R$139,R136)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A136="","",IF(COUNTIF($R$6:$R$145,R136)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T136" s="63" t="str">
@@ -10375,7 +10434,7 @@
         <x:v>场景|training_range|training_range|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S137" s="63" t="str">
-        <x:f>IF(A137="","",IF(COUNTIF($R$6:$R$139,R137)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A137="","",IF(COUNTIF($R$6:$R$145,R137)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T137" s="63" t="str">
@@ -10451,7 +10510,7 @@
         <x:v>场景|review_board|dungeon_runtime|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S138" s="63" t="str">
-        <x:f>IF(A138="","",IF(COUNTIF($R$6:$R$139,R138)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A138="","",IF(COUNTIF($R$6:$R$145,R138)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T138" s="63" t="str">
@@ -10527,7 +10586,7 @@
         <x:v>场景|review_board|training_range|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S139" s="63" t="str">
-        <x:f>IF(A139="","",IF(COUNTIF($R$6:$R$139,R139)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A139="","",IF(COUNTIF($R$6:$R$145,R139)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T139" s="63" t="str">
@@ -10544,6 +10603,460 @@
       </x:c>
       <x:c r="X139" s="63" t="str">
         <x:v>真实GPU窗口检查三条射击道、三类靶、枪弹组合区与灯光</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str">
+        <x:v>VFX-VISIBILITY-FIELD-3D</x:v>
+      </x:c>
+      <x:c r="B140" t="str">
+        <x:v>柔边真实单位视野场3D</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>特效</x:v>
+      </x:c>
+      <x:c r="D140" t="str">
+        <x:v>gameplay_vfx</x:v>
+      </x:c>
+      <x:c r="E140" t="str">
+        <x:v>visibility_field</x:v>
+      </x:c>
+      <x:c r="F140" t="str">
+        <x:v>field_mesh_3d</x:v>
+      </x:c>
+      <x:c r="G140" t="str">
+        <x:v>VFX-VISIBILITY-LIGHT</x:v>
+      </x:c>
+      <x:c r="H140" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I140" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J140" t="str">
+        <x:v>3D行动区/靶场/基地</x:v>
+      </x:c>
+      <x:c r="K140" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L140" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M140" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N140" t="str">
+        <x:v>ImmediateMesh 49+28射线</x:v>
+      </x:c>
+      <x:c r="O140" t="str">
+        <x:v>src/player3d/PlayerVision3D.gd</x:v>
+      </x:c>
+      <x:c r="P140" t="str">
+        <x:v>scenes/Player3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q140" t="str">
+        <x:v>真实视野;柔边;墙体遮挡;无描边;非灯光判定</x:v>
+      </x:c>
+      <x:c r="R140" t="str">
+        <x:f>LOWER(TRIM(C140)&amp;"|"&amp;TRIM(D140)&amp;"|"&amp;TRIM(E140)&amp;"|"&amp;TRIM(F140)&amp;"|"&amp;TRIM(H140)&amp;"|"&amp;TRIM(I140))</x:f>
+        <x:v>特效|gameplay_vfx|visibility_field|field_mesh_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S140" t="str">
+        <x:f>IF(A140="","",IF(COUNTIF($R$6:$R$145,R140)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T140" t="str">
+        <x:v>9cf388d92b26316426fe4aab529001ebd544731ea466470236ad73cdd655e87c</x:v>
+      </x:c>
+      <x:c r="U140" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V140" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="W140" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X140" t="str">
+        <x:v>逻辑与地面表现复用同批射线；96°/21m + 2.4m；柔边无描边且不受地板深度遮挡；真实照明拆为 VFX-PLAYER-FLASHLIGHT-3D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>UI-SCREEN-INVENTORY-3D</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>3D背包与保险界面</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="D141" t="str">
+        <x:v>screen</x:v>
+      </x:c>
+      <x:c r="E141" t="str">
+        <x:v>inventory</x:v>
+      </x:c>
+      <x:c r="F141" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G141" t="str">
+        <x:v>UI-SCREEN-INVENTORY</x:v>
+      </x:c>
+      <x:c r="H141" t="str">
+        <x:v>屏幕空间</x:v>
+      </x:c>
+      <x:c r="I141" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J141" t="str">
+        <x:v>3D行动区</x:v>
+      </x:c>
+      <x:c r="K141" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L141" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M141" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N141" t="str">
+        <x:v>全屏Control/12+2槽/96×96投影</x:v>
+      </x:c>
+      <x:c r="O141" t="str">
+        <x:v>src/ui/InventoryUI.gd</x:v>
+      </x:c>
+      <x:c r="P141" t="str">
+        <x:v>scenes/Dungeon3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q141" t="str">
+        <x:v>背包;保险;I键;Tab;模态输入锁;3D道具投影;实际点击装备</x:v>
+      </x:c>
+      <x:c r="R141" t="str">
+        <x:f>LOWER(TRIM(C141)&amp;"|"&amp;TRIM(D141)&amp;"|"&amp;TRIM(E141)&amp;"|"&amp;TRIM(F141)&amp;"|"&amp;TRIM(H141)&amp;"|"&amp;TRIM(I141))</x:f>
+        <x:v>ui|screen|inventory|root_3d|屏幕空间|default</x:v>
+      </x:c>
+      <x:c r="S141" t="str">
+        <x:f>IF(A141="","",IF(COUNTIF($R$6:$R$145,R141)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T141" t="str">
+        <x:v>ccd8f7d7f3c99454d157f0dfd2f34631a4d404931f2e1997b5c381db9ac90c99</x:v>
+      </x:c>
+      <x:c r="U141" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V141" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="W141" t="str">
+        <x:v>原创程序UI</x:v>
+      </x:c>
+      <x:c r="X141" t="str">
+        <x:v>复用背包根身份的3D子变体；I/Tab；打开时锁输入；道具共用 ItemModelFactory3D；实际 ItemSlot 信号完成换枪</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>UI-SCREEN-PAUSE-3D</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>3D共用暂停界面</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="D142" t="str">
+        <x:v>screen</x:v>
+      </x:c>
+      <x:c r="E142" t="str">
+        <x:v>pause</x:v>
+      </x:c>
+      <x:c r="F142" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G142"/>
+      <x:c r="H142" t="str">
+        <x:v>屏幕空间</x:v>
+      </x:c>
+      <x:c r="I142" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J142" t="str">
+        <x:v>地下城/基地/靶场</x:v>
+      </x:c>
+      <x:c r="K142" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L142" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M142" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N142" t="str">
+        <x:v>PackedScene/全屏Control</x:v>
+      </x:c>
+      <x:c r="O142" t="str">
+        <x:v>assets/art/ui/pause_3d/ui_pause_overlay_screen_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P142" t="str">
+        <x:v>src/ui/PauseMenu3D.gd</x:v>
+      </x:c>
+      <x:c r="Q142" t="str">
+        <x:v>暂停;Esc;继续;全局模态;3D HUD</x:v>
+      </x:c>
+      <x:c r="R142" t="str">
+        <x:f>LOWER(TRIM(C142)&amp;"|"&amp;TRIM(D142)&amp;"|"&amp;TRIM(E142)&amp;"|"&amp;TRIM(F142)&amp;"|"&amp;TRIM(H142)&amp;"|"&amp;TRIM(I142))</x:f>
+        <x:v>ui|screen|pause|root_3d|屏幕空间|default</x:v>
+      </x:c>
+      <x:c r="S142" t="str">
+        <x:f>IF(A142="","",IF(COUNTIF($R$6:$R$145,R142)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T142" t="str">
+        <x:v>8fed542ebf6b89002c6922a287e666394472252ad9673d8183dd9db604c19a88</x:v>
+      </x:c>
+      <x:c r="U142" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V142" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="W142" t="str">
+        <x:v>原创程序UI</x:v>
+      </x:c>
+      <x:c r="X142" t="str">
+        <x:v>三张3D地图共用；Esc先关闭最上层模态，再进入真实暂停</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>PRP-ROOM-LIGHT-SWITCH-3D</x:v>
+      </x:c>
+      <x:c r="B143" t="str">
+        <x:v>房间中央灯墙面开关3D</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>场景道具</x:v>
+      </x:c>
+      <x:c r="D143" t="str">
+        <x:v>facility</x:v>
+      </x:c>
+      <x:c r="E143" t="str">
+        <x:v>room_light_switch</x:v>
+      </x:c>
+      <x:c r="F143" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G143" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H143" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I143" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J143" t="str">
+        <x:v>随机关卡房间/四主题复用</x:v>
+      </x:c>
+      <x:c r="K143" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L143" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M143" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N143" t="str">
+        <x:v>PackedScene/Area3D</x:v>
+      </x:c>
+      <x:c r="O143" t="str">
+        <x:v>assets/art/props/dungeon_3d/prp_room_light_switch_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P143" t="str">
+        <x:v>src/world3d/RoomLightSwitch3D.gd</x:v>
+      </x:c>
+      <x:c r="Q143" t="str">
+        <x:v>房灯开关;墙面交互;中央顶灯;E键</x:v>
+      </x:c>
+      <x:c r="R143" t="str">
+        <x:f>LOWER(TRIM(C143)&amp;"|"&amp;TRIM(D143)&amp;"|"&amp;TRIM(E143)&amp;"|"&amp;TRIM(F143)&amp;"|"&amp;TRIM(H143)&amp;"|"&amp;TRIM(I143))</x:f>
+        <x:v>场景道具|facility|room_light_switch|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S143" t="str">
+        <x:f>IF(A143="","",IF(COUNTIF($R$6:$R$145,R143)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T143" t="str">
+        <x:v>7802bc3a71d892072e43962875e26b60443d19de35bcc77fe0cbedcfa6dd5d94</x:v>
+      </x:c>
+      <x:c r="U143" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V143" s="62" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="W143" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X143" t="str">
+        <x:v>每个房间共用一件；E键切换唯一中央顶灯；禁止复制到各主题局部目录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>VFX-PLAYER-FLASHLIGHT-3D</x:v>
+      </x:c>
+      <x:c r="B144" t="str">
+        <x:v>玩家真实探照灯组件3D</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>特效</x:v>
+      </x:c>
+      <x:c r="D144" t="str">
+        <x:v>gameplay_vfx</x:v>
+      </x:c>
+      <x:c r="E144" t="str">
+        <x:v>player_flashlight</x:v>
+      </x:c>
+      <x:c r="F144" t="str">
+        <x:v>light_rig_3d</x:v>
+      </x:c>
+      <x:c r="G144" t="str">
+        <x:v>VFX-VISIBILITY-FIELD-3D</x:v>
+      </x:c>
+      <x:c r="H144" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I144" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J144" t="str">
+        <x:v>3D行动区/靶场/基地</x:v>
+      </x:c>
+      <x:c r="K144" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L144" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M144" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N144" t="str">
+        <x:v>PackedScene/SpotLight3D+OmniLight3D</x:v>
+      </x:c>
+      <x:c r="O144" t="str">
+        <x:v>assets/art/vfx/visibility_3d/vfx_player_flashlight_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P144" t="str">
+        <x:v>src/player3d/PlayerFlashlight3D.gd</x:v>
+      </x:c>
+      <x:c r="Q144" t="str">
+        <x:v>真实探照灯;玩家灯光;前向聚光;角色补光;可调灯光</x:v>
+      </x:c>
+      <x:c r="R144" t="str">
+        <x:f>LOWER(TRIM(C144)&amp;"|"&amp;TRIM(D144)&amp;"|"&amp;TRIM(E144)&amp;"|"&amp;TRIM(F144)&amp;"|"&amp;TRIM(H144)&amp;"|"&amp;TRIM(I144))</x:f>
+        <x:v>特效|gameplay_vfx|player_flashlight|light_rig_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S144" t="str">
+        <x:f>IF(A144="","",IF(COUNTIF($R$6:$R$145,R144)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T144" t="str">
+        <x:v>b389efe1d1fcfd30087a6d3f3f2784effee95cf6c54769fde27ecb6806011a05</x:v>
+      </x:c>
+      <x:c r="U144" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V144" s="62" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="W144" t="str">
+        <x:v>原创程序灯光</x:v>
+      </x:c>
+      <x:c r="X144" t="str">
+        <x:v>独立于玩法视野；1盏投影主聚光 + 1盏无阴影近身补光；颜色/能量/范围/角度/衰减/挂点均可调</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>UI-ICON-ITEM-MODEL-3D</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>背包道具3D模型投影组件</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="D145" t="str">
+        <x:v>icon</x:v>
+      </x:c>
+      <x:c r="E145" t="str">
+        <x:v>item_model_icon</x:v>
+      </x:c>
+      <x:c r="F145" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G145" t="str">
+        <x:v>UI-SCREEN-INVENTORY-3D</x:v>
+      </x:c>
+      <x:c r="H145" t="str">
+        <x:v>屏幕空间/3D投影</x:v>
+      </x:c>
+      <x:c r="I145" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J145" t="str">
+        <x:v>背包/保险格/道具预览</x:v>
+      </x:c>
+      <x:c r="K145" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L145" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M145" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N145" t="str">
+        <x:v>96×96 SubViewport/UPDATE_ONCE</x:v>
+      </x:c>
+      <x:c r="O145" t="str">
+        <x:v>assets/art/ui/inventory_3d/ui_item_model_icon_root_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P145" t="str">
+        <x:v>src/ui/ItemModelIcon3D.gd</x:v>
+      </x:c>
+      <x:c r="Q145" t="str">
+        <x:v>3D道具图标;模型投影;背包图标;共享世界模型;单次渲染</x:v>
+      </x:c>
+      <x:c r="R145" t="str">
+        <x:f>LOWER(TRIM(C145)&amp;"|"&amp;TRIM(D145)&amp;"|"&amp;TRIM(E145)&amp;"|"&amp;TRIM(F145)&amp;"|"&amp;TRIM(H145)&amp;"|"&amp;TRIM(I145))</x:f>
+        <x:v>ui|icon|item_model_icon|root_3d|屏幕空间/3d投影|default</x:v>
+      </x:c>
+      <x:c r="S145" t="str">
+        <x:f>IF(A145="","",IF(COUNTIF($R$6:$R$145,R145)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T145" t="str">
+        <x:v>97c10f3884107c1263f3de1f8bc1ce84bb568ecd80418b62bdb023c55cdab9fe</x:v>
+      </x:c>
+      <x:c r="U145" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V145" s="62" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="W145" t="str">
+        <x:v>原创程序UI</x:v>
+      </x:c>
+      <x:c r="X145" t="str">
+        <x:v>与地面拾取共用 ItemModelFactory3D；96×96 内部视口缩放至56px槽位；只渲染一次；验收图：assets/art/ui/inventory_3d/ui_inventory_item_model_preview_v001.png</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10571,7 +11084,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2abd959a34ee4d7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2edbae0a0fb542b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11717,21 +12230,21 @@
         <x:v>InvincibleTimer 唯一解除</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="63" t="str">
-        <x:v>Enemy3D 七态状态机 × 模块表现映射</x:v>
-      </x:c>
-      <x:c r="B16" s="63"/>
-      <x:c r="C16" s="63"/>
-      <x:c r="D16" s="63"/>
-      <x:c r="E16" s="63"/>
-      <x:c r="F16" s="63"/>
-      <x:c r="G16" s="63"/>
-      <x:c r="H16" s="63"/>
-      <x:c r="I16" s="63"/>
-      <x:c r="J16" s="63"/>
-      <x:c r="K16" s="63"/>
-      <x:c r="L16" s="63"/>
+    <x:row r="16" ht="28" customHeight="1">
+      <x:c r="A16" s="69" t="str">
+        <x:v>Enemy3D 九态状态机 × 模块表现 × 模型轮廓碰撞</x:v>
+      </x:c>
+      <x:c r="B16" s="69"/>
+      <x:c r="C16" s="69"/>
+      <x:c r="D16" s="69"/>
+      <x:c r="E16" s="69"/>
+      <x:c r="F16" s="69"/>
+      <x:c r="G16" s="69"/>
+      <x:c r="H16" s="69"/>
+      <x:c r="I16" s="69"/>
+      <x:c r="J16" s="69"/>
+      <x:c r="K16" s="69"/>
+      <x:c r="L16" s="69"/>
     </x:row>
     <x:row r="17" ht="36" customHeight="1">
       <x:c r="A17" s="63" t="str">
@@ -11782,10 +12295,10 @@
         <x:v>待机</x:v>
       </x:c>
       <x:c r="D18" s="63" t="str">
-        <x:v>start/stagger</x:v>
+        <x:v>start/patrol/stagger</x:v>
       </x:c>
       <x:c r="E18" s="63" t="str">
-        <x:v>alert/dead</x:v>
+        <x:v>patrol/alert/dead</x:v>
       </x:c>
       <x:c r="F18" s="63" t="str">
         <x:v>低频脉冲</x:v>
@@ -11814,37 +12327,37 @@
         <x:v>顶层</x:v>
       </x:c>
       <x:c r="B19" s="63" t="str">
-        <x:v>alert</x:v>
+        <x:v>patrol</x:v>
       </x:c>
       <x:c r="C19" s="63" t="str">
-        <x:v>警觉</x:v>
+        <x:v>巡逻</x:v>
       </x:c>
       <x:c r="D19" s="63" t="str">
-        <x:v>idle</x:v>
+        <x:v>idle/search</x:v>
       </x:c>
       <x:c r="E19" s="63" t="str">
-        <x:v>chase/dead</x:v>
+        <x:v>idle/alert/stagger/dead</x:v>
       </x:c>
       <x:c r="F19" s="63" t="str">
-        <x:v>加速</x:v>
+        <x:v>低频脉冲</x:v>
       </x:c>
       <x:c r="G19" s="63" t="str">
-        <x:v>抬升</x:v>
+        <x:v>朝巡逻点</x:v>
       </x:c>
       <x:c r="H19" s="63" t="str">
-        <x:v>展开</x:v>
+        <x:v>慢速步态</x:v>
       </x:c>
       <x:c r="I19" s="63" t="str">
         <x:v>关闭</x:v>
       </x:c>
       <x:c r="J19" s="63" t="str">
-        <x:v>发现玩家</x:v>
+        <x:v>出生点附近巡逻</x:v>
       </x:c>
       <x:c r="K19" s="63" t="str">
-        <x:v>0.28s响应</x:v>
+        <x:v>无目标不原地僵住</x:v>
       </x:c>
       <x:c r="L19" s="63" t="str">
-        <x:v>模块变换</x:v>
+        <x:v>CharacterBody3D</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
@@ -11852,37 +12365,37 @@
         <x:v>顶层</x:v>
       </x:c>
       <x:c r="B20" s="63" t="str">
-        <x:v>chase</x:v>
+        <x:v>alert</x:v>
       </x:c>
       <x:c r="C20" s="63" t="str">
-        <x:v>追击</x:v>
+        <x:v>警觉</x:v>
       </x:c>
       <x:c r="D20" s="63" t="str">
-        <x:v>alert/attack/stagger</x:v>
+        <x:v>idle/patrol/search</x:v>
       </x:c>
       <x:c r="E20" s="63" t="str">
-        <x:v>telegraph/stagger/dead</x:v>
+        <x:v>chase/stagger/dead</x:v>
       </x:c>
       <x:c r="F20" s="63" t="str">
-        <x:v>稳定</x:v>
+        <x:v>加速</x:v>
       </x:c>
       <x:c r="G20" s="63" t="str">
-        <x:v>朝目标</x:v>
+        <x:v>抬升</x:v>
       </x:c>
       <x:c r="H20" s="63" t="str">
-        <x:v>步态</x:v>
+        <x:v>展开</x:v>
       </x:c>
       <x:c r="I20" s="63" t="str">
         <x:v>关闭</x:v>
       </x:c>
       <x:c r="J20" s="63" t="str">
-        <x:v>距离控制</x:v>
+        <x:v>发现玩家</x:v>
       </x:c>
       <x:c r="K20" s="63" t="str">
-        <x:v>七类速度差</x:v>
+        <x:v>0.28s响应</x:v>
       </x:c>
       <x:c r="L20" s="63" t="str">
-        <x:v>CharacterBody3D</x:v>
+        <x:v>模块变换</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
@@ -11890,37 +12403,37 @@
         <x:v>顶层</x:v>
       </x:c>
       <x:c r="B21" s="63" t="str">
-        <x:v>telegraph</x:v>
+        <x:v>chase</x:v>
       </x:c>
       <x:c r="C21" s="63" t="str">
-        <x:v>预警</x:v>
+        <x:v>追击</x:v>
       </x:c>
       <x:c r="D21" s="63" t="str">
-        <x:v>chase</x:v>
+        <x:v>alert/attack/stagger</x:v>
       </x:c>
       <x:c r="E21" s="63" t="str">
-        <x:v>attack/stagger/dead</x:v>
+        <x:v>search/telegraph/stagger/dead</x:v>
       </x:c>
       <x:c r="F21" s="63" t="str">
-        <x:v>高频脉冲</x:v>
+        <x:v>稳定</x:v>
       </x:c>
       <x:c r="G21" s="63" t="str">
-        <x:v>稳定</x:v>
+        <x:v>朝目标</x:v>
       </x:c>
       <x:c r="H21" s="63" t="str">
-        <x:v>蓄势</x:v>
+        <x:v>步态</x:v>
       </x:c>
       <x:c r="I21" s="63" t="str">
-        <x:v>红色预警环</x:v>
+        <x:v>关闭</x:v>
       </x:c>
       <x:c r="J21" s="63" t="str">
-        <x:v>攻击前摇</x:v>
+        <x:v>距离控制</x:v>
       </x:c>
       <x:c r="K21" s="63" t="str">
-        <x:v>不可省略</x:v>
+        <x:v>七类速度差</x:v>
       </x:c>
       <x:c r="L21" s="63" t="str">
-        <x:v>计时状态</x:v>
+        <x:v>CharacterBody3D</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="42" customHeight="1">
@@ -11928,37 +12441,37 @@
         <x:v>顶层</x:v>
       </x:c>
       <x:c r="B22" s="63" t="str">
-        <x:v>attack</x:v>
+        <x:v>search</x:v>
       </x:c>
       <x:c r="C22" s="63" t="str">
-        <x:v>攻击</x:v>
+        <x:v>搜索</x:v>
       </x:c>
       <x:c r="D22" s="63" t="str">
-        <x:v>telegraph</x:v>
+        <x:v>chase</x:v>
       </x:c>
       <x:c r="E22" s="63" t="str">
-        <x:v>chase/dead</x:v>
+        <x:v>patrol/alert/stagger/dead</x:v>
       </x:c>
       <x:c r="F22" s="63" t="str">
-        <x:v>峰值</x:v>
+        <x:v>渐缓</x:v>
       </x:c>
       <x:c r="G22" s="63" t="str">
-        <x:v>反冲</x:v>
+        <x:v>朝最后位置</x:v>
       </x:c>
       <x:c r="H22" s="63" t="str">
-        <x:v>执行</x:v>
+        <x:v>搜索步态</x:v>
       </x:c>
       <x:c r="I22" s="63" t="str">
-        <x:v>按攻击类型</x:v>
+        <x:v>搜索提示</x:v>
       </x:c>
       <x:c r="J22" s="63" t="str">
-        <x:v>近战/远程/召唤/爆炸</x:v>
+        <x:v>失去视线后搜索</x:v>
       </x:c>
       <x:c r="K22" s="63" t="str">
-        <x:v>七类差异</x:v>
+        <x:v>2.4s后回巡逻</x:v>
       </x:c>
       <x:c r="L22" s="63" t="str">
-        <x:v>profile策略</x:v>
+        <x:v>射线+最后位置</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="42" customHeight="1">
@@ -11966,37 +12479,37 @@
         <x:v>顶层</x:v>
       </x:c>
       <x:c r="B23" s="63" t="str">
-        <x:v>stagger</x:v>
+        <x:v>telegraph</x:v>
       </x:c>
       <x:c r="C23" s="63" t="str">
-        <x:v>硬直</x:v>
+        <x:v>预警</x:v>
       </x:c>
       <x:c r="D23" s="63" t="str">
-        <x:v>任意存活态</x:v>
+        <x:v>chase</x:v>
       </x:c>
       <x:c r="E23" s="63" t="str">
-        <x:v>chase/dead</x:v>
+        <x:v>attack/stagger/dead</x:v>
       </x:c>
       <x:c r="F23" s="63" t="str">
-        <x:v>闪色</x:v>
+        <x:v>高频脉冲</x:v>
       </x:c>
       <x:c r="G23" s="63" t="str">
-        <x:v>冲击</x:v>
+        <x:v>稳定</x:v>
       </x:c>
       <x:c r="H23" s="63" t="str">
-        <x:v>暂停</x:v>
+        <x:v>蓄势</x:v>
       </x:c>
       <x:c r="I23" s="63" t="str">
-        <x:v>伤害反馈</x:v>
+        <x:v>红色预警环</x:v>
       </x:c>
       <x:c r="J23" s="63" t="str">
-        <x:v>受击窗口</x:v>
+        <x:v>攻击前摇</x:v>
       </x:c>
       <x:c r="K23" s="63" t="str">
-        <x:v>方向可读</x:v>
+        <x:v>不可省略</x:v>
       </x:c>
       <x:c r="L23" s="63" t="str">
-        <x:v>统一伤害入口</x:v>
+        <x:v>计时状态</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="42" customHeight="1">
@@ -12004,36 +12517,112 @@
         <x:v>顶层</x:v>
       </x:c>
       <x:c r="B24" s="63" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="C24" s="63" t="str">
+        <x:v>攻击</x:v>
+      </x:c>
+      <x:c r="D24" s="63" t="str">
+        <x:v>telegraph</x:v>
+      </x:c>
+      <x:c r="E24" s="63" t="str">
+        <x:v>chase/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F24" s="63" t="str">
+        <x:v>峰值</x:v>
+      </x:c>
+      <x:c r="G24" s="63" t="str">
+        <x:v>反冲</x:v>
+      </x:c>
+      <x:c r="H24" s="63" t="str">
+        <x:v>执行</x:v>
+      </x:c>
+      <x:c r="I24" s="63" t="str">
+        <x:v>按攻击类型</x:v>
+      </x:c>
+      <x:c r="J24" s="63" t="str">
+        <x:v>近战/远程/召唤/爆炸</x:v>
+      </x:c>
+      <x:c r="K24" s="63" t="str">
+        <x:v>七类差异</x:v>
+      </x:c>
+      <x:c r="L24" s="63" t="str">
+        <x:v>profile策略</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>stagger</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>硬直</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>任意存活态</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>chase/dead</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>闪色</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>冲击</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>暂停</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>伤害反馈</x:v>
+      </x:c>
+      <x:c r="J25" t="str">
+        <x:v>受击窗口</x:v>
+      </x:c>
+      <x:c r="K25" t="str">
+        <x:v>方向可读</x:v>
+      </x:c>
+      <x:c r="L25" t="str">
+        <x:v>统一伤害入口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
         <x:v>dead</x:v>
       </x:c>
-      <x:c r="C24" s="63" t="str">
+      <x:c r="C26" t="str">
         <x:v>死亡</x:v>
       </x:c>
-      <x:c r="D24" s="63" t="str">
+      <x:c r="D26" t="str">
         <x:v>任意存活态</x:v>
       </x:c>
-      <x:c r="E24" s="63" t="str">
+      <x:c r="E26" t="str">
         <x:v>无（终态）</x:v>
       </x:c>
-      <x:c r="F24" s="63" t="str">
+      <x:c r="F26" t="str">
         <x:v>熄灭</x:v>
       </x:c>
-      <x:c r="G24" s="63" t="str">
+      <x:c r="G26" t="str">
         <x:v>压扁</x:v>
       </x:c>
-      <x:c r="H24" s="63" t="str">
+      <x:c r="H26" t="str">
         <x:v>停止</x:v>
       </x:c>
-      <x:c r="I24" s="63" t="str">
+      <x:c r="I26" t="str">
         <x:v>爆散/淡出</x:v>
       </x:c>
-      <x:c r="J24" s="63" t="str">
+      <x:c r="J26" t="str">
         <x:v>掉落与计数</x:v>
       </x:c>
-      <x:c r="K24" s="63" t="str">
+      <x:c r="K26" t="str">
         <x:v>不可回存活态</x:v>
       </x:c>
-      <x:c r="L24" s="63" t="str">
+      <x:c r="L26" t="str">
         <x:v>终态 + Tween</x:v>
       </x:c>
     </x:row>
@@ -12041,6 +12630,7 @@
   <x:mergeCells>
     <x:mergeCell ref="A1:L2"/>
     <x:mergeCell ref="A3:L3"/>
+    <x:mergeCell ref="A16:L16"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -12214,7 +12804,7 @@
         <x:v>场景道具</x:v>
       </x:c>
       <x:c r="C11" s="37" t="str">
-        <x:v>facility / container / door / debris</x:v>
+        <x:v>facility / container / door / debris / light / switch</x:v>
       </x:c>
       <x:c r="D11" s="37" t="str">
         <x:v>assets/art/props/</x:v>
@@ -12507,10 +13097,10 @@
         <x:v>验收</x:v>
       </x:c>
       <x:c r="C11" s="37" t="str">
-        <x:v>透明边缘或3D灯光/雾/碰撞/状态/节点预算</x:v>
+        <x:v>透明边缘或3D灯光/雾/碰撞/状态/玩法逻辑/节点预算</x:v>
       </x:c>
       <x:c r="D11" s="37" t="str">
-        <x:v>真实游戏镜头与严格专项通过</x:v>
+        <x:v>真实游戏镜头 + 玩法专项 + 性能专项通过</x:v>
       </x:c>
       <x:c r="E11" s="37" t="str">
         <x:v>只看母版或编辑器预览</x:v>
@@ -12519,7 +13109,7 @@
         <x:v>3D主题关卡</x:v>
       </x:c>
       <x:c r="G11" s="37" t="str">
-        <x:v>seed/灯池/七怪/56组合/撤离 PASS</x:v>
+        <x:v>seed/暗室开关/遮挡视野/七怪/56组合/撤离 PASS</x:v>
       </x:c>
       <x:c r="H11" s="37" t="str">
         <x:v>K/P/X</x:v>
@@ -13151,6 +13741,75 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="11" ht="58" customHeight="1">
+      <x:c r="A11" s="63" t="str">
+        <x:v>v1.5</x:v>
+      </x:c>
+      <x:c r="B11" s="64" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="C11" s="63" t="str">
+        <x:v>真实视野与3D输入验收登记</x:v>
+      </x:c>
+      <x:c r="D11" s="63" t="str">
+        <x:v>3D视野 / 背包 / 暂停 / Enemy3D</x:v>
+      </x:c>
+      <x:c r="E11" s="63" t="str">
+        <x:v>登记真实视野场、3D背包子变体和共用暂停UI；低血暗角完成接入；Enemy3D状态表由七态修正为九态</x:v>
+      </x:c>
+      <x:c r="F11" s="63" t="str">
+        <x:v>复用既有视野/背包/VFX根身份；新增暂停根；不改变2D资产ID</x:v>
+      </x:c>
+      <x:c r="G11" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="63" t="str">
+        <x:v>v1.6</x:v>
+      </x:c>
+      <x:c r="B12" s="64" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="C12" s="63" t="str">
+        <x:v>暗室照明与战斗生态登记</x:v>
+      </x:c>
+      <x:c r="D12" s="63" t="str">
+        <x:v>3D视野 / 房灯 / 怪物 / 枪械组合</x:v>
+      </x:c>
+      <x:c r="E12" s="63" t="str">
+        <x:v>登记柔边视野与表现层探照灯、中央顶灯与墙面开关；七类怪碰撞随模型轮廓；枪械/子弹3D适配与开局副枪完成</x:v>
+      </x:c>
+      <x:c r="F12" s="63" t="str">
+        <x:v>新增一个房灯开关根；其余复用既有根ID；玩法逻辑与表现解耦</x:v>
+      </x:c>
+      <x:c r="G12" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="60" customHeight="1">
+      <x:c r="A13" s="70" t="str">
+        <x:v>v1.7</x:v>
+      </x:c>
+      <x:c r="B13" s="71" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="C13" s="70" t="str">
+        <x:v>真实灯光与3D背包投影登记</x:v>
+      </x:c>
+      <x:c r="D13" s="70" t="str">
+        <x:v>玩家探照灯 / 3D背包 / 世界道具模型</x:v>
+      </x:c>
+      <x:c r="E13" s="70" t="str">
+        <x:v>登记独立真实探照灯和共用3D道具投影；视野不再持有灯光；实际槽位点击换枪纳入资产验收</x:v>
+      </x:c>
+      <x:c r="F13" s="70" t="str">
+        <x:v>新增两个可复用子资产；不复制每个道具图标；玩法视野与灯光继续解耦</x:v>
+      </x:c>
+      <x:c r="G13" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G2"/>

--- a/outputs/019f8417-e7f4-7bc3-aded-c62dfd1d1462/ShellStorm2_美术资产台账_v001.xlsx
+++ b/outputs/019f8417-e7f4-7bc3-aded-c62dfd1d1462/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf037c12262a645be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R3e1cd7d8497b4ae3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rdf02083753b14321"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rabe250e950244608"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R039802b8ef1641a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rb8d16a866a6d4d67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R9ea68df7be064d6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R8059162294d64002"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf64f1312d80946d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rd986e361c39d4b34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rbb4561200bcd4f4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rf0b0c6022c314180"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R1e250af707284e99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rac42cf6b203a4968"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R5dfbe29cb13a4b58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R71dcffa382ea424f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="19">
+  <x:fonts count="20">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -132,8 +132,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF137333"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -178,6 +184,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF10212C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F3E7"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -230,7 +241,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="72">
+  <x:cellXfs count="74">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -399,6 +410,8 @@
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -768,12 +781,12 @@
       <x:c r="B6" s="43"/>
       <x:c r="C6" s="45" t="n">
         <x:f>COUNTIF('资产主表'!$K$6:$K$200,"已完成")+COUNTIF('资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D6" s="43"/>
       <x:c r="E6" s="45" t="n">
         <x:f>COUNTIF('资产主表'!$K$6:$K$200,"待制作")+COUNTIF('资产主表'!$K$6:$K$200,"程序占位")</x:f>
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F6" s="43"/>
       <x:c r="G6" s="45" t="n">
@@ -782,7 +795,7 @@
       </x:c>
       <x:c r="H6" s="43"/>
       <x:c r="I6" s="46" t="str">
-        <x:v>全3D闭环 / 三档房间 / 暗室开关 / 七类怪 / 56枪弹组合</x:v>
+        <x:v>全3D闭环 / PH29 换弹覆盖态 / 真实头顶进度 / 单手枪同相</x:v>
       </x:c>
       <x:c r="J6" s="46"/>
     </x:row>
@@ -918,7 +931,7 @@
       </x:c>
       <x:c r="C13" s="52" t="n">
         <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A13,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A13,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D13" s="43"/>
       <x:c r="E13" s="51" t="str">
@@ -4266,10 +4279,10 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="J49" s="37" t="str">
-        <x:v>世界拾取/UI 图标</x:v>
+        <x:v>全部3D房间/清房奖励</x:v>
       </x:c>
       <x:c r="K49" s="37" t="str">
-        <x:v>程序占位</x:v>
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="L49" s="37" t="str">
         <x:v>P1</x:v>
@@ -4278,11 +4291,11 @@
         <x:v>v001</x:v>
       </x:c>
       <x:c r="N49" s="37" t="str">
-        <x:v>世界 24–40 px；UI 32 px</x:v>
-      </x:c>
-      <x:c r="O49" s="37" t="str"/>
+        <x:v>程序模型/0.32s Tween</x:v>
+      </x:c>
+      <x:c r="O49" s="37"/>
       <x:c r="P49" s="37" t="str">
-        <x:v>scenes/</x:v>
+        <x:v>src/world3d/RoomKeyPickup3D.gd</x:v>
       </x:c>
       <x:c r="Q49" s="37" t="str"/>
       <x:c r="R49" s="37" t="str">
@@ -4295,15 +4308,17 @@
       </x:c>
       <x:c r="T49" s="37" t="str"/>
       <x:c r="U49" s="37" t="str">
-        <x:v>待分配</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="V49" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W49" s="37" t="str">
-        <x:v>原创/待确认</x:v>
-      </x:c>
-      <x:c r="X49" s="37" t="str"/>
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X49" s="37" t="str">
+        <x:v>清房后在玩家附近安全边界生成；同房唯一且返回时可补发；成功拾取先关闭碰撞，再上弹旋转缩小后回收</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="37" t="str">
@@ -4332,10 +4347,10 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="J50" s="37" t="str">
-        <x:v>世界拾取/UI 图标</x:v>
+        <x:v>地面掉落/背包投影</x:v>
       </x:c>
       <x:c r="K50" s="37" t="str">
-        <x:v>程序占位</x:v>
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="L50" s="37" t="str">
         <x:v>P2</x:v>
@@ -4344,11 +4359,11 @@
         <x:v>v001</x:v>
       </x:c>
       <x:c r="N50" s="37" t="str">
-        <x:v>世界 24–40 px；UI 32 px</x:v>
-      </x:c>
-      <x:c r="O50" s="37" t="str"/>
+        <x:v>程序模型/0.32s Tween</x:v>
+      </x:c>
+      <x:c r="O50" s="37"/>
       <x:c r="P50" s="37" t="str">
-        <x:v>scenes/</x:v>
+        <x:v>src/world3d/GroundLootPickup3D.gd</x:v>
       </x:c>
       <x:c r="Q50" s="37" t="str"/>
       <x:c r="R50" s="37" t="str">
@@ -4361,15 +4376,17 @@
       </x:c>
       <x:c r="T50" s="37" t="str"/>
       <x:c r="U50" s="37" t="str">
-        <x:v>待分配</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="V50" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W50" s="37" t="str">
-        <x:v>原创/待确认</x:v>
-      </x:c>
-      <x:c r="X50" s="37" t="str"/>
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X50" s="37" t="str">
+        <x:v>与背包投影共用 ItemModelFactory3D；满包时保留，成功接收后播放0.32秒上弹旋转缩小动画</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="37" t="str">
@@ -8624,19 +8641,19 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T113" t="str">
-        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
       </x:c>
       <x:c r="U113" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V113" s="62" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W113" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X113" t="str">
-        <x:v>2D逻辑资产的3D表现变体；无腿、单手、无手臂</x:v>
+        <x:v>2D逻辑资产的3D表现变体；六态白名单正常；moving使用位移驱动独立组件循环；角色网格使用render layer 2；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -8700,19 +8717,19 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T114" t="str">
-        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
       </x:c>
       <x:c r="U114" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V114" s="62" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W114" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X114" t="str">
-        <x:v>PackedScene内独立Body节点；后续可替换GLB</x:v>
+        <x:v>PackedScene内独立Body节点；moving执行0.10m弹跳与压缩回弹；后续可替换GLB；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -8776,19 +8793,19 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T115" t="str">
-        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
       </x:c>
       <x:c r="U115" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V115" s="62" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W115" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X115" t="str">
-        <x:v>PackedScene内独立Head节点；无嘴无人脸</x:v>
+        <x:v>PackedScene内独立Head节点；无人脸；移动时采用小幅反相滞后，避免与身体刚性粘连；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -8852,19 +8869,19 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T116" t="str">
-        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
       </x:c>
       <x:c r="U116" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V116" s="62" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W116" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X116" t="str">
-        <x:v>唯一可见手；随VisualRoot转向并保持身体局部位置</x:v>
+        <x:v>唯一可见手；随VisualRoot转向；与weapon_socket使用完全相同的移动偏移，局部关系不变；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -8928,19 +8945,19 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T117" t="str">
-        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
       </x:c>
       <x:c r="U117" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V117" s="62" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W117" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X117" t="str">
-        <x:v>独立Scarf节点；保留移动与冲刺滞后动态</x:v>
+        <x:v>独立Scarf节点；moving读取同一周期并使用较慢跟随形成滞后，冲刺保留飘动；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -9004,19 +9021,19 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T118" t="str">
-        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
       </x:c>
       <x:c r="U118" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V118" s="62" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W118" t="str">
         <x:v>原创逻辑挂点</x:v>
       </x:c>
       <x:c r="X118" t="str">
-        <x:v>手和挂点保持局部关系；VisualRoot统一跟随准星转向</x:v>
+        <x:v>手和挂点保持固定局部关系；随moving同相偏移；手持枪模型使用render layer 2；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -9774,7 +9791,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X128" s="63" t="str">
-        <x:v>同根支持 street/ceiling；房间只实例化唯一中央顶灯，不生成室内路灯或假光池；默认关闭并由墙面开关控制</x:v>
+        <x:v>同根支持street/ceiling；房间只实例化唯一中央顶灯，默认关闭并由墙面开关控制；PH28开启能量较旧基线提高约22%</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="34" customHeight="1">
@@ -10222,13 +10239,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V134" s="64" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W134" s="63" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X134" s="63" t="str">
-        <x:v>真实GPU窗口检查暗室、家具、角色、怪物和战斗；开灯状态复用同一身份，验收图：assets/art/environments/dungeon_3d/env_dungeon_runtime_light_on_preview_top3d_v001.png</x:v>
+        <x:v>真实GPU窗口检查暗室、家具、角色、怪物和战斗；开灯状态复用同一身份，验收图：assets/art/environments/dungeon_3d/env_dungeon_runtime_light_on_preview_top3d_v001.png；WeaponModel3D为换弹唯一计时源；开始/连续进度/完成或取消信号驱动六态覆盖动画与头顶条；56组合共用</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="34" customHeight="1">
@@ -10302,7 +10319,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X135" s="63" t="str">
-        <x:v>追猎/远程/召唤/盾甲/自爆/伏击/Boss；统一九态：idle/patrol/alert/chase/search/telegraph/attack/stagger/dead</x:v>
+        <x:v>九态AI视线允许射线命中玩家本体并保留实体墙遮挡；3D基础HP乘旧楼层/主题/精英倍率，开局手枪普通命中不秒杀基础怪</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="34" customHeight="1">
@@ -10514,19 +10531,19 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T138" s="63" t="str">
-        <x:v>b6001154cf08404addb31b69dd38eaba41abe2a82ff6d2408bb5af8fe7a105b0</x:v>
+        <x:v>3b2c2212f1283ed366a31dc3a101b3555c78768c3906600eb0b18c74423fb247</x:v>
       </x:c>
       <x:c r="U138" s="63" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V138" s="64" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W138" s="63" t="str">
         <x:v>项目运行截图</x:v>
       </x:c>
       <x:c r="X138" s="63" t="str">
-        <x:v>真实GPU窗口检查房间、灯池、家具、角色、怪物和战斗可读性</x:v>
+        <x:v>实际GPU窗口确认360°遮挡逻辑与96°定向表现；PH28三层玩家灯去除头顶溢光，角色正面柔光、增强中央灯与战斗轮廓通过验收</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="34" customHeight="1">
@@ -10646,7 +10663,7 @@
         <x:v>v001</x:v>
       </x:c>
       <x:c r="N140" t="str">
-        <x:v>ImmediateMesh 49+28射线</x:v>
+        <x:v>360°逻辑射线 + ImmediateMesh 49+28表现射线</x:v>
       </x:c>
       <x:c r="O140" t="str">
         <x:v>src/player3d/PlayerVision3D.gd</x:v>
@@ -10655,7 +10672,7 @@
         <x:v>scenes/Player3D.tscn</x:v>
       </x:c>
       <x:c r="Q140" t="str">
-        <x:v>真实视野;柔边;墙体遮挡;无描边;非灯光判定</x:v>
+        <x:v>360度逻辑视野;96度目光表现;柔边;墙体遮挡;无描边;非灯光判定</x:v>
       </x:c>
       <x:c r="R140" t="str">
         <x:f>LOWER(TRIM(C140)&amp;"|"&amp;TRIM(D140)&amp;"|"&amp;TRIM(E140)&amp;"|"&amp;TRIM(F140)&amp;"|"&amp;TRIM(H140)&amp;"|"&amp;TRIM(I140))</x:f>
@@ -10666,7 +10683,7 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T140" t="str">
-        <x:v>9cf388d92b26316426fe4aab529001ebd544731ea466470236ad73cdd655e87c</x:v>
+        <x:v>f2b2eaf61798845c9068d45db0fdad2b32930df5b14a259e36bb8be67eefda07</x:v>
       </x:c>
       <x:c r="U140" t="str">
         <x:v>Codex</x:v>
@@ -10678,7 +10695,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X140" t="str">
-        <x:v>逻辑与地面表现复用同批射线；96°/21m + 2.4m；柔边无描边且不受地板深度遮挡；真实照明拆为 VFX-PLAYER-FLASHLIGHT-3D</x:v>
+        <x:v>目标显隐使用21m内360°逐目标物理遮挡；身后无遮挡目标保持可见，任意方向的墙/关闭门/实体家具均可遮挡。地面表现保留96°/21m + 2.4m、49+28固定射线、柔边无描边和地板深度豁免；真实照明仍拆为 VFX-PLAYER-FLASHLIGHT-3D。</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -10948,7 +10965,7 @@
         <x:v>v001</x:v>
       </x:c>
       <x:c r="N144" t="str">
-        <x:v>PackedScene/SpotLight3D+OmniLight3D</x:v>
+        <x:v>PackedScene/2 SpotLight3D+1 OmniLight3D</x:v>
       </x:c>
       <x:c r="O144" t="str">
         <x:v>assets/art/vfx/visibility_3d/vfx_player_flashlight_root_top3d_v001.tscn</x:v>
@@ -10980,7 +10997,7 @@
         <x:v>原创程序灯光</x:v>
       </x:c>
       <x:c r="X144" t="str">
-        <x:v>独立于玩法视野；1盏投影主聚光 + 1盏无阴影近身补光；颜色/能量/范围/角度/衰减/挂点均可调</x:v>
+        <x:v>独立于玩法视野；环境layer1=投影主聚光+无阴影近身溢光，角色/手持枪layer2=微弱无阴影正面柔光；头顶环境灯不影响角色</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -11084,7 +11101,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2edbae0a0fb542b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc54e4f8a28d64a35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11555,7 +11572,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J14" s="63" t="str">
-        <x:v>六态整体变换</x:v>
+        <x:v>六态整体变换 + reloading覆盖</x:v>
       </x:c>
       <x:c r="K14" s="63" t="str">
         <x:v>3D表现根</x:v>
@@ -11564,7 +11581,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M14" s="63" t="str">
-        <x:v>与2D共用状态ID；摄像机不跟随VisualRoot旋转</x:v>
+        <x:v>与2D共用六态ID；reloading不替换顶层；摄像机和头顶条不跟随VisualRoot旋转</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="34" customHeight="1">
@@ -11596,7 +11613,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="63" t="str">
-        <x:v>呼吸/移动压缩/死亡倾倒</x:v>
+        <x:v>独立移动弹性/呼吸/死亡倾倒</x:v>
       </x:c>
       <x:c r="K15" s="63" t="str">
         <x:v>防护服主体</x:v>
@@ -11605,7 +11622,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M15" s="63" t="str">
-        <x:v>无腿、无脚、无手臂</x:v>
+        <x:v>无腿、无脚、无手臂；render layer 2；移动振幅沿用2D弹性</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -11637,7 +11654,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J16" s="63" t="str">
-        <x:v>移动滞后/冲刺飘动</x:v>
+        <x:v>移动周期滞后/冲刺飘动</x:v>
       </x:c>
       <x:c r="K16" s="63" t="str">
         <x:v>身份配件</x:v>
@@ -11646,7 +11663,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="M16" s="63" t="str">
-        <x:v>独立红围巾组件</x:v>
+        <x:v>独立红围巾组件；moving以较慢跟随形成可读滞后</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="34" customHeight="1">
@@ -11678,7 +11695,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J17" s="63" t="str">
-        <x:v>呼吸滞后/受击/死亡</x:v>
+        <x:v>移动反相滞后/呼吸/受击/死亡</x:v>
       </x:c>
       <x:c r="K17" s="63" t="str">
         <x:v>头壳/传感器</x:v>
@@ -11687,7 +11704,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M17" s="63" t="str">
-        <x:v>单传感器；无嘴无人脸</x:v>
+        <x:v>单传感器；无嘴无人脸；只受角色正面柔光与房间公共灯</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="34" customHeight="1">
@@ -11713,13 +11730,13 @@
         <x:v>(0.72,1.22,-0.18)</x:v>
       </x:c>
       <x:c r="H18" s="63" t="str">
-        <x:v>随root；局部不旋转</x:v>
+        <x:v>随root；换弹时同相位移/旋转</x:v>
       </x:c>
       <x:c r="I18" s="63" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J18" s="63" t="str">
-        <x:v>随身体转向；保持局部握持位</x:v>
+        <x:v>moving同相；换弹下压/操作/回位；保持握持位</x:v>
       </x:c>
       <x:c r="K18" s="63" t="str">
         <x:v>唯一握持手</x:v>
@@ -11728,7 +11745,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M18" s="63" t="str">
-        <x:v>只有一只手；不单独追踪准星</x:v>
+        <x:v>只有一只手；与weapon_socket在moving/reloading全周期保持固定相对向量</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="34" customHeight="1">
@@ -11754,13 +11771,13 @@
         <x:v>(0.72,1.24,-0.34)</x:v>
       </x:c>
       <x:c r="H19" s="63" t="str">
-        <x:v>随root；局部不旋转</x:v>
+        <x:v>随root；换弹时同相位移/旋转</x:v>
       </x:c>
       <x:c r="I19" s="63" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="J19" s="63" t="str">
-        <x:v>枪械挂载/枪口特效</x:v>
+        <x:v>与唯一手同相；换弹下压/操作/回位；枪械挂载/枪口特效</x:v>
       </x:c>
       <x:c r="K19" s="63" t="str">
         <x:v>武器系统</x:v>
@@ -11769,7 +11786,48 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M19" s="63" t="str">
-        <x:v>挂点与手保持固定局部关系；枪身读取BlueprintRegistry并只做局部后坐力</x:v>
+        <x:v>挂点与手在moving/reloading保持固定局部关系；手持枪网格统一render layer 2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="34" customHeight="1">
+      <x:c r="A20" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B20" s="63" t="str">
+        <x:v>reload_progress</x:v>
+      </x:c>
+      <x:c r="C20" s="63" t="str">
+        <x:v>ReloadProgress3D</x:v>
+      </x:c>
+      <x:c r="D20" s="63" t="str">
+        <x:v>player_root</x:v>
+      </x:c>
+      <x:c r="E20" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F20" s="63" t="str">
+        <x:v>QuadMesh×2</x:v>
+      </x:c>
+      <x:c r="G20" s="63" t="str">
+        <x:v>(0,2.72,0.06)</x:v>
+      </x:c>
+      <x:c r="H20" s="63" t="str">
+        <x:v>朝向相机；不随VisualRoot旋转</x:v>
+      </x:c>
+      <x:c r="I20" s="63" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J20" s="63" t="str">
+        <x:v>读取真实换弹进度；左端固定；完成/取消隐藏</x:v>
+      </x:c>
+      <x:c r="K20" s="63" t="str">
+        <x:v>状态UI子组件</x:v>
+      </x:c>
+      <x:c r="L20" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M20" s="63" t="str">
+        <x:v>无独立计时器/SubViewport；不参与碰撞、视野、灯光或输入；56组合共用</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11836,7 +11894,7 @@
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>2D/3D 共用六态 ID 与转换白名单；Low HP / Silenced / Invincible 为叠加层。3D 首版继续用组件变换，新增动画前先查本表</x:v>
+        <x:v>2D/3D 共用六态 ID 与转换白名单；Low HP / Silenced / Invincible / Reloading 为叠加层。Reloading 读取武器唯一计时，新增动画前先查本表</x:v>
       </x:c>
       <x:c r="B3" s="6"/>
       <x:c r="C3" s="6"/>
@@ -11943,25 +12001,25 @@
         <x:v>idle,dashing,hurt,locked,dead</x:v>
       </x:c>
       <x:c r="F7" s="37" t="str">
-        <x:v>上下弹性</x:v>
+        <x:v>位移驱动弹跳/压缩回弹</x:v>
       </x:c>
       <x:c r="G7" s="37" t="str">
-        <x:v>随身滞后</x:v>
+        <x:v>较小反相滞后</x:v>
       </x:c>
       <x:c r="H7" s="37" t="str">
         <x:v>不显示</x:v>
       </x:c>
       <x:c r="I7" s="37" t="str">
-        <x:v>随身体左右镜像</x:v>
+        <x:v>与挂点同相移动</x:v>
       </x:c>
       <x:c r="J7" s="37" t="str">
-        <x:v>移动滞后</x:v>
+        <x:v>周期滞后</x:v>
       </x:c>
       <x:c r="K7" s="37" t="str">
         <x:v>地面划痕</x:v>
       </x:c>
       <x:c r="L7" s="37" t="str">
-        <x:v>2D/3D组件变换；整体表现根随准星转向</x:v>
+        <x:v>2D/3D组件变换；独立moving循环；整体根随准星；手与挂点局部关系固定</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -12228,6 +12286,44 @@
       </x:c>
       <x:c r="L14" s="37" t="str">
         <x:v>InvincibleTimer 唯一解除</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="34" customHeight="1">
+      <x:c r="A15" s="63" t="str">
+        <x:v>叠加</x:v>
+      </x:c>
+      <x:c r="B15" s="63" t="str">
+        <x:v>reloading</x:v>
+      </x:c>
+      <x:c r="C15" s="63" t="str">
+        <x:v>换弹</x:v>
+      </x:c>
+      <x:c r="D15" s="63" t="str">
+        <x:v>任意持枪存活态</x:v>
+      </x:c>
+      <x:c r="E15" s="63" t="str">
+        <x:v>不改变顶层；完成/取消退出</x:v>
+      </x:c>
+      <x:c r="F15" s="63" t="str">
+        <x:v>保持当前顶层</x:v>
+      </x:c>
+      <x:c r="G15" s="63" t="str">
+        <x:v>保持当前顶层</x:v>
+      </x:c>
+      <x:c r="H15" s="63" t="str">
+        <x:v>不显示</x:v>
+      </x:c>
+      <x:c r="I15" s="63" t="str">
+        <x:v>与weapon_socket同相下压/操作/回位</x:v>
+      </x:c>
+      <x:c r="J15" s="63" t="str">
+        <x:v>保持当前顶层</x:v>
+      </x:c>
+      <x:c r="K15" s="63" t="str">
+        <x:v>3D头顶billboard进度条；2D弹药栏</x:v>
+      </x:c>
+      <x:c r="L15" s="63" t="str">
+        <x:v>WeaponModel3D唯一计时源；0→1；换枪/补弹/清空/死亡取消</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="28" customHeight="1">
@@ -13547,6 +13643,24 @@
       <x:c r="G23" s="61"/>
       <x:c r="H23" s="61"/>
     </x:row>
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="73" t="str">
+        <x:v>换弹覆盖层：唯一手 + weapon_socket 同相三阶段动作；头顶 billboard 读取真实 0→1 进度；verify_3d_reload_state_flow.tscn PASS</x:v>
+      </x:c>
+      <x:c r="B24" s="73"/>
+      <x:c r="C24" s="73"/>
+      <x:c r="D24" s="73"/>
+      <x:c r="E24" s="73"/>
+      <x:c r="F24" s="73"/>
+      <x:c r="G24" s="73"/>
+      <x:c r="H24" s="73"/>
+      <x:c r="I24" s="73"/>
+      <x:c r="J24" s="73"/>
+      <x:c r="K24" s="73"/>
+      <x:c r="L24" s="73"/>
+      <x:c r="M24" s="73"/>
+      <x:c r="N24" s="73"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:N2"/>
@@ -13554,6 +13668,7 @@
     <x:mergeCell ref="A13:H13"/>
     <x:mergeCell ref="A21:H21"/>
     <x:mergeCell ref="A23:H23"/>
+    <x:mergeCell ref="A24:N24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -13810,6 +13925,75 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="14" ht="54" customHeight="1">
+      <x:c r="A14" s="63" t="str">
+        <x:v>v1.8</x:v>
+      </x:c>
+      <x:c r="B14" s="64" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="C14" s="63" t="str">
+        <x:v>360°逻辑视野契约修正</x:v>
+      </x:c>
+      <x:c r="D14" s="63" t="str">
+        <x:v>VFX-VISIBILITY-FIELD-3D / PlayerVision3D</x:v>
+      </x:c>
+      <x:c r="E14" s="63" t="str">
+        <x:v>目标显隐改为21m内360°物理遮挡；保留96°柔边目光场与探照灯表现。</x:v>
+      </x:c>
+      <x:c r="F14" s="63" t="str">
+        <x:v>AssetID和路径不变；只更新玩法角度契约、诊断字段与验收。</x:v>
+      </x:c>
+      <x:c r="G14" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="72" customHeight="1">
+      <x:c r="A15" s="70" t="str">
+        <x:v>v1.9</x:v>
+      </x:c>
+      <x:c r="B15" s="71" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="C15" s="70" t="str">
+        <x:v>3D战斗生命、AI与反馈闭环</x:v>
+      </x:c>
+      <x:c r="D15" s="70" t="str">
+        <x:v>Enemy3D / 玩家状态动画 / 三层灯组 / 钥匙与掉落</x:v>
+      </x:c>
+      <x:c r="E15" s="70" t="str">
+        <x:v>修复AI视线与3D HP倍率；moving独立动画；环境/角色灯分层；中央灯增强；拾取上弹旋转；钥匙近距生成、查重与补发</x:v>
+      </x:c>
+      <x:c r="F15" s="70" t="str">
+        <x:v>不新增AssetID或复制模型；更新既有根资产行为、哈希、状态职责与验收契约</x:v>
+      </x:c>
+      <x:c r="G15" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="72" customHeight="1">
+      <x:c r="A16" s="63" t="str">
+        <x:v>v1.10</x:v>
+      </x:c>
+      <x:c r="B16" s="64" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="C16" s="63" t="str">
+        <x:v>3D换弹覆盖状态登记</x:v>
+      </x:c>
+      <x:c r="D16" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D / WPN-GUN-KIT-3D / 玩家状态机</x:v>
+      </x:c>
+      <x:c r="E16" s="63" t="str">
+        <x:v>换弹成为可与移动并存的覆盖态；武器唯一计时驱动单手/枪同相动画和头顶billboard进度条；完成/补弹/换枪/死亡清理</x:v>
+      </x:c>
+      <x:c r="F16" s="63" t="str">
+        <x:v>不新增AssetID；六态白名单与56组合不变；复用既有角色根和枪械套件</x:v>
+      </x:c>
+      <x:c r="G16" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G2"/>

--- a/outputs/019f8417-e7f4-7bc3-aded-c62dfd1d1462/ShellStorm2_美术资产台账_v001.xlsx
+++ b/outputs/019f8417-e7f4-7bc3-aded-c62dfd1d1462/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf64f1312d80946d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rd986e361c39d4b34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rbb4561200bcd4f4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rf0b0c6022c314180"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R1e250af707284e99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rac42cf6b203a4968"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R5dfbe29cb13a4b58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R71dcffa382ea424f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8db6a911985d42be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R35b8b0bedd9b4554"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rc39ac0ba6b8d4f2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Re947ec0d70f2431b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R0d468249c12e48b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R07671a5e19124163"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R7cb7398f221e4b8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rb332978a099b43a4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="20">
+  <x:fonts count="23">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -138,8 +138,26 @@
       <x:color rgb="FF137333"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFD8F4FF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FFD8F4FF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FFE2F8FF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="23">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -189,6 +207,66 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE2F3E7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF163044"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234B63"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17384A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF163044"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234B63"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17384A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF163044"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234B63"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF24495D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF163044"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234B63"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF24495D"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -241,7 +319,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="74">
+  <x:cellXfs count="96">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -412,6 +490,44 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -775,13 +891,11 @@
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="45" t="n">
-        <x:f>COUNTA('资产主表'!$A$6:$A$200)</x:f>
-        <x:v>140</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B6" s="43"/>
       <x:c r="C6" s="45" t="n">
-        <x:f>COUNTIF('资产主表'!$K$6:$K$200,"已完成")+COUNTIF('资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>44</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D6" s="43"/>
       <x:c r="E6" s="45" t="n">
@@ -795,9 +909,11 @@
       </x:c>
       <x:c r="H6" s="43"/>
       <x:c r="I6" s="46" t="str">
-        <x:v>全3D闭环 / PH29 换弹覆盖态 / 真实头顶进度 / 单手枪同相</x:v>
-      </x:c>
-      <x:c r="J6" s="46"/>
+        <x:v>PH33 方形猫：头/身/单手/脚四模块；双眼双耳；圆短尾</x:v>
+      </x:c>
+      <x:c r="J6" s="46" t="str">
+        <x:v>基地 + 四主题副本 + 独立靶场 + 角色与遭遇预览场</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="43"/>
@@ -848,12 +964,10 @@
         <x:v>角色</x:v>
       </x:c>
       <x:c r="B10" s="50" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A10)</x:f>
-        <x:v>13</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" s="50" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A10,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A10,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D10" s="43"/>
       <x:c r="E10" s="51" t="str">
@@ -1329,7 +1443,7 @@
         <x:v>角色|player|player_capsule01|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S6" s="36" t="str">
-        <x:f>IF(A6="","",IF(COUNTIF($R$6:$R$145,R6)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A6="","",IF(COUNTIF($R$6:$R$155,R6)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T6" s="36" t="str"/>
@@ -1403,7 +1517,7 @@
         <x:v>角色|player_component|player_capsule01|head|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S7" s="37" t="str">
-        <x:f>IF(A7="","",IF(COUNTIF($R$6:$R$145,R7)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A7="","",IF(COUNTIF($R$6:$R$155,R7)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T7" s="37" t="str">
@@ -1479,7 +1593,7 @@
         <x:v>角色|player_component|player_capsule01|body|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S8" s="37" t="str">
-        <x:f>IF(A8="","",IF(COUNTIF($R$6:$R$145,R8)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A8="","",IF(COUNTIF($R$6:$R$155,R8)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T8" s="37" t="str">
@@ -1555,7 +1669,7 @@
         <x:v>角色|player_component|player_capsule01|hand_l_source|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S9" s="37" t="str">
-        <x:f>IF(A9="","",IF(COUNTIF($R$6:$R$145,R9)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A9="","",IF(COUNTIF($R$6:$R$155,R9)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T9" s="37" t="str">
@@ -1631,7 +1745,7 @@
         <x:v>角色|player_component|player_capsule01|hand|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S10" s="37" t="str">
-        <x:f>IF(A10="","",IF(COUNTIF($R$6:$R$145,R10)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A10="","",IF(COUNTIF($R$6:$R$155,R10)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T10" s="37" t="str">
@@ -1707,7 +1821,7 @@
         <x:v>角色|player_accessory|player_capsule01|scarf|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S11" s="37" t="str">
-        <x:f>IF(A11="","",IF(COUNTIF($R$6:$R$145,R11)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A11="","",IF(COUNTIF($R$6:$R$155,R11)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T11" s="37" t="str">
@@ -1783,7 +1897,7 @@
         <x:v>角色|review_board|player_capsule01|preview|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S12" s="37" t="str">
-        <x:f>IF(A12="","",IF(COUNTIF($R$6:$R$145,R12)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A12="","",IF(COUNTIF($R$6:$R$155,R12)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T12" s="37" t="str"/>
@@ -1851,7 +1965,7 @@
         <x:v>特效|player_state|player_dash|root|侧面朝右（可水平翻转）|dashing</x:v>
       </x:c>
       <x:c r="S13" s="37" t="str">
-        <x:f>IF(A13="","",IF(COUNTIF($R$6:$R$145,R13)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A13="","",IF(COUNTIF($R$6:$R$155,R13)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T13" s="37" t="str"/>
@@ -1919,7 +2033,7 @@
         <x:v>特效|player_state|player_hurt|root|侧面朝右（可水平翻转）|hurt</x:v>
       </x:c>
       <x:c r="S14" s="37" t="str">
-        <x:f>IF(A14="","",IF(COUNTIF($R$6:$R$145,R14)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A14="","",IF(COUNTIF($R$6:$R$155,R14)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T14" s="37" t="str"/>
@@ -1985,7 +2099,7 @@
         <x:v>特效|player_overlay|player_low_hp|root|侧面朝右（可水平翻转）|low_health</x:v>
       </x:c>
       <x:c r="S15" s="37" t="str">
-        <x:f>IF(A15="","",IF(COUNTIF($R$6:$R$145,R15)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A15="","",IF(COUNTIF($R$6:$R$155,R15)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T15" s="37" t="str"/>
@@ -2051,7 +2165,7 @@
         <x:v>特效|player_overlay|player_silenced|root|侧面朝右（可水平翻转）|silenced</x:v>
       </x:c>
       <x:c r="S16" s="37" t="str">
-        <x:f>IF(A16="","",IF(COUNTIF($R$6:$R$145,R16)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A16="","",IF(COUNTIF($R$6:$R$155,R16)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T16" s="37" t="str"/>
@@ -2119,7 +2233,7 @@
         <x:v>敌人|normal_melee|melee_chaser|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S17" s="37" t="str">
-        <x:f>IF(A17="","",IF(COUNTIF($R$6:$R$145,R17)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A17="","",IF(COUNTIF($R$6:$R$155,R17)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T17" s="37" t="str"/>
@@ -2189,7 +2303,7 @@
         <x:v>敌人|normal_ranged|ranged_caster|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S18" s="37" t="str">
-        <x:f>IF(A18="","",IF(COUNTIF($R$6:$R$145,R18)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A18="","",IF(COUNTIF($R$6:$R$155,R18)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T18" s="37" t="str"/>
@@ -2257,7 +2371,7 @@
         <x:v>敌人|normal_summoner|summoner|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S19" s="37" t="str">
-        <x:f>IF(A19="","",IF(COUNTIF($R$6:$R$145,R19)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A19="","",IF(COUNTIF($R$6:$R$155,R19)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T19" s="37" t="str"/>
@@ -2325,7 +2439,7 @@
         <x:v>敌人|normal_tank|shielded|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S20" s="37" t="str">
-        <x:f>IF(A20="","",IF(COUNTIF($R$6:$R$145,R20)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A20="","",IF(COUNTIF($R$6:$R$155,R20)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T20" s="37" t="str"/>
@@ -2393,7 +2507,7 @@
         <x:v>敌人|normal_bomber|exploder|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S21" s="37" t="str">
-        <x:f>IF(A21="","",IF(COUNTIF($R$6:$R$145,R21)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A21="","",IF(COUNTIF($R$6:$R$155,R21)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T21" s="37" t="str"/>
@@ -2461,7 +2575,7 @@
         <x:v>敌人|normal_ambusher|ambusher|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S22" s="37" t="str">
-        <x:f>IF(A22="","",IF(COUNTIF($R$6:$R$145,R22)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A22="","",IF(COUNTIF($R$6:$R$155,R22)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T22" s="37" t="str"/>
@@ -2529,7 +2643,7 @@
         <x:v>敌人|boss|boss|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S23" s="37" t="str">
-        <x:f>IF(A23="","",IF(COUNTIF($R$6:$R$145,R23)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A23="","",IF(COUNTIF($R$6:$R$155,R23)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T23" s="37" t="str"/>
@@ -2599,7 +2713,7 @@
         <x:v>枪械|gunbody|bp_pistol|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S24" s="37" t="str">
-        <x:f>IF(A24="","",IF(COUNTIF($R$6:$R$145,R24)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A24="","",IF(COUNTIF($R$6:$R$155,R24)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T24" s="37" t="str"/>
@@ -2669,7 +2783,7 @@
         <x:v>枪械|gunbody|bp_shotgun|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S25" s="37" t="str">
-        <x:f>IF(A25="","",IF(COUNTIF($R$6:$R$145,R25)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A25="","",IF(COUNTIF($R$6:$R$155,R25)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T25" s="37" t="str"/>
@@ -2739,7 +2853,7 @@
         <x:v>枪械|gunbody|bp_rifle|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S26" s="37" t="str">
-        <x:f>IF(A26="","",IF(COUNTIF($R$6:$R$145,R26)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A26="","",IF(COUNTIF($R$6:$R$155,R26)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T26" s="37" t="str"/>
@@ -2809,7 +2923,7 @@
         <x:v>枪械|gunbody|bp_machinegun|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S27" s="37" t="str">
-        <x:f>IF(A27="","",IF(COUNTIF($R$6:$R$145,R27)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A27="","",IF(COUNTIF($R$6:$R$155,R27)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T27" s="37" t="str"/>
@@ -2879,7 +2993,7 @@
         <x:v>枪械|gunbody|bp_sniper|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S28" s="37" t="str">
-        <x:f>IF(A28="","",IF(COUNTIF($R$6:$R$145,R28)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A28="","",IF(COUNTIF($R$6:$R$155,R28)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T28" s="37" t="str"/>
@@ -2949,7 +3063,7 @@
         <x:v>枪械|gunbody|bp_launcher|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S29" s="37" t="str">
-        <x:f>IF(A29="","",IF(COUNTIF($R$6:$R$145,R29)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A29="","",IF(COUNTIF($R$6:$R$155,R29)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T29" s="37" t="str"/>
@@ -3019,7 +3133,7 @@
         <x:v>枪械|gunbody|bp_charge|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S30" s="37" t="str">
-        <x:f>IF(A30="","",IF(COUNTIF($R$6:$R$145,R30)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A30="","",IF(COUNTIF($R$6:$R$155,R30)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T30" s="37" t="str"/>
@@ -3087,7 +3201,7 @@
         <x:v>枪械|bullet_module|mod_bullet_standard|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S31" s="37" t="str">
-        <x:f>IF(A31="","",IF(COUNTIF($R$6:$R$145,R31)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A31="","",IF(COUNTIF($R$6:$R$155,R31)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T31" s="37" t="str"/>
@@ -3155,7 +3269,7 @@
         <x:v>枪械|bullet_module|mod_bullet_sticky|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S32" s="37" t="str">
-        <x:f>IF(A32="","",IF(COUNTIF($R$6:$R$145,R32)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A32="","",IF(COUNTIF($R$6:$R$155,R32)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T32" s="37" t="str"/>
@@ -3223,7 +3337,7 @@
         <x:v>枪械|bullet_module|mod_bullet_bounce|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S33" s="37" t="str">
-        <x:f>IF(A33="","",IF(COUNTIF($R$6:$R$145,R33)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A33="","",IF(COUNTIF($R$6:$R$155,R33)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T33" s="37" t="str"/>
@@ -3291,7 +3405,7 @@
         <x:v>枪械|bullet_module|mod_bullet_piercing|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S34" s="37" t="str">
-        <x:f>IF(A34="","",IF(COUNTIF($R$6:$R$145,R34)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A34="","",IF(COUNTIF($R$6:$R$155,R34)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T34" s="37" t="str"/>
@@ -3359,7 +3473,7 @@
         <x:v>枪械|bullet_module|mod_bullet_explosive|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S35" s="37" t="str">
-        <x:f>IF(A35="","",IF(COUNTIF($R$6:$R$145,R35)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A35="","",IF(COUNTIF($R$6:$R$155,R35)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T35" s="37" t="str"/>
@@ -3427,7 +3541,7 @@
         <x:v>枪械|bullet_module|mod_bullet_homing|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S36" s="37" t="str">
-        <x:f>IF(A36="","",IF(COUNTIF($R$6:$R$145,R36)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A36="","",IF(COUNTIF($R$6:$R$155,R36)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T36" s="37" t="str"/>
@@ -3495,7 +3609,7 @@
         <x:v>枪械|bullet_module|mod_bullet_blackhole|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S37" s="37" t="str">
-        <x:f>IF(A37="","",IF(COUNTIF($R$6:$R$145,R37)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A37="","",IF(COUNTIF($R$6:$R$155,R37)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T37" s="37" t="str"/>
@@ -3563,7 +3677,7 @@
         <x:v>枪械|bullet_module|mod_bullet_balloon|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S38" s="37" t="str">
-        <x:f>IF(A38="","",IF(COUNTIF($R$6:$R$145,R38)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A38="","",IF(COUNTIF($R$6:$R$155,R38)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T38" s="37" t="str"/>
@@ -3631,7 +3745,7 @@
         <x:v>枪械|attachment|attach_triple_muzzle|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S39" s="37" t="str">
-        <x:f>IF(A39="","",IF(COUNTIF($R$6:$R$145,R39)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A39="","",IF(COUNTIF($R$6:$R$155,R39)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T39" s="37" t="str"/>
@@ -3699,7 +3813,7 @@
         <x:v>枪械|attachment|attach_rubber_stock|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S40" s="37" t="str">
-        <x:f>IF(A40="","",IF(COUNTIF($R$6:$R$145,R40)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A40="","",IF(COUNTIF($R$6:$R$155,R40)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T40" s="37" t="str"/>
@@ -3767,7 +3881,7 @@
         <x:v>枪械|attachment|attach_scope|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S41" s="37" t="str">
-        <x:f>IF(A41="","",IF(COUNTIF($R$6:$R$145,R41)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A41="","",IF(COUNTIF($R$6:$R$155,R41)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T41" s="37" t="str"/>
@@ -3835,7 +3949,7 @@
         <x:v>枪械|attachment|attach_big_mag|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S42" s="37" t="str">
-        <x:f>IF(A42="","",IF(COUNTIF($R$6:$R$145,R42)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A42="","",IF(COUNTIF($R$6:$R$155,R42)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T42" s="37" t="str"/>
@@ -3903,7 +4017,7 @@
         <x:v>枪械|attachment|attach_fan|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S43" s="37" t="str">
-        <x:f>IF(A43="","",IF(COUNTIF($R$6:$R$145,R43)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A43="","",IF(COUNTIF($R$6:$R$155,R43)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T43" s="37" t="str"/>
@@ -3971,7 +4085,7 @@
         <x:v>枪械|attachment|attach_copy_sticker|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S44" s="37" t="str">
-        <x:f>IF(A44="","",IF(COUNTIF($R$6:$R$145,R44)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A44="","",IF(COUNTIF($R$6:$R$155,R44)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T44" s="37" t="str"/>
@@ -4039,7 +4153,7 @@
         <x:v>道具|consumable|item_beacon|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S45" s="37" t="str">
-        <x:f>IF(A45="","",IF(COUNTIF($R$6:$R$145,R45)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A45="","",IF(COUNTIF($R$6:$R$155,R45)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T45" s="37" t="str"/>
@@ -4105,7 +4219,7 @@
         <x:v>道具|key|item_room_key|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S46" s="37" t="str">
-        <x:f>IF(A46="","",IF(COUNTIF($R$6:$R$145,R46)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A46="","",IF(COUNTIF($R$6:$R$155,R46)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T46" s="37" t="str"/>
@@ -4171,7 +4285,7 @@
         <x:v>道具|pickup|soul_orb|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S47" s="37" t="str">
-        <x:f>IF(A47="","",IF(COUNTIF($R$6:$R$145,R47)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A47="","",IF(COUNTIF($R$6:$R$155,R47)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T47" s="37" t="str"/>
@@ -4237,7 +4351,7 @@
         <x:v>道具|container|container|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S48" s="37" t="str">
-        <x:f>IF(A48="","",IF(COUNTIF($R$6:$R$145,R48)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A48="","",IF(COUNTIF($R$6:$R$155,R48)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T48" s="37" t="str"/>
@@ -4303,7 +4417,7 @@
         <x:v>道具|pickup|room_key_pickup|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S49" s="37" t="str">
-        <x:f>IF(A49="","",IF(COUNTIF($R$6:$R$145,R49)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A49="","",IF(COUNTIF($R$6:$R$155,R49)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T49" s="37" t="str"/>
@@ -4371,7 +4485,7 @@
         <x:v>道具|pickup_base|ground_item|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S50" s="37" t="str">
-        <x:f>IF(A50="","",IF(COUNTIF($R$6:$R$145,R50)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A50="","",IF(COUNTIF($R$6:$R$155,R50)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T50" s="37" t="str"/>
@@ -4439,7 +4553,7 @@
         <x:v>场景|biome_kit|base_world|root|顶视|default</x:v>
       </x:c>
       <x:c r="S51" s="37" t="str">
-        <x:f>IF(A51="","",IF(COUNTIF($R$6:$R$145,R51)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A51="","",IF(COUNTIF($R$6:$R$155,R51)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T51" s="37" t="str"/>
@@ -4507,7 +4621,7 @@
         <x:v>场景|biome_kit|iron_frontier|root|顶视|default</x:v>
       </x:c>
       <x:c r="S52" s="37" t="str">
-        <x:f>IF(A52="","",IF(COUNTIF($R$6:$R$145,R52)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A52="","",IF(COUNTIF($R$6:$R$155,R52)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T52" s="37" t="str"/>
@@ -4575,7 +4689,7 @@
         <x:v>场景|biome_kit|rust_foundry|root|顶视|default</x:v>
       </x:c>
       <x:c r="S53" s="37" t="str">
-        <x:f>IF(A53="","",IF(COUNTIF($R$6:$R$145,R53)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A53="","",IF(COUNTIF($R$6:$R$155,R53)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T53" s="37" t="str"/>
@@ -4643,7 +4757,7 @@
         <x:v>场景|biome_kit|spore_depths|root|顶视|default</x:v>
       </x:c>
       <x:c r="S54" s="37" t="str">
-        <x:f>IF(A54="","",IF(COUNTIF($R$6:$R$145,R54)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A54="","",IF(COUNTIF($R$6:$R$155,R54)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T54" s="37" t="str"/>
@@ -4711,7 +4825,7 @@
         <x:v>场景|biome_kit|abyss_archive|root|顶视|default</x:v>
       </x:c>
       <x:c r="S55" s="37" t="str">
-        <x:f>IF(A55="","",IF(COUNTIF($R$6:$R$145,R55)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A55="","",IF(COUNTIF($R$6:$R$155,R55)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T55" s="37" t="str"/>
@@ -4779,7 +4893,7 @@
         <x:v>场景|biome_kit|training_range|root|顶视|default</x:v>
       </x:c>
       <x:c r="S56" s="37" t="str">
-        <x:f>IF(A56="","",IF(COUNTIF($R$6:$R$145,R56)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A56="","",IF(COUNTIF($R$6:$R$155,R56)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T56" s="37" t="str"/>
@@ -4847,7 +4961,7 @@
         <x:v>场景|room_dressing|room_combat|root|顶视|default</x:v>
       </x:c>
       <x:c r="S57" s="37" t="str">
-        <x:f>IF(A57="","",IF(COUNTIF($R$6:$R$145,R57)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A57="","",IF(COUNTIF($R$6:$R$155,R57)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T57" s="37" t="str"/>
@@ -4915,7 +5029,7 @@
         <x:v>场景|room_dressing|room_elite|root|顶视|default</x:v>
       </x:c>
       <x:c r="S58" s="37" t="str">
-        <x:f>IF(A58="","",IF(COUNTIF($R$6:$R$145,R58)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A58="","",IF(COUNTIF($R$6:$R$155,R58)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T58" s="37" t="str"/>
@@ -4983,7 +5097,7 @@
         <x:v>场景|room_dressing|room_boss|root|顶视|default</x:v>
       </x:c>
       <x:c r="S59" s="37" t="str">
-        <x:f>IF(A59="","",IF(COUNTIF($R$6:$R$145,R59)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A59="","",IF(COUNTIF($R$6:$R$155,R59)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T59" s="37" t="str"/>
@@ -5051,7 +5165,7 @@
         <x:v>场景|room_dressing|room_event|root|顶视|default</x:v>
       </x:c>
       <x:c r="S60" s="37" t="str">
-        <x:f>IF(A60="","",IF(COUNTIF($R$6:$R$145,R60)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A60="","",IF(COUNTIF($R$6:$R$155,R60)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T60" s="37" t="str"/>
@@ -5119,7 +5233,7 @@
         <x:v>场景|room_dressing|room_extraction|root|顶视|default</x:v>
       </x:c>
       <x:c r="S61" s="37" t="str">
-        <x:f>IF(A61="","",IF(COUNTIF($R$6:$R$145,R61)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A61="","",IF(COUNTIF($R$6:$R$155,R61)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T61" s="37" t="str"/>
@@ -5187,7 +5301,7 @@
         <x:v>场景|room_dressing|room_merchant|root|顶视|default</x:v>
       </x:c>
       <x:c r="S62" s="37" t="str">
-        <x:f>IF(A62="","",IF(COUNTIF($R$6:$R$145,R62)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A62="","",IF(COUNTIF($R$6:$R$155,R62)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T62" s="37" t="str"/>
@@ -5255,7 +5369,7 @@
         <x:v>场景|room_dressing|room_scavenge|root|顶视|default</x:v>
       </x:c>
       <x:c r="S63" s="37" t="str">
-        <x:f>IF(A63="","",IF(COUNTIF($R$6:$R$145,R63)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A63="","",IF(COUNTIF($R$6:$R$155,R63)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T63" s="37" t="str"/>
@@ -5323,7 +5437,7 @@
         <x:v>场景|room_dressing|room_storage|root|顶视|default</x:v>
       </x:c>
       <x:c r="S64" s="37" t="str">
-        <x:f>IF(A64="","",IF(COUNTIF($R$6:$R$145,R64)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A64="","",IF(COUNTIF($R$6:$R$155,R64)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T64" s="37" t="str"/>
@@ -5391,7 +5505,7 @@
         <x:v>场景|room_dressing|room_trap|root|顶视|default</x:v>
       </x:c>
       <x:c r="S65" s="37" t="str">
-        <x:f>IF(A65="","",IF(COUNTIF($R$6:$R$145,R65)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A65="","",IF(COUNTIF($R$6:$R$155,R65)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T65" s="37" t="str"/>
@@ -5459,7 +5573,7 @@
         <x:v>场景|room_dressing|room_upgrade|root|顶视|default</x:v>
       </x:c>
       <x:c r="S66" s="37" t="str">
-        <x:f>IF(A66="","",IF(COUNTIF($R$6:$R$145,R66)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A66="","",IF(COUNTIF($R$6:$R$155,R66)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T66" s="37" t="str"/>
@@ -5527,7 +5641,7 @@
         <x:v>场景|room_dressing|room_spawn|root|顶视|default</x:v>
       </x:c>
       <x:c r="S67" s="37" t="str">
-        <x:f>IF(A67="","",IF(COUNTIF($R$6:$R$145,R67)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A67="","",IF(COUNTIF($R$6:$R$155,R67)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T67" s="37" t="str"/>
@@ -5595,7 +5709,7 @@
         <x:v>场景|room_dressing|room_stairs|root|顶视|default</x:v>
       </x:c>
       <x:c r="S68" s="37" t="str">
-        <x:f>IF(A68="","",IF(COUNTIF($R$6:$R$145,R68)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A68="","",IF(COUNTIF($R$6:$R$155,R68)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T68" s="37" t="str"/>
@@ -5663,7 +5777,7 @@
         <x:v>场景道具|facility|base_briefing|root|顶视|default</x:v>
       </x:c>
       <x:c r="S69" s="37" t="str">
-        <x:f>IF(A69="","",IF(COUNTIF($R$6:$R$145,R69)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A69="","",IF(COUNTIF($R$6:$R$155,R69)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T69" s="37" t="str"/>
@@ -5731,7 +5845,7 @@
         <x:v>场景道具|facility|base_workshop|root|顶视|default</x:v>
       </x:c>
       <x:c r="S70" s="37" t="str">
-        <x:f>IF(A70="","",IF(COUNTIF($R$6:$R$145,R70)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A70="","",IF(COUNTIF($R$6:$R$155,R70)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T70" s="37" t="str"/>
@@ -5799,7 +5913,7 @@
         <x:v>场景道具|facility|base_divination|root|顶视|default</x:v>
       </x:c>
       <x:c r="S71" s="37" t="str">
-        <x:f>IF(A71="","",IF(COUNTIF($R$6:$R$145,R71)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A71="","",IF(COUNTIF($R$6:$R$155,R71)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T71" s="37" t="str"/>
@@ -5867,7 +5981,7 @@
         <x:v>场景道具|facility|base_vault|root|顶视|default</x:v>
       </x:c>
       <x:c r="S72" s="37" t="str">
-        <x:f>IF(A72="","",IF(COUNTIF($R$6:$R$145,R72)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A72="","",IF(COUNTIF($R$6:$R$155,R72)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T72" s="37" t="str"/>
@@ -5935,7 +6049,7 @@
         <x:v>场景道具|facility|base_monster_archive|root|顶视|default</x:v>
       </x:c>
       <x:c r="S73" s="37" t="str">
-        <x:f>IF(A73="","",IF(COUNTIF($R$6:$R$145,R73)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A73="","",IF(COUNTIF($R$6:$R$155,R73)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T73" s="37" t="str"/>
@@ -6003,7 +6117,7 @@
         <x:v>场景道具|facility|base_card_collection|root|顶视|default</x:v>
       </x:c>
       <x:c r="S74" s="37" t="str">
-        <x:f>IF(A74="","",IF(COUNTIF($R$6:$R$145,R74)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A74="","",IF(COUNTIF($R$6:$R$155,R74)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T74" s="37" t="str"/>
@@ -6071,7 +6185,7 @@
         <x:v>场景道具|facility|base_terminal|root|顶视|default</x:v>
       </x:c>
       <x:c r="S75" s="37" t="str">
-        <x:f>IF(A75="","",IF(COUNTIF($R$6:$R$145,R75)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A75="","",IF(COUNTIF($R$6:$R$155,R75)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T75" s="37" t="str"/>
@@ -6139,7 +6253,7 @@
         <x:v>场景道具|facility|dungeon_gate|root|顶视|default</x:v>
       </x:c>
       <x:c r="S76" s="37" t="str">
-        <x:f>IF(A76="","",IF(COUNTIF($R$6:$R$145,R76)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A76="","",IF(COUNTIF($R$6:$R$155,R76)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T76" s="37" t="str"/>
@@ -6207,7 +6321,7 @@
         <x:v>场景道具|facility|workbench|root|顶视|default</x:v>
       </x:c>
       <x:c r="S77" s="37" t="str">
-        <x:f>IF(A77="","",IF(COUNTIF($R$6:$R$145,R77)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A77="","",IF(COUNTIF($R$6:$R$155,R77)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T77" s="37" t="str"/>
@@ -6275,7 +6389,7 @@
         <x:v>场景道具|facility|door|root|顶视|default</x:v>
       </x:c>
       <x:c r="S78" s="37" t="str">
-        <x:f>IF(A78="","",IF(COUNTIF($R$6:$R$145,R78)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A78="","",IF(COUNTIF($R$6:$R$155,R78)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T78" s="37" t="str"/>
@@ -6343,7 +6457,7 @@
         <x:v>ui|screen|hud|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S79" s="37" t="str">
-        <x:f>IF(A79="","",IF(COUNTIF($R$6:$R$145,R79)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A79="","",IF(COUNTIF($R$6:$R$155,R79)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T79" s="37" t="str"/>
@@ -6411,7 +6525,7 @@
         <x:v>ui|screen|inventory|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S80" s="37" t="str">
-        <x:f>IF(A80="","",IF(COUNTIF($R$6:$R$145,R80)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A80="","",IF(COUNTIF($R$6:$R$155,R80)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T80" s="37" t="str"/>
@@ -6479,7 +6593,7 @@
         <x:v>ui|screen|merchant|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S81" s="37" t="str">
-        <x:f>IF(A81="","",IF(COUNTIF($R$6:$R$145,R81)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A81="","",IF(COUNTIF($R$6:$R$155,R81)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T81" s="37" t="str"/>
@@ -6547,7 +6661,7 @@
         <x:v>ui|screen|workshop|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S82" s="37" t="str">
-        <x:f>IF(A82="","",IF(COUNTIF($R$6:$R$145,R82)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A82="","",IF(COUNTIF($R$6:$R$155,R82)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T82" s="37" t="str"/>
@@ -6615,7 +6729,7 @@
         <x:v>ui|screen|workbench|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S83" s="37" t="str">
-        <x:f>IF(A83="","",IF(COUNTIF($R$6:$R$145,R83)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A83="","",IF(COUNTIF($R$6:$R$155,R83)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T83" s="37" t="str"/>
@@ -6683,7 +6797,7 @@
         <x:v>ui|screen|weapon_tree|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S84" s="37" t="str">
-        <x:f>IF(A84="","",IF(COUNTIF($R$6:$R$145,R84)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A84="","",IF(COUNTIF($R$6:$R$155,R84)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T84" s="37" t="str"/>
@@ -6751,7 +6865,7 @@
         <x:v>ui|screen|fate_select|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S85" s="37" t="str">
-        <x:f>IF(A85="","",IF(COUNTIF($R$6:$R$145,R85)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A85="","",IF(COUNTIF($R$6:$R$155,R85)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T85" s="37" t="str"/>
@@ -6819,7 +6933,7 @@
         <x:v>ui|screen|fate_collection|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S86" s="37" t="str">
-        <x:f>IF(A86="","",IF(COUNTIF($R$6:$R$145,R86)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A86="","",IF(COUNTIF($R$6:$R$155,R86)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T86" s="37" t="str"/>
@@ -6887,7 +7001,7 @@
         <x:v>ui|screen|level_select|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S87" s="37" t="str">
-        <x:f>IF(A87="","",IF(COUNTIF($R$6:$R$145,R87)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A87="","",IF(COUNTIF($R$6:$R$155,R87)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T87" s="37" t="str"/>
@@ -6955,7 +7069,7 @@
         <x:v>ui|screen|vault|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S88" s="37" t="str">
-        <x:f>IF(A88="","",IF(COUNTIF($R$6:$R$145,R88)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A88="","",IF(COUNTIF($R$6:$R$155,R88)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T88" s="37" t="str"/>
@@ -7023,7 +7137,7 @@
         <x:v>ui|screen|monster_archive|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S89" s="37" t="str">
-        <x:f>IF(A89="","",IF(COUNTIF($R$6:$R$145,R89)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A89="","",IF(COUNTIF($R$6:$R$155,R89)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T89" s="37" t="str"/>
@@ -7091,7 +7205,7 @@
         <x:v>ui|screen|base_menu|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S90" s="37" t="str">
-        <x:f>IF(A90="","",IF(COUNTIF($R$6:$R$145,R90)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A90="","",IF(COUNTIF($R$6:$R$155,R90)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T90" s="37" t="str"/>
@@ -7159,7 +7273,7 @@
         <x:v>ui|screen|mobile_controls|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S91" s="37" t="str">
-        <x:f>IF(A91="","",IF(COUNTIF($R$6:$R$145,R91)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A91="","",IF(COUNTIF($R$6:$R$155,R91)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T91" s="37" t="str"/>
@@ -7227,7 +7341,7 @@
         <x:v>特效|gameplay_vfx|explosion|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S92" s="37" t="str">
-        <x:f>IF(A92="","",IF(COUNTIF($R$6:$R$145,R92)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A92="","",IF(COUNTIF($R$6:$R$155,R92)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T92" s="37" t="str"/>
@@ -7295,7 +7409,7 @@
         <x:v>特效|gameplay_vfx|muzzle_flash|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S93" s="37" t="str">
-        <x:f>IF(A93="","",IF(COUNTIF($R$6:$R$145,R93)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A93="","",IF(COUNTIF($R$6:$R$155,R93)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T93" s="37" t="str"/>
@@ -7363,7 +7477,7 @@
         <x:v>特效|gameplay_vfx|damage_number|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S94" s="37" t="str">
-        <x:f>IF(A94="","",IF(COUNTIF($R$6:$R$145,R94)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A94="","",IF(COUNTIF($R$6:$R$155,R94)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T94" s="37" t="str"/>
@@ -7431,7 +7545,7 @@
         <x:v>特效|gameplay_vfx|spark|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S95" s="37" t="str">
-        <x:f>IF(A95="","",IF(COUNTIF($R$6:$R$145,R95)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A95="","",IF(COUNTIF($R$6:$R$155,R95)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T95" s="37" t="str"/>
@@ -7499,7 +7613,7 @@
         <x:v>特效|gameplay_vfx|room_transition|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S96" s="37" t="str">
-        <x:f>IF(A96="","",IF(COUNTIF($R$6:$R$145,R96)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A96="","",IF(COUNTIF($R$6:$R$155,R96)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T96" s="37" t="str"/>
@@ -7569,7 +7683,7 @@
         <x:v>特效|gameplay_vfx|health_vignette|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S97" s="37" t="str">
-        <x:f>IF(A97="","",IF(COUNTIF($R$6:$R$145,R97)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A97="","",IF(COUNTIF($R$6:$R$155,R97)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T97" s="37" t="str"/>
@@ -7637,7 +7751,7 @@
         <x:v>特效|gameplay_vfx|visibility_light|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S98" s="37" t="str">
-        <x:f>IF(A98="","",IF(COUNTIF($R$6:$R$145,R98)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A98="","",IF(COUNTIF($R$6:$R$155,R98)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T98" s="37" t="str"/>
@@ -7705,7 +7819,7 @@
         <x:v>特效|gameplay_vfx|extraction_beacon|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S99" s="37" t="str">
-        <x:f>IF(A99="","",IF(COUNTIF($R$6:$R$145,R99)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A99="","",IF(COUNTIF($R$6:$R$155,R99)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T99" s="37" t="str"/>
@@ -7773,7 +7887,7 @@
         <x:v>音频|bgm|bgm_wasteland|root|不适用|default</x:v>
       </x:c>
       <x:c r="S100" s="37" t="str">
-        <x:f>IF(A100="","",IF(COUNTIF($R$6:$R$145,R100)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A100="","",IF(COUNTIF($R$6:$R$155,R100)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T100" s="37" t="str"/>
@@ -7839,7 +7953,7 @@
         <x:v>音频|sfx|pistol_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S101" s="37" t="str">
-        <x:f>IF(A101="","",IF(COUNTIF($R$6:$R$145,R101)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A101="","",IF(COUNTIF($R$6:$R$155,R101)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T101" s="37" t="str"/>
@@ -7905,7 +8019,7 @@
         <x:v>音频|sfx|rifle_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S102" s="37" t="str">
-        <x:f>IF(A102="","",IF(COUNTIF($R$6:$R$145,R102)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A102="","",IF(COUNTIF($R$6:$R$155,R102)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T102" s="37" t="str"/>
@@ -7971,7 +8085,7 @@
         <x:v>音频|sfx|shotgun_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S103" s="37" t="str">
-        <x:f>IF(A103="","",IF(COUNTIF($R$6:$R$145,R103)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A103="","",IF(COUNTIF($R$6:$R$155,R103)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T103" s="37" t="str"/>
@@ -8037,7 +8151,7 @@
         <x:v>音频|sfx|smg_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S104" s="37" t="str">
-        <x:f>IF(A104="","",IF(COUNTIF($R$6:$R$145,R104)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A104="","",IF(COUNTIF($R$6:$R$155,R104)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T104" s="37" t="str"/>
@@ -8103,7 +8217,7 @@
         <x:v>音频|sfx|sniper_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S105" s="37" t="str">
-        <x:f>IF(A105="","",IF(COUNTIF($R$6:$R$145,R105)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A105="","",IF(COUNTIF($R$6:$R$155,R105)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T105" s="37" t="str"/>
@@ -8169,7 +8283,7 @@
         <x:v>音频|sfx|player_hit|root|不适用|default</x:v>
       </x:c>
       <x:c r="S106" s="37" t="str">
-        <x:f>IF(A106="","",IF(COUNTIF($R$6:$R$145,R106)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A106="","",IF(COUNTIF($R$6:$R$155,R106)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T106" s="37" t="str"/>
@@ -8235,7 +8349,7 @@
         <x:v>音频|sfx|player_dash|root|不适用|default</x:v>
       </x:c>
       <x:c r="S107" s="37" t="str">
-        <x:f>IF(A107="","",IF(COUNTIF($R$6:$R$145,R107)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A107="","",IF(COUNTIF($R$6:$R$155,R107)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T107" s="37" t="str"/>
@@ -8301,7 +8415,7 @@
         <x:v>音频|sfx|enemy_hit|root|不适用|default</x:v>
       </x:c>
       <x:c r="S108" s="37" t="str">
-        <x:f>IF(A108="","",IF(COUNTIF($R$6:$R$145,R108)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A108="","",IF(COUNTIF($R$6:$R$155,R108)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T108" s="37" t="str"/>
@@ -8367,7 +8481,7 @@
         <x:v>音频|sfx|enemy_die|root|不适用|default</x:v>
       </x:c>
       <x:c r="S109" s="37" t="str">
-        <x:f>IF(A109="","",IF(COUNTIF($R$6:$R$145,R109)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A109="","",IF(COUNTIF($R$6:$R$155,R109)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T109" s="37" t="str"/>
@@ -8433,7 +8547,7 @@
         <x:v>音频|sfx|reload|root|不适用|default</x:v>
       </x:c>
       <x:c r="S110" s="37" t="str">
-        <x:f>IF(A110="","",IF(COUNTIF($R$6:$R$145,R110)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A110="","",IF(COUNTIF($R$6:$R$155,R110)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T110" s="37" t="str"/>
@@ -8499,7 +8613,7 @@
         <x:v>音频|sfx|extraction_start|root|不适用|default</x:v>
       </x:c>
       <x:c r="S111" s="37" t="str">
-        <x:f>IF(A111="","",IF(COUNTIF($R$6:$R$145,R111)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A111="","",IF(COUNTIF($R$6:$R$155,R111)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T111" s="37" t="str"/>
@@ -8565,7 +8679,7 @@
         <x:v>音频|sfx|extraction_done|root|不适用|default</x:v>
       </x:c>
       <x:c r="S112" s="37" t="str">
-        <x:f>IF(A112="","",IF(COUNTIF($R$6:$R$145,R112)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A112="","",IF(COUNTIF($R$6:$R$155,R112)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T112" s="37" t="str"/>
@@ -8585,7 +8699,7 @@
         <x:v>CHR-PLY-CAPSULE01-3D</x:v>
       </x:c>
       <x:c r="B113" t="str">
-        <x:v>胶囊防护体3D根组件</x:v>
+        <x:v>方形猫角色3D根组件</x:v>
       </x:c>
       <x:c r="C113" t="str">
         <x:v>角色</x:v>
@@ -8637,23 +8751,23 @@
         <x:v>角色|player|player_capsule01|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S113" t="str">
-        <x:f>IF(A113="","",IF(COUNTIF($R$6:$R$145,R113)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A113="","",IF(COUNTIF($R$6:$R$155,R113)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T113" t="str">
-        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
       </x:c>
       <x:c r="U113" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V113" s="62" t="n">
-        <x:v>46225</x:v>
+      <x:c r="V113" s="62" t="str">
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="W113" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
-      <x:c r="X113" t="str">
-        <x:v>2D逻辑资产的3D表现变体；六态白名单正常；moving使用位移驱动独立组件循环；角色网格使用render layer 2；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
+      <x:c r="X113" s="63" t="str">
+        <x:v>VisualRoot四主模块；方头/方身/方手/方脚；双眼双耳；圆短尾；六态与动作覆盖保持；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -8661,7 +8775,7 @@
         <x:v>CHR-PLY-CAPSULE01-BODY-3D</x:v>
       </x:c>
       <x:c r="B114" t="str">
-        <x:v>胶囊防护体3D身躯</x:v>
+        <x:v>方形猫角色3D身躯</x:v>
       </x:c>
       <x:c r="C114" t="str">
         <x:v>角色</x:v>
@@ -8713,23 +8827,23 @@
         <x:v>角色|player|player_capsule01|body_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S114" t="str">
-        <x:f>IF(A114="","",IF(COUNTIF($R$6:$R$145,R114)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A114="","",IF(COUNTIF($R$6:$R$155,R114)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T114" t="str">
-        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
       </x:c>
       <x:c r="U114" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V114" s="62" t="n">
-        <x:v>46225</x:v>
+      <x:c r="V114" s="62" t="str">
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="W114" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X114" t="str">
-        <x:v>PackedScene内独立Body节点；moving执行0.10m弹跳与压缩回弹；后续可替换GLB；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
+        <x:v>VisualRoot/Body：BoxMesh身躯、BellyPatch、圆形TailStub；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -8737,7 +8851,7 @@
         <x:v>CHR-PLY-CAPSULE01-HEAD-3D</x:v>
       </x:c>
       <x:c r="B115" t="str">
-        <x:v>胶囊防护体3D头壳</x:v>
+        <x:v>方形猫角色3D头部</x:v>
       </x:c>
       <x:c r="C115" t="str">
         <x:v>角色</x:v>
@@ -8789,23 +8903,23 @@
         <x:v>角色|player|player_capsule01|head_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S115" t="str">
-        <x:f>IF(A115="","",IF(COUNTIF($R$6:$R$145,R115)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A115="","",IF(COUNTIF($R$6:$R$155,R115)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T115" t="str">
-        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
       </x:c>
       <x:c r="U115" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V115" s="62" t="n">
-        <x:v>46225</x:v>
+      <x:c r="V115" s="62" t="str">
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="W115" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X115" t="str">
-        <x:v>PackedScene内独立Head节点；无人脸；移动时采用小幅反相滞后，避免与身体刚性粘连；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
+        <x:v>VisualRoot/Head：BoxMesh方头；Eyes双矩形眼；Ears双三角耳；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -8813,7 +8927,7 @@
         <x:v>CHR-PLY-CAPSULE01-HAND-3D</x:v>
       </x:c>
       <x:c r="B116" t="str">
-        <x:v>胶囊防护体3D唯一手部</x:v>
+        <x:v>方形猫角色3D唯一手部</x:v>
       </x:c>
       <x:c r="C116" t="str">
         <x:v>角色</x:v>
@@ -8865,23 +8979,23 @@
         <x:v>角色|player|player_capsule01|hand_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S116" t="str">
-        <x:f>IF(A116="","",IF(COUNTIF($R$6:$R$145,R116)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A116="","",IF(COUNTIF($R$6:$R$155,R116)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T116" t="str">
-        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
       </x:c>
       <x:c r="U116" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V116" s="62" t="n">
-        <x:v>46225</x:v>
+      <x:c r="V116" s="62" t="str">
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="W116" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X116" t="str">
-        <x:v>唯一可见手；随VisualRoot转向；与weapon_socket使用完全相同的移动偏移，局部关系不变；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
+        <x:v>VisualRoot/Hand：单个BoxMesh悬浮握持手；全动作与weapon_socket同相；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -8889,7 +9003,7 @@
         <x:v>CHR-PLY-CAPSULE01-SCARF-3D</x:v>
       </x:c>
       <x:c r="B117" t="str">
-        <x:v>胶囊防护体3D红围巾</x:v>
+        <x:v>旧3D红围巾兼容节点</x:v>
       </x:c>
       <x:c r="C117" t="str">
         <x:v>角色</x:v>
@@ -8941,23 +9055,23 @@
         <x:v>角色|player|player_capsule01|scarf_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S117" t="str">
-        <x:f>IF(A117="","",IF(COUNTIF($R$6:$R$145,R117)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A117="","",IF(COUNTIF($R$6:$R$155,R117)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T117" t="str">
-        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
       </x:c>
       <x:c r="U117" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V117" s="62" t="n">
-        <x:v>46225</x:v>
+      <x:c r="V117" s="62" t="str">
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="W117" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X117" t="str">
-        <x:v>独立Scarf节点；moving读取同一周期并使用较慢跟随形成滞后，冲刺保留飘动；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
+        <x:v>VisualRoot/Scarf默认隐藏，仅为旧场景兼容；当前四主模块不计入scarf；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -8965,7 +9079,7 @@
         <x:v>CHR-PLY-CAPSULE01-WEAPON-SOCKET-3D</x:v>
       </x:c>
       <x:c r="B118" t="str">
-        <x:v>胶囊防护体3D武器挂点</x:v>
+        <x:v>方形猫角色3D武器挂点</x:v>
       </x:c>
       <x:c r="C118" t="str">
         <x:v>角色</x:v>
@@ -9017,23 +9131,23 @@
         <x:v>角色|player|player_capsule01|weapon_socket_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S118" t="str">
-        <x:f>IF(A118="","",IF(COUNTIF($R$6:$R$145,R118)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A118="","",IF(COUNTIF($R$6:$R$155,R118)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T118" t="str">
-        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
       </x:c>
       <x:c r="U118" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V118" s="62" t="n">
-        <x:v>46225</x:v>
+      <x:c r="V118" s="62" t="str">
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="W118" t="str">
         <x:v>原创逻辑挂点</x:v>
       </x:c>
       <x:c r="X118" t="str">
-        <x:v>手和挂点保持固定局部关系；随moving同相偏移；手持枪模型使用render layer 2；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
+        <x:v>VisualRoot/WeaponSocket：(0.60,1.15,-0.42)，与唯一手固定相对向量；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -9093,7 +9207,7 @@
         <x:v>场景|base|base_world|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S119" t="str">
-        <x:f>IF(A119="","",IF(COUNTIF($R$6:$R$145,R119)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A119="","",IF(COUNTIF($R$6:$R$155,R119)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T119" t="str">
@@ -9169,7 +9283,7 @@
         <x:v>场景道具|facility|base_facility_module|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S120" t="str">
-        <x:f>IF(A120="","",IF(COUNTIF($R$6:$R$145,R120)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A120="","",IF(COUNTIF($R$6:$R$155,R120)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T120" t="str">
@@ -9245,7 +9359,7 @@
         <x:v>场景道具|door|dungeon_gate|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S121" t="str">
-        <x:f>IF(A121="","",IF(COUNTIF($R$6:$R$145,R121)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A121="","",IF(COUNTIF($R$6:$R$155,R121)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T121" t="str">
@@ -9321,7 +9435,7 @@
         <x:v>场景|review_board|base_world|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S122" t="str">
-        <x:f>IF(A122="","",IF(COUNTIF($R$6:$R$145,R122)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A122="","",IF(COUNTIF($R$6:$R$155,R122)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T122" t="str">
@@ -9395,7 +9509,7 @@
         <x:v>场景|room|dungeon_runtime|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S123" s="63" t="str">
-        <x:f>IF(A123="","",IF(COUNTIF($R$6:$R$145,R123)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A123="","",IF(COUNTIF($R$6:$R$155,R123)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T123" s="63" t="str">
@@ -9471,7 +9585,7 @@
         <x:v>场景|biome|iron_frontier|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S124" s="63" t="str">
-        <x:f>IF(A124="","",IF(COUNTIF($R$6:$R$145,R124)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A124="","",IF(COUNTIF($R$6:$R$155,R124)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T124" s="63" t="str">
@@ -9547,7 +9661,7 @@
         <x:v>场景|biome|rust_foundry|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S125" s="63" t="str">
-        <x:f>IF(A125="","",IF(COUNTIF($R$6:$R$145,R125)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A125="","",IF(COUNTIF($R$6:$R$155,R125)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T125" s="63" t="str">
@@ -9623,7 +9737,7 @@
         <x:v>场景|biome|spore_depths|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S126" s="63" t="str">
-        <x:f>IF(A126="","",IF(COUNTIF($R$6:$R$145,R126)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A126="","",IF(COUNTIF($R$6:$R$155,R126)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T126" s="63" t="str">
@@ -9699,7 +9813,7 @@
         <x:v>场景|biome|abyss_archive|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S127" s="63" t="str">
-        <x:f>IF(A127="","",IF(COUNTIF($R$6:$R$145,R127)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A127="","",IF(COUNTIF($R$6:$R$155,R127)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T127" s="63" t="str">
@@ -9775,7 +9889,7 @@
         <x:v>场景道具|light|wasteland_light|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S128" s="63" t="str">
-        <x:f>IF(A128="","",IF(COUNTIF($R$6:$R$145,R128)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A128="","",IF(COUNTIF($R$6:$R$155,R128)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T128" s="63" t="str">
@@ -9851,7 +9965,7 @@
         <x:v>场景道具|furniture|room_furniture|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S129" s="63" t="str">
-        <x:f>IF(A129="","",IF(COUNTIF($R$6:$R$145,R129)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A129="","",IF(COUNTIF($R$6:$R$155,R129)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T129" s="63" t="str">
@@ -9927,7 +10041,7 @@
         <x:v>场景道具|container|search_container|root_3d|俯视3d|closed_opened</x:v>
       </x:c>
       <x:c r="S130" s="63" t="str">
-        <x:f>IF(A130="","",IF(COUNTIF($R$6:$R$145,R130)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A130="","",IF(COUNTIF($R$6:$R$155,R130)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T130" s="63" t="str">
@@ -10003,7 +10117,7 @@
         <x:v>场景道具|facility|service_station|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S131" s="63" t="str">
-        <x:f>IF(A131="","",IF(COUNTIF($R$6:$R$145,R131)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A131="","",IF(COUNTIF($R$6:$R$155,R131)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T131" s="63" t="str">
@@ -10079,7 +10193,7 @@
         <x:v>场景道具|facility|extraction_beacon|root_3d|俯视3d|locked_active_done</x:v>
       </x:c>
       <x:c r="S132" s="63" t="str">
-        <x:f>IF(A132="","",IF(COUNTIF($R$6:$R$145,R132)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A132="","",IF(COUNTIF($R$6:$R$155,R132)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T132" s="63" t="str">
@@ -10155,7 +10269,7 @@
         <x:v>特效|environment|hazard_field|root_3d|俯视3d|active</x:v>
       </x:c>
       <x:c r="S133" s="63" t="str">
-        <x:f>IF(A133="","",IF(COUNTIF($R$6:$R$145,R133)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A133="","",IF(COUNTIF($R$6:$R$155,R133)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T133" s="63" t="str">
@@ -10229,7 +10343,7 @@
         <x:v>枪械|gunbody|blueprint_gun_catalog|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S134" s="63" t="str">
-        <x:f>IF(A134="","",IF(COUNTIF($R$6:$R$145,R134)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A134="","",IF(COUNTIF($R$6:$R$155,R134)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T134" s="63" t="str">
@@ -10303,7 +10417,7 @@
         <x:v>敌人|normal_elite_boss|enemy_ecosystem|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S135" s="63" t="str">
-        <x:f>IF(A135="","",IF(COUNTIF($R$6:$R$145,R135)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A135="","",IF(COUNTIF($R$6:$R$155,R135)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T135" s="63" t="str">
@@ -10377,7 +10491,7 @@
         <x:v>特效|combat|combat_feedback|root_3d|俯视3d|muzzle_impact_damage_explosion</x:v>
       </x:c>
       <x:c r="S136" s="63" t="str">
-        <x:f>IF(A136="","",IF(COUNTIF($R$6:$R$145,R136)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A136="","",IF(COUNTIF($R$6:$R$155,R136)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T136" s="63" t="str">
@@ -10451,7 +10565,7 @@
         <x:v>场景|training_range|training_range|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S137" s="63" t="str">
-        <x:f>IF(A137="","",IF(COUNTIF($R$6:$R$145,R137)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A137="","",IF(COUNTIF($R$6:$R$155,R137)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T137" s="63" t="str">
@@ -10527,7 +10641,7 @@
         <x:v>场景|review_board|dungeon_runtime|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S138" s="63" t="str">
-        <x:f>IF(A138="","",IF(COUNTIF($R$6:$R$145,R138)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A138="","",IF(COUNTIF($R$6:$R$155,R138)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T138" s="63" t="str">
@@ -10603,7 +10717,7 @@
         <x:v>场景|review_board|training_range|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S139" s="63" t="str">
-        <x:f>IF(A139="","",IF(COUNTIF($R$6:$R$145,R139)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A139="","",IF(COUNTIF($R$6:$R$155,R139)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T139" s="63" t="str">
@@ -10679,7 +10793,7 @@
         <x:v>特效|gameplay_vfx|visibility_field|field_mesh_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S140" t="str">
-        <x:f>IF(A140="","",IF(COUNTIF($R$6:$R$145,R140)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A140="","",IF(COUNTIF($R$6:$R$155,R140)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T140" t="str">
@@ -10755,7 +10869,7 @@
         <x:v>ui|screen|inventory|root_3d|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S141" t="str">
-        <x:f>IF(A141="","",IF(COUNTIF($R$6:$R$145,R141)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A141="","",IF(COUNTIF($R$6:$R$155,R141)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T141" t="str">
@@ -10829,7 +10943,7 @@
         <x:v>ui|screen|pause|root_3d|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S142" t="str">
-        <x:f>IF(A142="","",IF(COUNTIF($R$6:$R$145,R142)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A142="","",IF(COUNTIF($R$6:$R$155,R142)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T142" t="str">
@@ -10905,7 +11019,7 @@
         <x:v>场景道具|facility|room_light_switch|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S143" t="str">
-        <x:f>IF(A143="","",IF(COUNTIF($R$6:$R$145,R143)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A143="","",IF(COUNTIF($R$6:$R$155,R143)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T143" t="str">
@@ -10981,7 +11095,7 @@
         <x:v>特效|gameplay_vfx|player_flashlight|light_rig_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S144" t="str">
-        <x:f>IF(A144="","",IF(COUNTIF($R$6:$R$145,R144)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A144="","",IF(COUNTIF($R$6:$R$155,R144)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T144" t="str">
@@ -11057,7 +11171,7 @@
         <x:v>ui|icon|item_model_icon|root_3d|屏幕空间/3d投影|default</x:v>
       </x:c>
       <x:c r="S145" t="str">
-        <x:f>IF(A145="","",IF(COUNTIF($R$6:$R$145,R145)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A145="","",IF(COUNTIF($R$6:$R$155,R145)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T145" t="str">
@@ -11074,6 +11188,766 @@
       </x:c>
       <x:c r="X145" t="str">
         <x:v>与地面拾取共用 ItemModelFactory3D；96×96 内部视口缩放至56px槽位；只渲染一次；验收图：assets/art/ui/inventory_3d/ui_inventory_item_model_preview_v001.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="44" customHeight="1">
+      <x:c r="A146" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-BODY-DIY-3D</x:v>
+      </x:c>
+      <x:c r="B146" s="63" t="str">
+        <x:v>胶囊防护体3D身体DIY变体</x:v>
+      </x:c>
+      <x:c r="C146" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D146" s="63" t="str">
+        <x:v>player_variant</x:v>
+      </x:c>
+      <x:c r="E146" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F146" s="63" t="str">
+        <x:v>body_diy_3d</x:v>
+      </x:c>
+      <x:c r="G146" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-BODY-3D</x:v>
+      </x:c>
+      <x:c r="H146" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I146" s="63" t="str">
+        <x:v>diy</x:v>
+      </x:c>
+      <x:c r="J146" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K146" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L146" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M146" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N146" s="63" t="str">
+        <x:v>3种程序材质</x:v>
+      </x:c>
+      <x:c r="O146" s="63" t="str">
+        <x:v>src/player3d/PlayerAvatar3D.gd</x:v>
+      </x:c>
+      <x:c r="P146" s="63" t="str">
+        <x:v>VisualRoot/Body</x:v>
+      </x:c>
+      <x:c r="Q146" s="63" t="str">
+        <x:v>身体;防护服;DIY;橄榄;沙色;钴蓝</x:v>
+      </x:c>
+      <x:c r="R146" s="63" t="str">
+        <x:f>LOWER(TRIM(C146)&amp;"|"&amp;TRIM(D146)&amp;"|"&amp;TRIM(E146)&amp;"|"&amp;TRIM(F146)&amp;"|"&amp;TRIM(H146)&amp;"|"&amp;TRIM(I146))</x:f>
+        <x:v>角色|player_variant|player_capsule01|body_diy_3d|俯视3d|diy</x:v>
+      </x:c>
+      <x:c r="S146" s="63" t="str">
+        <x:f>IF(A146="","",IF(COUNTIF($R$6:$R$155,R146)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T146" s="63" t="str">
+        <x:v>43c7fa3fa002c9e5a2ec27f04fedeefacee2f32f3a91cb232e98f080513e2f7b</x:v>
+      </x:c>
+      <x:c r="U146" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V146" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W146" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X146" s="63" t="str">
+        <x:v>胶囊防护体3D身体DIY变体；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；verify_player3d_diy_flow PASS ｜ PH33：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="44" customHeight="1">
+      <x:c r="A147" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HEAD-DIY-3D</x:v>
+      </x:c>
+      <x:c r="B147" s="63" t="str">
+        <x:v>胶囊防护体3D头部DIY变体</x:v>
+      </x:c>
+      <x:c r="C147" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D147" s="63" t="str">
+        <x:v>player_variant</x:v>
+      </x:c>
+      <x:c r="E147" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F147" s="63" t="str">
+        <x:v>head_diy_3d</x:v>
+      </x:c>
+      <x:c r="G147" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HEAD-3D</x:v>
+      </x:c>
+      <x:c r="H147" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I147" s="63" t="str">
+        <x:v>diy</x:v>
+      </x:c>
+      <x:c r="J147" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K147" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L147" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M147" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N147" s="63" t="str">
+        <x:v>3种程序材质</x:v>
+      </x:c>
+      <x:c r="O147" s="63" t="str">
+        <x:v>src/player3d/PlayerAvatar3D.gd</x:v>
+      </x:c>
+      <x:c r="P147" s="63" t="str">
+        <x:v>VisualRoot/Head</x:v>
+      </x:c>
+      <x:c r="Q147" s="63" t="str">
+        <x:v>头壳;传感器;DIY;青色面板;琥珀装甲</x:v>
+      </x:c>
+      <x:c r="R147" s="63" t="str">
+        <x:f>LOWER(TRIM(C147)&amp;"|"&amp;TRIM(D147)&amp;"|"&amp;TRIM(E147)&amp;"|"&amp;TRIM(F147)&amp;"|"&amp;TRIM(H147)&amp;"|"&amp;TRIM(I147))</x:f>
+        <x:v>角色|player_variant|player_capsule01|head_diy_3d|俯视3d|diy</x:v>
+      </x:c>
+      <x:c r="S147" s="63" t="str">
+        <x:f>IF(A147="","",IF(COUNTIF($R$6:$R$155,R147)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T147" s="63" t="str">
+        <x:v>43c7fa3fa002c9e5a2ec27f04fedeefacee2f32f3a91cb232e98f080513e2f7b</x:v>
+      </x:c>
+      <x:c r="U147" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V147" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W147" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X147" s="63" t="str">
+        <x:v>胶囊防护体3D头部DIY变体；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；verify_player3d_diy_flow PASS ｜ PH33：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="44" customHeight="1">
+      <x:c r="A148" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HAND-DIY-3D</x:v>
+      </x:c>
+      <x:c r="B148" s="63" t="str">
+        <x:v>胶囊防护体3D手部DIY变体</x:v>
+      </x:c>
+      <x:c r="C148" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D148" s="63" t="str">
+        <x:v>player_variant</x:v>
+      </x:c>
+      <x:c r="E148" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F148" s="63" t="str">
+        <x:v>hand_diy_3d</x:v>
+      </x:c>
+      <x:c r="G148" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HAND-3D</x:v>
+      </x:c>
+      <x:c r="H148" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I148" s="63" t="str">
+        <x:v>diy</x:v>
+      </x:c>
+      <x:c r="J148" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K148" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L148" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M148" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N148" s="63" t="str">
+        <x:v>3种程序材质/抓握压缩</x:v>
+      </x:c>
+      <x:c r="O148" s="63" t="str">
+        <x:v>src/player3d/PlayerAvatar3D.gd</x:v>
+      </x:c>
+      <x:c r="P148" s="63" t="str">
+        <x:v>VisualRoot/Hand</x:v>
+      </x:c>
+      <x:c r="Q148" s="63" t="str">
+        <x:v>唯一手;握持;DIY;橙色;青绿</x:v>
+      </x:c>
+      <x:c r="R148" s="63" t="str">
+        <x:f>LOWER(TRIM(C148)&amp;"|"&amp;TRIM(D148)&amp;"|"&amp;TRIM(E148)&amp;"|"&amp;TRIM(F148)&amp;"|"&amp;TRIM(H148)&amp;"|"&amp;TRIM(I148))</x:f>
+        <x:v>角色|player_variant|player_capsule01|hand_diy_3d|俯视3d|diy</x:v>
+      </x:c>
+      <x:c r="S148" s="63" t="str">
+        <x:f>IF(A148="","",IF(COUNTIF($R$6:$R$155,R148)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T148" s="63" t="str">
+        <x:v>43c7fa3fa002c9e5a2ec27f04fedeefacee2f32f3a91cb232e98f080513e2f7b</x:v>
+      </x:c>
+      <x:c r="U148" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V148" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W148" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X148" s="63" t="str">
+        <x:v>胶囊防护体3D手部DIY变体；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；verify_player3d_diy_flow PASS ｜ PH33：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="44" customHeight="1">
+      <x:c r="A149" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HAT-DIY-3D</x:v>
+      </x:c>
+      <x:c r="B149" s="63" t="str">
+        <x:v>胶囊防护体3D帽子DIY组件</x:v>
+      </x:c>
+      <x:c r="C149" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D149" s="63" t="str">
+        <x:v>player_accessory</x:v>
+      </x:c>
+      <x:c r="E149" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F149" s="63" t="str">
+        <x:v>hat_diy_3d</x:v>
+      </x:c>
+      <x:c r="G149" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HEAD-3D</x:v>
+      </x:c>
+      <x:c r="H149" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I149" s="63" t="str">
+        <x:v>diy</x:v>
+      </x:c>
+      <x:c r="J149" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K149" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L149" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M149" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N149" s="63" t="str">
+        <x:v>软帽/安全帽/密封兜帽</x:v>
+      </x:c>
+      <x:c r="O149" s="63" t="str">
+        <x:v>src/player3d/PlayerAvatar3D.gd</x:v>
+      </x:c>
+      <x:c r="P149" s="63" t="str">
+        <x:v>VisualRoot/Head/Wearables</x:v>
+      </x:c>
+      <x:c r="Q149" s="63" t="str">
+        <x:v>帽子;软帽;安全帽;兜帽;DIY</x:v>
+      </x:c>
+      <x:c r="R149" s="63" t="str">
+        <x:f>LOWER(TRIM(C149)&amp;"|"&amp;TRIM(D149)&amp;"|"&amp;TRIM(E149)&amp;"|"&amp;TRIM(F149)&amp;"|"&amp;TRIM(H149)&amp;"|"&amp;TRIM(I149))</x:f>
+        <x:v>角色|player_accessory|player_capsule01|hat_diy_3d|俯视3d|diy</x:v>
+      </x:c>
+      <x:c r="S149" s="63" t="str">
+        <x:f>IF(A149="","",IF(COUNTIF($R$6:$R$155,R149)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T149" s="63" t="str">
+        <x:v>43c7fa3fa002c9e5a2ec27f04fedeefacee2f32f3a91cb232e98f080513e2f7b</x:v>
+      </x:c>
+      <x:c r="U149" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V149" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W149" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X149" s="63" t="str">
+        <x:v>胶囊防护体3D帽子DIY组件；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；verify_player3d_diy_flow PASS ｜ PH32灯光修正：角色专用层2；禁用投影/GI，仅接收AvatarFrontFill，不遮挡头壳传感器或探照灯 ｜ PH33：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="44" customHeight="1">
+      <x:c r="A150" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-GLASSES-DIY-3D</x:v>
+      </x:c>
+      <x:c r="B150" s="63" t="str">
+        <x:v>胶囊防护体3D眼镜DIY组件</x:v>
+      </x:c>
+      <x:c r="C150" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D150" s="63" t="str">
+        <x:v>player_accessory</x:v>
+      </x:c>
+      <x:c r="E150" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F150" s="63" t="str">
+        <x:v>glasses_diy_3d</x:v>
+      </x:c>
+      <x:c r="G150" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HEAD-3D</x:v>
+      </x:c>
+      <x:c r="H150" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I150" s="63" t="str">
+        <x:v>diy</x:v>
+      </x:c>
+      <x:c r="J150" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K150" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L150" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M150" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N150" s="63" t="str">
+        <x:v>单目镜/双目护镜/宽面护目镜</x:v>
+      </x:c>
+      <x:c r="O150" s="63" t="str">
+        <x:v>src/player3d/PlayerAvatar3D.gd</x:v>
+      </x:c>
+      <x:c r="P150" s="63" t="str">
+        <x:v>VisualRoot/Head/Wearables</x:v>
+      </x:c>
+      <x:c r="Q150" s="63" t="str">
+        <x:v>眼镜;单目镜;护目镜;宽面护目镜;DIY</x:v>
+      </x:c>
+      <x:c r="R150" s="63" t="str">
+        <x:f>LOWER(TRIM(C150)&amp;"|"&amp;TRIM(D150)&amp;"|"&amp;TRIM(E150)&amp;"|"&amp;TRIM(F150)&amp;"|"&amp;TRIM(H150)&amp;"|"&amp;TRIM(I150))</x:f>
+        <x:v>角色|player_accessory|player_capsule01|glasses_diy_3d|俯视3d|diy</x:v>
+      </x:c>
+      <x:c r="S150" s="63" t="str">
+        <x:f>IF(A150="","",IF(COUNTIF($R$6:$R$155,R150)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T150" s="63" t="str">
+        <x:v>43c7fa3fa002c9e5a2ec27f04fedeefacee2f32f3a91cb232e98f080513e2f7b</x:v>
+      </x:c>
+      <x:c r="U150" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V150" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W150" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X150" s="63" t="str">
+        <x:v>胶囊防护体3D眼镜DIY组件；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；verify_player3d_diy_flow PASS ｜ PH32灯光修正：角色专用层2；禁用投影/GI，仅接收AvatarFrontFill，不遮挡头壳传感器或探照灯 ｜ PH33：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="44" customHeight="1">
+      <x:c r="A151" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-FOOT-3D</x:v>
+      </x:c>
+      <x:c r="B151" s="63" t="str">
+        <x:v>方形猫角色3D脚部模块</x:v>
+      </x:c>
+      <x:c r="C151" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D151" s="63" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="E151" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F151" s="63" t="str">
+        <x:v>feet_3d</x:v>
+      </x:c>
+      <x:c r="G151" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="H151" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I151" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J151" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K151" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L151" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M151" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N151" s="63" t="str">
+        <x:v>双BoxMesh短脚</x:v>
+      </x:c>
+      <x:c r="O151" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P151" s="63" t="str">
+        <x:v>VisualRoot/Feet</x:v>
+      </x:c>
+      <x:c r="Q151" s="63" t="str">
+        <x:v>脚;脚部;双脚;方脚;猫脚</x:v>
+      </x:c>
+      <x:c r="R151" s="63" t="str">
+        <x:f>LOWER(TRIM(C151)&amp;"|"&amp;TRIM(D151)&amp;"|"&amp;TRIM(E151)&amp;"|"&amp;TRIM(F151)&amp;"|"&amp;TRIM(H151)&amp;"|"&amp;TRIM(I151))</x:f>
+        <x:v>角色|player|player_capsule01|feet_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S151" s="63" t="str">
+        <x:f>IF(A151="","",IF(COUNTIF($R$6:$R$155,R151)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T151" s="63" t="str">
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+      </x:c>
+      <x:c r="U151" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V151" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W151" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X151" s="63" t="str">
+        <x:v>方形猫角色3D脚部模块；复用CHR-PLY-CAPSULE01-3D玩家根；方形主语言，TailStub为用户指定圆尾例外；自动与视觉验收PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="44" customHeight="1">
+      <x:c r="A152" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-EYES-3D</x:v>
+      </x:c>
+      <x:c r="B152" s="63" t="str">
+        <x:v>方形猫角色3D双眼配件</x:v>
+      </x:c>
+      <x:c r="C152" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D152" s="63" t="str">
+        <x:v>player_accessory</x:v>
+      </x:c>
+      <x:c r="E152" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F152" s="63" t="str">
+        <x:v>eyes_3d</x:v>
+      </x:c>
+      <x:c r="G152" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HEAD-3D</x:v>
+      </x:c>
+      <x:c r="H152" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I152" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J152" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K152" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L152" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M152" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N152" s="63" t="str">
+        <x:v>2个矩形豆豆眼</x:v>
+      </x:c>
+      <x:c r="O152" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P152" s="63" t="str">
+        <x:v>VisualRoot/Head/Eyes</x:v>
+      </x:c>
+      <x:c r="Q152" s="63" t="str">
+        <x:v>眼睛;双眼;豆豆眼;矩形眼</x:v>
+      </x:c>
+      <x:c r="R152" s="63" t="str">
+        <x:f>LOWER(TRIM(C152)&amp;"|"&amp;TRIM(D152)&amp;"|"&amp;TRIM(E152)&amp;"|"&amp;TRIM(F152)&amp;"|"&amp;TRIM(H152)&amp;"|"&amp;TRIM(I152))</x:f>
+        <x:v>角色|player_accessory|player_capsule01|eyes_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S152" s="63" t="str">
+        <x:f>IF(A152="","",IF(COUNTIF($R$6:$R$155,R152)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T152" s="63" t="str">
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+      </x:c>
+      <x:c r="U152" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V152" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W152" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X152" s="63" t="str">
+        <x:v>方形猫角色3D双眼配件；复用CHR-PLY-CAPSULE01-3D玩家根；方形主语言，TailStub为用户指定圆尾例外；自动与视觉验收PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="44" customHeight="1">
+      <x:c r="A153" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-EARS-3D</x:v>
+      </x:c>
+      <x:c r="B153" s="63" t="str">
+        <x:v>方形猫角色3D双耳配件</x:v>
+      </x:c>
+      <x:c r="C153" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D153" s="63" t="str">
+        <x:v>player_accessory</x:v>
+      </x:c>
+      <x:c r="E153" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F153" s="63" t="str">
+        <x:v>ears_3d</x:v>
+      </x:c>
+      <x:c r="G153" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HEAD-3D</x:v>
+      </x:c>
+      <x:c r="H153" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I153" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J153" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K153" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L153" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M153" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N153" s="63" t="str">
+        <x:v>2个三角耳</x:v>
+      </x:c>
+      <x:c r="O153" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P153" s="63" t="str">
+        <x:v>VisualRoot/Head/Ears</x:v>
+      </x:c>
+      <x:c r="Q153" s="63" t="str">
+        <x:v>耳朵;双耳;猫耳;三角耳</x:v>
+      </x:c>
+      <x:c r="R153" s="63" t="str">
+        <x:f>LOWER(TRIM(C153)&amp;"|"&amp;TRIM(D153)&amp;"|"&amp;TRIM(E153)&amp;"|"&amp;TRIM(F153)&amp;"|"&amp;TRIM(H153)&amp;"|"&amp;TRIM(I153))</x:f>
+        <x:v>角色|player_accessory|player_capsule01|ears_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S153" s="63" t="str">
+        <x:f>IF(A153="","",IF(COUNTIF($R$6:$R$155,R153)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T153" s="63" t="str">
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+      </x:c>
+      <x:c r="U153" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V153" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W153" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X153" s="63" t="str">
+        <x:v>方形猫角色3D双耳配件；复用CHR-PLY-CAPSULE01-3D玩家根；方形主语言，TailStub为用户指定圆尾例外；自动与视觉验收PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="44" customHeight="1">
+      <x:c r="A154" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-TAIL-STUB-3D</x:v>
+      </x:c>
+      <x:c r="B154" s="63" t="str">
+        <x:v>方形猫角色3D圆短尾</x:v>
+      </x:c>
+      <x:c r="C154" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D154" s="63" t="str">
+        <x:v>player_accessory</x:v>
+      </x:c>
+      <x:c r="E154" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F154" s="63" t="str">
+        <x:v>tail_stub_3d</x:v>
+      </x:c>
+      <x:c r="G154" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-BODY-3D</x:v>
+      </x:c>
+      <x:c r="H154" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I154" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J154" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K154" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L154" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M154" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N154" s="63" t="str">
+        <x:v>单个SphereMesh圆尾团</x:v>
+      </x:c>
+      <x:c r="O154" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P154" s="63" t="str">
+        <x:v>VisualRoot/Body/TailStub</x:v>
+      </x:c>
+      <x:c r="Q154" s="63" t="str">
+        <x:v>尾巴;短尾;圆尾;尾团;无长尾</x:v>
+      </x:c>
+      <x:c r="R154" s="63" t="str">
+        <x:f>LOWER(TRIM(C154)&amp;"|"&amp;TRIM(D154)&amp;"|"&amp;TRIM(E154)&amp;"|"&amp;TRIM(F154)&amp;"|"&amp;TRIM(H154)&amp;"|"&amp;TRIM(I154))</x:f>
+        <x:v>角色|player_accessory|player_capsule01|tail_stub_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S154" s="63" t="str">
+        <x:f>IF(A154="","",IF(COUNTIF($R$6:$R$155,R154)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T154" s="63" t="str">
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+      </x:c>
+      <x:c r="U154" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V154" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W154" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X154" s="63" t="str">
+        <x:v>方形猫角色3D圆短尾；复用CHR-PLY-CAPSULE01-3D玩家根；方形主语言，TailStub为用户指定圆尾例外；自动与视觉验收PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="44" customHeight="1">
+      <x:c r="A155" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-FEET-DIY-3D</x:v>
+      </x:c>
+      <x:c r="B155" s="63" t="str">
+        <x:v>方形猫角色3D脚部DIY变体</x:v>
+      </x:c>
+      <x:c r="C155" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D155" s="63" t="str">
+        <x:v>player_variant</x:v>
+      </x:c>
+      <x:c r="E155" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F155" s="63" t="str">
+        <x:v>feet_diy_3d</x:v>
+      </x:c>
+      <x:c r="G155" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-FOOT-3D</x:v>
+      </x:c>
+      <x:c r="H155" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I155" s="63" t="str">
+        <x:v>diy</x:v>
+      </x:c>
+      <x:c r="J155" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K155" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L155" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M155" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N155" s="63" t="str">
+        <x:v>4种程序材质</x:v>
+      </x:c>
+      <x:c r="O155" s="63" t="str">
+        <x:v>src/player3d/PlayerAvatar3D.gd</x:v>
+      </x:c>
+      <x:c r="P155" s="63" t="str">
+        <x:v>VisualRoot/Feet</x:v>
+      </x:c>
+      <x:c r="Q155" s="63" t="str">
+        <x:v>脚部DIY;猫脚;短靴;橙色;沙色;钴蓝;青绿</x:v>
+      </x:c>
+      <x:c r="R155" s="63" t="str">
+        <x:f>LOWER(TRIM(C155)&amp;"|"&amp;TRIM(D155)&amp;"|"&amp;TRIM(E155)&amp;"|"&amp;TRIM(F155)&amp;"|"&amp;TRIM(H155)&amp;"|"&amp;TRIM(I155))</x:f>
+        <x:v>角色|player_variant|player_capsule01|feet_diy_3d|俯视3d|diy</x:v>
+      </x:c>
+      <x:c r="S155" s="63" t="str">
+        <x:f>IF(A155="","",IF(COUNTIF($R$6:$R$155,R155)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T155" s="63" t="str">
+        <x:v>43c7fa3fa002c9e5a2ec27f04fedeefacee2f32f3a91cb232e98f080513e2f7b</x:v>
+      </x:c>
+      <x:c r="U155" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V155" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W155" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X155" s="63" t="str">
+        <x:v>方形猫角色3D脚部DIY变体；复用CHR-PLY-CAPSULE01-3D玩家根；方形主语言，TailStub为用户指定圆尾例外；自动与视觉验收PASS</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11101,7 +11975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc54e4f8a28d64a35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54ff6c904d8a485a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11543,7 +12417,7 @@
         <x:v>必要时高于双手</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="34" customHeight="1">
+    <x:row r="14" ht="38" customHeight="1">
       <x:c r="A14" s="63" t="str">
         <x:v>player_capsule01_3d</x:v>
       </x:c>
@@ -11572,7 +12446,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J14" s="63" t="str">
-        <x:v>六态整体变换 + reloading覆盖</x:v>
+        <x:v>六态整体 + reloading/firing/charging/knockback覆盖</x:v>
       </x:c>
       <x:c r="K14" s="63" t="str">
         <x:v>3D表现根</x:v>
@@ -11581,10 +12455,10 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M14" s="63" t="str">
-        <x:v>与2D共用六态ID；reloading不替换顶层；摄像机和头顶条不跟随VisualRoot旋转</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="34" customHeight="1">
+        <x:v>四主模块：Body/Head/Hand/Feet；2D旧胶囊不在本次迁移范围</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="38" customHeight="1">
       <x:c r="A15" s="63" t="str">
         <x:v>player_capsule01_3d</x:v>
       </x:c>
@@ -11601,10 +12475,10 @@
         <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
       </x:c>
       <x:c r="F15" s="63" t="str">
-        <x:v>CapsuleMesh</x:v>
+        <x:v>BoxMesh + 子件</x:v>
       </x:c>
       <x:c r="G15" s="63" t="str">
-        <x:v>(0,0.88,0)</x:v>
+        <x:v>(0,0.76,0.02)</x:v>
       </x:c>
       <x:c r="H15" s="63" t="str">
         <x:v>随root</x:v>
@@ -11613,27 +12487,27 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="63" t="str">
-        <x:v>独立移动弹性/呼吸/死亡倾倒</x:v>
+        <x:v>呼吸/移动压缩/射击前探/死亡倾倒</x:v>
       </x:c>
       <x:c r="K15" s="63" t="str">
-        <x:v>防护服主体</x:v>
+        <x:v>方形猫身</x:v>
       </x:c>
       <x:c r="L15" s="63" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="M15" s="63" t="str">
-        <x:v>无腿、无脚、无手臂；render layer 2；移动振幅沿用2D弹性</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="34" customHeight="1">
+        <x:v>BodyShell + BellyPatch；方形主轮廓</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="38" customHeight="1">
       <x:c r="A16" s="63" t="str">
         <x:v>player_capsule01_3d</x:v>
       </x:c>
       <x:c r="B16" s="63" t="str">
-        <x:v>scarf</x:v>
+        <x:v>head</x:v>
       </x:c>
       <x:c r="C16" s="63" t="str">
-        <x:v>VisualRoot/Scarf</x:v>
+        <x:v>VisualRoot/Head</x:v>
       </x:c>
       <x:c r="D16" s="63" t="str">
         <x:v>root</x:v>
@@ -11642,39 +12516,39 @@
         <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
       </x:c>
       <x:c r="F16" s="63" t="str">
-        <x:v>Cylinder+Box</x:v>
+        <x:v>BoxMesh + 子件</x:v>
       </x:c>
       <x:c r="G16" s="63" t="str">
-        <x:v>(0,1.43,0)</x:v>
+        <x:v>(0,1.72,-0.08)</x:v>
       </x:c>
       <x:c r="H16" s="63" t="str">
-        <x:v>随root + 轻摆</x:v>
+        <x:v>随root</x:v>
       </x:c>
       <x:c r="I16" s="63" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J16" s="63" t="str">
-        <x:v>移动周期滞后/冲刺飘动</x:v>
+        <x:v>移动反相滞后/后坐/受击/死亡</x:v>
       </x:c>
       <x:c r="K16" s="63" t="str">
-        <x:v>身份配件</x:v>
+        <x:v>方形猫头</x:v>
       </x:c>
       <x:c r="L16" s="63" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M16" s="63" t="str">
-        <x:v>独立红围巾组件；moving以较慢跟随形成可读滞后</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="34" customHeight="1">
+        <x:v>无嘴无鼻；Eyes与Ears固定归Head</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="38" customHeight="1">
       <x:c r="A17" s="63" t="str">
         <x:v>player_capsule01_3d</x:v>
       </x:c>
       <x:c r="B17" s="63" t="str">
-        <x:v>head</x:v>
+        <x:v>hand</x:v>
       </x:c>
       <x:c r="C17" s="63" t="str">
-        <x:v>VisualRoot/Head</x:v>
+        <x:v>VisualRoot/Hand</x:v>
       </x:c>
       <x:c r="D17" s="63" t="str">
         <x:v>root</x:v>
@@ -11683,39 +12557,39 @@
         <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
       </x:c>
       <x:c r="F17" s="63" t="str">
-        <x:v>SphereMesh</x:v>
+        <x:v>BoxMesh</x:v>
       </x:c>
       <x:c r="G17" s="63" t="str">
-        <x:v>(0,1.84,-0.01)</x:v>
+        <x:v>(0.60,1.10,-0.30)</x:v>
       </x:c>
       <x:c r="H17" s="63" t="str">
-        <x:v>随root</x:v>
+        <x:v>随root；动作同相</x:v>
       </x:c>
       <x:c r="I17" s="63" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J17" s="63" t="str">
-        <x:v>移动反相滞后/呼吸/受击/死亡</x:v>
+        <x:v>移动/换弹/射击/蓄力/击飞保持握持</x:v>
       </x:c>
       <x:c r="K17" s="63" t="str">
-        <x:v>头壳/传感器</x:v>
+        <x:v>唯一悬浮手</x:v>
       </x:c>
       <x:c r="L17" s="63" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="M17" s="63" t="str">
-        <x:v>单传感器；无嘴无人脸；只受角色正面柔光与房间公共灯</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="34" customHeight="1">
+        <x:v>无手臂、无第二手；与WeaponSocket固定相对向量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="38" customHeight="1">
       <x:c r="A18" s="63" t="str">
         <x:v>player_capsule01_3d</x:v>
       </x:c>
       <x:c r="B18" s="63" t="str">
-        <x:v>hand</x:v>
+        <x:v>feet</x:v>
       </x:c>
       <x:c r="C18" s="63" t="str">
-        <x:v>VisualRoot/Hand</x:v>
+        <x:v>VisualRoot/Feet</x:v>
       </x:c>
       <x:c r="D18" s="63" t="str">
         <x:v>root</x:v>
@@ -11724,110 +12598,520 @@
         <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
       </x:c>
       <x:c r="F18" s="63" t="str">
-        <x:v>SphereMesh</x:v>
+        <x:v>BoxMesh×2</x:v>
       </x:c>
       <x:c r="G18" s="63" t="str">
-        <x:v>(0.72,1.22,-0.18)</x:v>
+        <x:v>(0,0.22,-0.02)</x:v>
       </x:c>
       <x:c r="H18" s="63" t="str">
-        <x:v>随root；换弹时同相位移/旋转</x:v>
+        <x:v>随root；FootL/R交替</x:v>
       </x:c>
       <x:c r="I18" s="63" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J18" s="63" t="str">
-        <x:v>moving同相；换弹下压/操作/回位；保持握持位</x:v>
+        <x:v>moving交替抬脚；冲刺/受击/死亡随整体</x:v>
       </x:c>
       <x:c r="K18" s="63" t="str">
-        <x:v>唯一握持手</x:v>
+        <x:v>双脚主模块</x:v>
       </x:c>
       <x:c r="L18" s="63" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="M18" s="63" t="str">
-        <x:v>只有一只手；与weapon_socket在moving/reloading全周期保持固定相对向量</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="34" customHeight="1">
+        <x:v>FootL/FootR属于同一可替换Feet模块</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="38" customHeight="1">
       <x:c r="A19" s="63" t="str">
         <x:v>player_capsule01_3d</x:v>
       </x:c>
       <x:c r="B19" s="63" t="str">
-        <x:v>weapon_socket</x:v>
+        <x:v>eyes</x:v>
       </x:c>
       <x:c r="C19" s="63" t="str">
-        <x:v>VisualRoot/WeaponSocket</x:v>
+        <x:v>VisualRoot/Head/Eyes</x:v>
       </x:c>
       <x:c r="D19" s="63" t="str">
-        <x:v>root</x:v>
+        <x:v>head</x:v>
       </x:c>
       <x:c r="E19" s="63" t="str">
-        <x:v>无纹理</x:v>
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
       </x:c>
       <x:c r="F19" s="63" t="str">
-        <x:v>Marker3D</x:v>
+        <x:v>BoxMesh×2</x:v>
       </x:c>
       <x:c r="G19" s="63" t="str">
-        <x:v>(0.72,1.24,-0.34)</x:v>
+        <x:v>(0,-0.03,-0.56)</x:v>
       </x:c>
       <x:c r="H19" s="63" t="str">
-        <x:v>随root；换弹时同相位移/旋转</x:v>
+        <x:v>继承Head</x:v>
       </x:c>
       <x:c r="I19" s="63" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J19" s="63" t="str">
-        <x:v>与唯一手同相；换弹下压/操作/回位；枪械挂载/枪口特效</x:v>
+        <x:v>随头部滞后/后坐/受击</x:v>
       </x:c>
       <x:c r="K19" s="63" t="str">
-        <x:v>武器系统</x:v>
+        <x:v>面部配件</x:v>
       </x:c>
       <x:c r="L19" s="63" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="M19" s="63" t="str">
-        <x:v>挂点与手在moving/reloading保持固定局部关系；手持枪网格统一render layer 2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="34" customHeight="1">
+        <x:v>EyeL/EyeR；深色窄矩形豆豆眼；无嘴</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="38" customHeight="1">
       <x:c r="A20" s="63" t="str">
         <x:v>player_capsule01_3d</x:v>
       </x:c>
       <x:c r="B20" s="63" t="str">
-        <x:v>reload_progress</x:v>
+        <x:v>ears</x:v>
       </x:c>
       <x:c r="C20" s="63" t="str">
-        <x:v>ReloadProgress3D</x:v>
+        <x:v>VisualRoot/Head/Ears</x:v>
       </x:c>
       <x:c r="D20" s="63" t="str">
-        <x:v>player_root</x:v>
+        <x:v>head</x:v>
       </x:c>
       <x:c r="E20" s="63" t="str">
         <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
       </x:c>
       <x:c r="F20" s="63" t="str">
-        <x:v>QuadMesh×2</x:v>
+        <x:v>三边CylinderMesh×4</x:v>
       </x:c>
       <x:c r="G20" s="63" t="str">
-        <x:v>(0,2.72,0.06)</x:v>
+        <x:v>沿Head顶部</x:v>
       </x:c>
       <x:c r="H20" s="63" t="str">
-        <x:v>朝向相机；不随VisualRoot旋转</x:v>
+        <x:v>继承Head</x:v>
       </x:c>
       <x:c r="I20" s="63" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J20" s="63" t="str">
-        <x:v>读取真实换弹进度；左端固定；完成/取消隐藏</x:v>
+        <x:v>随头部滞后/后坐/受击</x:v>
       </x:c>
       <x:c r="K20" s="63" t="str">
-        <x:v>状态UI子组件</x:v>
+        <x:v>头部配件</x:v>
       </x:c>
       <x:c r="L20" s="63" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="M20" s="63" t="str">
-        <x:v>无独立计时器/SubViewport；不参与碰撞、视野、灯光或输入；56组合共用</x:v>
+        <x:v>EarL/EarR各含Inner；三角形语言</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="38" customHeight="1">
+      <x:c r="A21" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B21" s="63" t="str">
+        <x:v>tail_stub</x:v>
+      </x:c>
+      <x:c r="C21" s="63" t="str">
+        <x:v>VisualRoot/Body/TailStub</x:v>
+      </x:c>
+      <x:c r="D21" s="63" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="E21" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F21" s="63" t="str">
+        <x:v>SphereMesh</x:v>
+      </x:c>
+      <x:c r="G21" s="63" t="str">
+        <x:v>(-0.51,-0.02,0.24)</x:v>
+      </x:c>
+      <x:c r="H21" s="63" t="str">
+        <x:v>继承Body + 轻摆</x:v>
+      </x:c>
+      <x:c r="I21" s="63" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J21" s="63" t="str">
+        <x:v>moving轻摆/弹性缩放</x:v>
+      </x:c>
+      <x:c r="K21" s="63" t="str">
+        <x:v>身体配件</x:v>
+      </x:c>
+      <x:c r="L21" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M21" s="63" t="str">
+        <x:v>唯一圆形例外；短圆尾团，禁止长尾</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="38" customHeight="1">
+      <x:c r="A22" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B22" s="63" t="str">
+        <x:v>weapon_socket</x:v>
+      </x:c>
+      <x:c r="C22" s="63" t="str">
+        <x:v>VisualRoot/WeaponSocket</x:v>
+      </x:c>
+      <x:c r="D22" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E22" s="63" t="str">
+        <x:v>无纹理</x:v>
+      </x:c>
+      <x:c r="F22" s="63" t="str">
+        <x:v>Marker3D</x:v>
+      </x:c>
+      <x:c r="G22" s="63" t="str">
+        <x:v>(0.60,1.15,-0.42)</x:v>
+      </x:c>
+      <x:c r="H22" s="63" t="str">
+        <x:v>随root；动作同相</x:v>
+      </x:c>
+      <x:c r="I22" s="63" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J22" s="63" t="str">
+        <x:v>枪械挂载/枪口特效</x:v>
+      </x:c>
+      <x:c r="K22" s="63" t="str">
+        <x:v>武器系统</x:v>
+      </x:c>
+      <x:c r="L22" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M22" s="63" t="str">
+        <x:v>与唯一手全动作固定局部关系；枪模layer 2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="38" customHeight="1">
+      <x:c r="A23" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B23" s="63" t="str">
+        <x:v>reload_progress</x:v>
+      </x:c>
+      <x:c r="C23" s="63" t="str">
+        <x:v>ReloadProgress3D</x:v>
+      </x:c>
+      <x:c r="D23" s="63" t="str">
+        <x:v>player_root</x:v>
+      </x:c>
+      <x:c r="E23" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F23" s="63" t="str">
+        <x:v>QuadMesh×2</x:v>
+      </x:c>
+      <x:c r="G23" s="63" t="str">
+        <x:v>(0,2.92,0.06)</x:v>
+      </x:c>
+      <x:c r="H23" s="63" t="str">
+        <x:v>朝向相机；不随VisualRoot旋转</x:v>
+      </x:c>
+      <x:c r="I23" s="63" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J23" s="63" t="str">
+        <x:v>读取真实换弹进度</x:v>
+      </x:c>
+      <x:c r="K23" s="63" t="str">
+        <x:v>状态UI子组件</x:v>
+      </x:c>
+      <x:c r="L23" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M23" s="63" t="str">
+        <x:v>高于猫耳；无独立计时器/SubViewport</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="38" customHeight="1">
+      <x:c r="A24" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B24" s="63" t="str">
+        <x:v>body_diy</x:v>
+      </x:c>
+      <x:c r="C24" s="63" t="str">
+        <x:v>VisualRoot/Body</x:v>
+      </x:c>
+      <x:c r="D24" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E24" s="63" t="str">
+        <x:v>无独立纹理/程序材质</x:v>
+      </x:c>
+      <x:c r="F24" s="63" t="str">
+        <x:v>4种配色</x:v>
+      </x:c>
+      <x:c r="G24" s="63" t="str">
+        <x:v>沿Body</x:v>
+      </x:c>
+      <x:c r="H24" s="63" t="str">
+        <x:v>随root</x:v>
+      </x:c>
+      <x:c r="I24" s="63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J24" s="63" t="str">
+        <x:v>继承身体动态</x:v>
+      </x:c>
+      <x:c r="K24" s="63" t="str">
+        <x:v>身体外观</x:v>
+      </x:c>
+      <x:c r="L24" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M24" s="63" t="str">
+        <x:v>cat_orange + 旧三色兼容</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="38" customHeight="1">
+      <x:c r="A25" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B25" s="63" t="str">
+        <x:v>head_diy</x:v>
+      </x:c>
+      <x:c r="C25" s="63" t="str">
+        <x:v>VisualRoot/Head</x:v>
+      </x:c>
+      <x:c r="D25" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E25" s="63" t="str">
+        <x:v>无独立纹理/程序材质</x:v>
+      </x:c>
+      <x:c r="F25" s="63" t="str">
+        <x:v>4种配色</x:v>
+      </x:c>
+      <x:c r="G25" s="63" t="str">
+        <x:v>沿Head</x:v>
+      </x:c>
+      <x:c r="H25" s="63" t="str">
+        <x:v>随root</x:v>
+      </x:c>
+      <x:c r="I25" s="63" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J25" s="63" t="str">
+        <x:v>继承头部动态</x:v>
+      </x:c>
+      <x:c r="K25" s="63" t="str">
+        <x:v>头部外观</x:v>
+      </x:c>
+      <x:c r="L25" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M25" s="63" t="str">
+        <x:v>cat_orange + 旧三色兼容；双眼/双耳节点不变</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="38" customHeight="1">
+      <x:c r="A26" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B26" s="63" t="str">
+        <x:v>hand_diy</x:v>
+      </x:c>
+      <x:c r="C26" s="63" t="str">
+        <x:v>VisualRoot/Hand</x:v>
+      </x:c>
+      <x:c r="D26" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E26" s="63" t="str">
+        <x:v>无独立纹理/程序材质</x:v>
+      </x:c>
+      <x:c r="F26" s="63" t="str">
+        <x:v>4种配色</x:v>
+      </x:c>
+      <x:c r="G26" s="63" t="str">
+        <x:v>(0.60,1.10,-0.30)</x:v>
+      </x:c>
+      <x:c r="H26" s="63" t="str">
+        <x:v>随root+同相动作</x:v>
+      </x:c>
+      <x:c r="I26" s="63" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J26" s="63" t="str">
+        <x:v>抓握压缩；与socket同相</x:v>
+      </x:c>
+      <x:c r="K26" s="63" t="str">
+        <x:v>唯一手外观</x:v>
+      </x:c>
+      <x:c r="L26" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M26" s="63" t="str">
+        <x:v>cat_orange + 旧三色兼容</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="38" customHeight="1">
+      <x:c r="A27" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B27" s="63" t="str">
+        <x:v>feet_diy</x:v>
+      </x:c>
+      <x:c r="C27" s="63" t="str">
+        <x:v>VisualRoot/Feet</x:v>
+      </x:c>
+      <x:c r="D27" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E27" s="63" t="str">
+        <x:v>无独立纹理/程序材质</x:v>
+      </x:c>
+      <x:c r="F27" s="63" t="str">
+        <x:v>4种配色</x:v>
+      </x:c>
+      <x:c r="G27" s="63" t="str">
+        <x:v>沿Feet</x:v>
+      </x:c>
+      <x:c r="H27" s="63" t="str">
+        <x:v>随root+交替步态</x:v>
+      </x:c>
+      <x:c r="I27" s="63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J27" s="63" t="str">
+        <x:v>FootL/R交替抬起</x:v>
+      </x:c>
+      <x:c r="K27" s="63" t="str">
+        <x:v>脚部外观</x:v>
+      </x:c>
+      <x:c r="L27" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M27" s="63" t="str">
+        <x:v>cat_orange / boot_sand / boot_cobalt / boot_teal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="38" customHeight="1">
+      <x:c r="A28" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B28" s="63" t="str">
+        <x:v>hat</x:v>
+      </x:c>
+      <x:c r="C28" s="63" t="str">
+        <x:v>VisualRoot/Head/Wearables/Hat*</x:v>
+      </x:c>
+      <x:c r="D28" s="63" t="str">
+        <x:v>head</x:v>
+      </x:c>
+      <x:c r="E28" s="63" t="str">
+        <x:v>无独立纹理/程序网格</x:v>
+      </x:c>
+      <x:c r="F28" s="63" t="str">
+        <x:v>3种帽型</x:v>
+      </x:c>
+      <x:c r="G28" s="63" t="str">
+        <x:v>沿Head</x:v>
+      </x:c>
+      <x:c r="H28" s="63" t="str">
+        <x:v>继承Head</x:v>
+      </x:c>
+      <x:c r="I28" s="63" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J28" s="63" t="str">
+        <x:v>头部滞后/受击/死亡</x:v>
+      </x:c>
+      <x:c r="K28" s="63" t="str">
+        <x:v>头部外戴件</x:v>
+      </x:c>
+      <x:c r="L28" s="63" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="M28" s="63" t="str">
+        <x:v>可选；layer2，禁投影/GI；不得替代猫耳节点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="38" customHeight="1">
+      <x:c r="A29" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B29" s="63" t="str">
+        <x:v>glasses</x:v>
+      </x:c>
+      <x:c r="C29" s="63" t="str">
+        <x:v>VisualRoot/Head/Wearables/Glasses*</x:v>
+      </x:c>
+      <x:c r="D29" s="63" t="str">
+        <x:v>head</x:v>
+      </x:c>
+      <x:c r="E29" s="63" t="str">
+        <x:v>无独立纹理/程序网格</x:v>
+      </x:c>
+      <x:c r="F29" s="63" t="str">
+        <x:v>3种护目件</x:v>
+      </x:c>
+      <x:c r="G29" s="63" t="str">
+        <x:v>沿Head前侧</x:v>
+      </x:c>
+      <x:c r="H29" s="63" t="str">
+        <x:v>继承Head</x:v>
+      </x:c>
+      <x:c r="I29" s="63" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J29" s="63" t="str">
+        <x:v>头部滞后/受击/死亡</x:v>
+      </x:c>
+      <x:c r="K29" s="63" t="str">
+        <x:v>护目件</x:v>
+      </x:c>
+      <x:c r="L29" s="63" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="M29" s="63" t="str">
+        <x:v>可选；layer2，禁投影/GI；不得替代双眼节点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="38" customHeight="1">
+      <x:c r="A30" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B30" s="63" t="str">
+        <x:v>scarf_legacy</x:v>
+      </x:c>
+      <x:c r="C30" s="63" t="str">
+        <x:v>VisualRoot/Scarf</x:v>
+      </x:c>
+      <x:c r="D30" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E30" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F30" s="63" t="str">
+        <x:v>隐藏兼容节点</x:v>
+      </x:c>
+      <x:c r="G30" s="63" t="str">
+        <x:v>(0,1.32,0)</x:v>
+      </x:c>
+      <x:c r="H30" s="63" t="str">
+        <x:v>随root</x:v>
+      </x:c>
+      <x:c r="I30" s="63" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J30" s="63" t="str">
+        <x:v>不参与当前轮廓</x:v>
+      </x:c>
+      <x:c r="K30" s="63" t="str">
+        <x:v>旧场景兼容</x:v>
+      </x:c>
+      <x:c r="L30" s="63" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="M30" s="63" t="str">
+        <x:v>默认visible=false；不计入四主模块</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11894,7 +13178,7 @@
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>2D/3D 共用六态 ID 与转换白名单；Low HP / Silenced / Invincible / Reloading 为叠加层。Reloading 读取武器唯一计时，新增动画前先查本表</x:v>
+        <x:v>2D/3D 共用六态 ID 与转换白名单；Low HP / Silenced / Invincible / Reloading / Firing / Charging / Knockback 为叠加层。武器与命中是唯一动作来源，新增动画前先查本表</x:v>
       </x:c>
       <x:c r="B3" s="6"/>
       <x:c r="C3" s="6"/>
@@ -12077,25 +13361,25 @@
         <x:v>idle,moving,locked,dead</x:v>
       </x:c>
       <x:c r="F9" s="37" t="str">
-        <x:v>冲击压缩</x:v>
+        <x:v>冲击压缩 + 击退弹性</x:v>
       </x:c>
       <x:c r="G9" s="37" t="str">
-        <x:v>后仰</x:v>
+        <x:v>后仰 + 回弹</x:v>
       </x:c>
       <x:c r="H9" s="37" t="str">
         <x:v>不显示</x:v>
       </x:c>
       <x:c r="I9" s="37" t="str">
-        <x:v>随身体左右镜像</x:v>
+        <x:v>与weapon_socket同相后退/回正</x:v>
       </x:c>
       <x:c r="J9" s="37" t="str">
-        <x:v>抖动</x:v>
+        <x:v>抖动/滞后</x:v>
       </x:c>
       <x:c r="K9" s="37" t="str">
-        <x:v>红闪/屏闪</x:v>
+        <x:v>红闪/击退轨迹</x:v>
       </x:c>
       <x:c r="L9" s="37" t="str">
-        <x:v>2D/3D受击压缩/闪色；握持关系不变</x:v>
+        <x:v>真实命中方向 + 递减XZ冲量；不扩张六态</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -12722,11 +14006,303 @@
         <x:v>终态 + Tween</x:v>
       </x:c>
     </x:row>
+    <x:row r="28" ht="38" customHeight="1">
+      <x:c r="A28" s="81" t="str">
+        <x:v>Player3D 动作覆盖层 × 组件表现（不新增顶层状态）</x:v>
+      </x:c>
+      <x:c r="B28" s="81"/>
+      <x:c r="C28" s="81"/>
+      <x:c r="D28" s="81"/>
+      <x:c r="E28" s="81"/>
+      <x:c r="F28" s="81"/>
+      <x:c r="G28" s="81"/>
+      <x:c r="H28" s="81"/>
+      <x:c r="I28" s="81"/>
+      <x:c r="J28" s="81"/>
+      <x:c r="K28" s="81"/>
+      <x:c r="L28" s="81"/>
+    </x:row>
+    <x:row r="29" ht="38" customHeight="1">
+      <x:c r="A29" s="82" t="str">
+        <x:v>层级｜状态ID｜中文名｜唯一来源｜退出｜Body｜Head｜Hand L（停用）｜Hand（握持）｜Scarf｜VFX/UI｜首版实现</x:v>
+      </x:c>
+      <x:c r="B29" s="82"/>
+      <x:c r="C29" s="82"/>
+      <x:c r="D29" s="82"/>
+      <x:c r="E29" s="82"/>
+      <x:c r="F29" s="82"/>
+      <x:c r="G29" s="82"/>
+      <x:c r="H29" s="82"/>
+      <x:c r="I29" s="82"/>
+      <x:c r="J29" s="82"/>
+      <x:c r="K29" s="82"/>
+      <x:c r="L29" s="82"/>
+    </x:row>
+    <x:row r="30" ht="38" customHeight="1">
+      <x:c r="A30" s="63" t="str">
+        <x:v>叠加</x:v>
+      </x:c>
+      <x:c r="B30" s="63" t="str">
+        <x:v>firing</x:v>
+      </x:c>
+      <x:c r="C30" s="63" t="str">
+        <x:v>射击</x:v>
+      </x:c>
+      <x:c r="D30" s="63" t="str">
+        <x:v>WeaponModel3D.shot_fired</x:v>
+      </x:c>
+      <x:c r="E30" s="63" t="str">
+        <x:v>短时回弹后退出</x:v>
+      </x:c>
+      <x:c r="F30" s="63" t="str">
+        <x:v>前探/压缩/回弹</x:v>
+      </x:c>
+      <x:c r="G30" s="63" t="str">
+        <x:v>小幅前探</x:v>
+      </x:c>
+      <x:c r="H30" s="63" t="str">
+        <x:v>不显示</x:v>
+      </x:c>
+      <x:c r="I30" s="63" t="str">
+        <x:v>与weapon_socket同相后坐</x:v>
+      </x:c>
+      <x:c r="J30" s="63" t="str">
+        <x:v>受冲量轻摆</x:v>
+      </x:c>
+      <x:c r="K30" s="63" t="str">
+        <x:v>枪口闪光/后坐</x:v>
+      </x:c>
+      <x:c r="L30" s="63" t="str">
+        <x:v>真实发射信号；0.14s基础弹性；不独立计时</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="38" customHeight="1">
+      <x:c r="A31" s="63" t="str">
+        <x:v>叠加</x:v>
+      </x:c>
+      <x:c r="B31" s="63" t="str">
+        <x:v>charging</x:v>
+      </x:c>
+      <x:c r="C31" s="63" t="str">
+        <x:v>蓄力</x:v>
+      </x:c>
+      <x:c r="D31" s="63" t="str">
+        <x:v>WeaponModel3D.charge_active / charge_ratio</x:v>
+      </x:c>
+      <x:c r="E31" s="63" t="str">
+        <x:v>释放/取消/换枪/死亡</x:v>
+      </x:c>
+      <x:c r="F31" s="63" t="str">
+        <x:v>下压蓄势</x:v>
+      </x:c>
+      <x:c r="G31" s="63" t="str">
+        <x:v>轻微压低</x:v>
+      </x:c>
+      <x:c r="H31" s="63" t="str">
+        <x:v>不显示</x:v>
+      </x:c>
+      <x:c r="I31" s="63" t="str">
+        <x:v>与weapon_socket同相蓄势</x:v>
+      </x:c>
+      <x:c r="J31" s="63" t="str">
+        <x:v>低频张力摆动</x:v>
+      </x:c>
+      <x:c r="K31" s="63" t="str">
+        <x:v>紫色能量提示（可选）</x:v>
+      </x:c>
+      <x:c r="L31" s="63" t="str">
+        <x:v>读取真实蓄力进度；禁用输入不取消脚本蓄力</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="38" customHeight="1">
+      <x:c r="A32" s="63" t="str">
+        <x:v>叠加</x:v>
+      </x:c>
+      <x:c r="B32" s="63" t="str">
+        <x:v>knockback</x:v>
+      </x:c>
+      <x:c r="C32" s="63" t="str">
+        <x:v>受击击飞</x:v>
+      </x:c>
+      <x:c r="D32" s="63" t="str">
+        <x:v>Player3D 命中方向/强度/时长</x:v>
+      </x:c>
+      <x:c r="E32" s="63" t="str">
+        <x:v>冲量归零或死亡</x:v>
+      </x:c>
+      <x:c r="F32" s="63" t="str">
+        <x:v>反向位移/压缩/弹回</x:v>
+      </x:c>
+      <x:c r="G32" s="63" t="str">
+        <x:v>后仰/回正</x:v>
+      </x:c>
+      <x:c r="H32" s="63" t="str">
+        <x:v>不显示</x:v>
+      </x:c>
+      <x:c r="I32" s="63" t="str">
+        <x:v>与weapon_socket同相后退/回正</x:v>
+      </x:c>
+      <x:c r="J32" s="63" t="str">
+        <x:v>滞后甩动</x:v>
+      </x:c>
+      <x:c r="K32" s="63" t="str">
+        <x:v>红闪/短轨迹</x:v>
+      </x:c>
+      <x:c r="L32" s="63" t="str">
+        <x:v>hurt 消费递减XZ冲量；不新增顶层状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="34" customHeight="1">
+      <x:c r="A34" s="93" t="str">
+        <x:v>Player3D DIY 外观槽 × 动态继承（不影响六态/玩法）</x:v>
+      </x:c>
+      <x:c r="B34" s="93"/>
+      <x:c r="C34" s="93"/>
+      <x:c r="D34" s="93"/>
+      <x:c r="E34" s="93"/>
+      <x:c r="F34" s="93"/>
+      <x:c r="G34" s="93"/>
+      <x:c r="H34" s="93"/>
+      <x:c r="I34" s="93"/>
+      <x:c r="J34" s="93"/>
+      <x:c r="K34" s="93"/>
+      <x:c r="L34" s="93"/>
+    </x:row>
+    <x:row r="35" ht="34" customHeight="1">
+      <x:c r="A35" s="94" t="str">
+        <x:v>槽位｜候选变体｜父组件｜移动｜射击/蓄力｜受击/击飞｜换弹｜死亡｜挂点契约｜验收｜复用范围｜首版实现</x:v>
+      </x:c>
+      <x:c r="B35" s="94"/>
+      <x:c r="C35" s="94"/>
+      <x:c r="D35" s="94"/>
+      <x:c r="E35" s="94"/>
+      <x:c r="F35" s="94"/>
+      <x:c r="G35" s="94"/>
+      <x:c r="H35" s="94"/>
+      <x:c r="I35" s="94"/>
+      <x:c r="J35" s="94"/>
+      <x:c r="K35" s="94"/>
+      <x:c r="L35" s="94"/>
+    </x:row>
+    <x:row r="36" ht="34" customHeight="1">
+      <x:c r="A36" s="63" t="str">
+        <x:v>body/head/hand/feet/hat/glasses</x:v>
+      </x:c>
+      <x:c r="B36" s="63" t="str">
+        <x:v>4+4+4+4+3+3</x:v>
+      </x:c>
+      <x:c r="C36" s="63" t="str">
+        <x:v>Body/Head/Hand/Feet/Wearables</x:v>
+      </x:c>
+      <x:c r="D36" s="63" t="str">
+        <x:v>身体弹性+双脚交替+圆短尾轻摆</x:v>
+      </x:c>
+      <x:c r="E36" s="63" t="str">
+        <x:v>手/枪同相后坐；头前探</x:v>
+      </x:c>
+      <x:c r="F36" s="63" t="str">
+        <x:v>整体后仰/脚随根回正</x:v>
+      </x:c>
+      <x:c r="G36" s="63" t="str">
+        <x:v>Hand+Socket同相</x:v>
+      </x:c>
+      <x:c r="H36" s="63" t="str">
+        <x:v>四主模块随根倾倒</x:v>
+      </x:c>
+      <x:c r="I36" s="63" t="str">
+        <x:v>唯一手/挂点相对向量固定</x:v>
+      </x:c>
+      <x:c r="J36" s="63" t="str">
+        <x:v>四主模块+双眼双耳短尾+六态覆盖</x:v>
+      </x:c>
+      <x:c r="K36" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="L36" s="63" t="str">
+        <x:v>Godot原生方体/三角耳/圆尾；Player3D.set_avatar_customization</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="38" customHeight="1">
+      <x:c r="A38" s="63" t="str">
+        <x:v>PH33 方形猫子组件 × 动作归属（不新增状态）</x:v>
+      </x:c>
+      <x:c r="B38" s="63"/>
+      <x:c r="C38" s="63"/>
+      <x:c r="D38" s="63"/>
+      <x:c r="E38" s="63"/>
+      <x:c r="F38" s="63"/>
+      <x:c r="G38" s="63"/>
+      <x:c r="H38" s="63"/>
+      <x:c r="I38" s="63"/>
+      <x:c r="J38" s="63"/>
+      <x:c r="K38" s="63"/>
+      <x:c r="L38" s="63"/>
+    </x:row>
+    <x:row r="39" ht="38" customHeight="1">
+      <x:c r="A39" s="63" t="str">
+        <x:v>父模块｜子组件｜节点数量｜Idle｜Moving｜Dashing｜Hurt/Knockback｜Reload/Fire｜Dead｜图形语言｜禁止事项｜验收</x:v>
+      </x:c>
+      <x:c r="B39" s="63"/>
+      <x:c r="C39" s="63"/>
+      <x:c r="D39" s="63"/>
+      <x:c r="E39" s="63"/>
+      <x:c r="F39" s="63"/>
+      <x:c r="G39" s="63"/>
+      <x:c r="H39" s="63"/>
+      <x:c r="I39" s="63"/>
+      <x:c r="J39" s="63"/>
+      <x:c r="K39" s="63"/>
+      <x:c r="L39" s="63"/>
+    </x:row>
+    <x:row r="40" ht="38" customHeight="1">
+      <x:c r="A40" s="63" t="str">
+        <x:v>Head / Body / Feet</x:v>
+      </x:c>
+      <x:c r="B40" s="63" t="str">
+        <x:v>Eyes / Ears / TailStub / FootL / FootR</x:v>
+      </x:c>
+      <x:c r="C40" s="63" t="str">
+        <x:v>2 / 2 / 1 / 2</x:v>
+      </x:c>
+      <x:c r="D40" s="63" t="str">
+        <x:v>双眼双耳稳定；短尾微摆</x:v>
+      </x:c>
+      <x:c r="E40" s="63" t="str">
+        <x:v>双脚交替抬起；短尾轻摆</x:v>
+      </x:c>
+      <x:c r="F40" s="63" t="str">
+        <x:v>随VisualRoot压缩</x:v>
+      </x:c>
+      <x:c r="G40" s="63" t="str">
+        <x:v>随父模块后仰回正</x:v>
+      </x:c>
+      <x:c r="H40" s="63" t="str">
+        <x:v>手/枪动作不牵动脚；头部继承</x:v>
+      </x:c>
+      <x:c r="I40" s="63" t="str">
+        <x:v>随父模块倾倒</x:v>
+      </x:c>
+      <x:c r="J40" s="63" t="str">
+        <x:v>方头方身方手方脚；圆尾唯一例外</x:v>
+      </x:c>
+      <x:c r="K40" s="63" t="str">
+        <x:v>嘴/鼻/第二手/长尾/烘焙跨模块</x:v>
+      </x:c>
+      <x:c r="L40" s="63" t="str">
+        <x:v>节点路径+数量+步态+持枪+视觉</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:L2"/>
     <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A16:L16"/>
+    <x:mergeCell ref="A28:L28"/>
+    <x:mergeCell ref="A29:L29"/>
+    <x:mergeCell ref="A34:L34"/>
+    <x:mergeCell ref="A35:L35"/>
+    <x:mergeCell ref="A38:L38"/>
+    <x:mergeCell ref="A39:L39"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -13661,6 +15237,78 @@
       <x:c r="M24" s="73"/>
       <x:c r="N24" s="73"/>
     </x:row>
+    <x:row r="25" ht="30" customHeight="1">
+      <x:c r="A25" s="63" t="str">
+        <x:v>独立3D验收场：scenes/Player3DStateGallery.tscn ｜ 真正驱动 Player3D 六态、WeaponModel3D 换弹覆盖、Enemy3D/Boss 九态与 ThemedNPC3D；验证：verify_player3d_state_gallery_flow.tscn / verify_player3d_state_gallery_visual.tscn PASS</x:v>
+      </x:c>
+      <x:c r="B25" s="63"/>
+      <x:c r="C25" s="63"/>
+      <x:c r="D25" s="63"/>
+      <x:c r="E25" s="63"/>
+      <x:c r="F25" s="63"/>
+      <x:c r="G25" s="63"/>
+      <x:c r="H25" s="63"/>
+      <x:c r="I25" s="63"/>
+      <x:c r="J25" s="63"/>
+      <x:c r="K25" s="63"/>
+      <x:c r="L25" s="63"/>
+      <x:c r="M25" s="63"/>
+      <x:c r="N25" s="63"/>
+    </x:row>
+    <x:row r="26" ht="32" customHeight="1">
+      <x:c r="A26" s="83" t="str">
+        <x:v>动作覆盖层：firing 由 WeaponModel3D.shot_fired 启动；charging 读取真实蓄力；knockback 以命中方向驱动 hurt 冲量与弹性回正；唯一 Hand + weapon_socket 全程同相。验证：verify_player3d_state_gallery_flow.tscn PASS</x:v>
+      </x:c>
+      <x:c r="B26" s="83"/>
+      <x:c r="C26" s="83"/>
+      <x:c r="D26" s="83"/>
+      <x:c r="E26" s="83"/>
+      <x:c r="F26" s="83"/>
+      <x:c r="G26" s="83"/>
+      <x:c r="H26" s="83"/>
+      <x:c r="I26" s="83"/>
+      <x:c r="J26" s="83"/>
+      <x:c r="K26" s="83"/>
+      <x:c r="L26" s="83"/>
+      <x:c r="M26" s="83"/>
+      <x:c r="N26" s="83"/>
+    </x:row>
+    <x:row r="28" ht="34" customHeight="1">
+      <x:c r="A28" s="95" t="str">
+        <x:v>DIY 组件：body/head/hand 三组外观变体 + hat/glasses 独立头部配件；真实入口 Player3D.set_avatar_customization()；握持点内收，移动/射击/击飞中 Hand + weapon_socket 同相。验证：verify_player3d_diy_flow.tscn PASS</x:v>
+      </x:c>
+      <x:c r="B28" s="95"/>
+      <x:c r="C28" s="95"/>
+      <x:c r="D28" s="95"/>
+      <x:c r="E28" s="95"/>
+      <x:c r="F28" s="95"/>
+      <x:c r="G28" s="95"/>
+      <x:c r="H28" s="95"/>
+      <x:c r="I28" s="95"/>
+      <x:c r="J28" s="95"/>
+      <x:c r="K28" s="95"/>
+      <x:c r="L28" s="95"/>
+      <x:c r="M28" s="95"/>
+      <x:c r="N28" s="95"/>
+    </x:row>
+    <x:row r="29" ht="38" customHeight="1">
+      <x:c r="A29" t="str">
+        <x:v>PH33 方形猫：复用CHR-PLY-CAPSULE01-3D；Body/Head/Hand/Feet四主模块；Head含双矩形眼与双三角耳，Body含圆短尾；无嘴、无长尾、无第二手；moving双脚交替，手与weapon_socket全动作同相。</x:v>
+      </x:c>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+      <x:c r="H29"/>
+      <x:c r="I29"/>
+      <x:c r="J29"/>
+      <x:c r="K29"/>
+      <x:c r="L29"/>
+      <x:c r="M29"/>
+      <x:c r="N29"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:N2"/>
@@ -13669,6 +15317,10 @@
     <x:mergeCell ref="A21:H21"/>
     <x:mergeCell ref="A23:H23"/>
     <x:mergeCell ref="A24:N24"/>
+    <x:mergeCell ref="A25:N25"/>
+    <x:mergeCell ref="A26:N26"/>
+    <x:mergeCell ref="A28:N28"/>
+    <x:mergeCell ref="A29:N29"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -13994,6 +15646,75 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="17" ht="52" customHeight="1">
+      <x:c r="A17" s="63" t="str">
+        <x:v>v1.11</x:v>
+      </x:c>
+      <x:c r="B17" s="63" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="C17" s="63" t="str">
+        <x:v>3D动作覆盖层登记</x:v>
+      </x:c>
+      <x:c r="D17" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D / WPN-GUN-KIT-3D</x:v>
+      </x:c>
+      <x:c r="E17" s="63" t="str">
+        <x:v>登记 firing/charging/knockback：真实武器/命中来源、手与weapon_socket同相、击飞基础位移与弹性回正；预览场控件和自动验收补齐</x:v>
+      </x:c>
+      <x:c r="F17" s="63" t="str">
+        <x:v>不新增AssetID或贴图；六态保持互斥，动作以既有组件程序组合</x:v>
+      </x:c>
+      <x:c r="G17" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="50" customHeight="1">
+      <x:c r="A18" s="63" t="str">
+        <x:v>v1.12</x:v>
+      </x:c>
+      <x:c r="B18" s="63" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="C18" s="63" t="str">
+        <x:v>3D角色DIY组件登记</x:v>
+      </x:c>
+      <x:c r="D18" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D 及五个子变体</x:v>
+      </x:c>
+      <x:c r="E18" s="63" t="str">
+        <x:v>登记 body/head/hand/hat/glasses 可装配变体、内收握持点、动态继承和预览/自动验收</x:v>
+      </x:c>
+      <x:c r="F18" s="63" t="str">
+        <x:v>新增子AssetID；不增加角色根，不改玩法或六态</x:v>
+      </x:c>
+      <x:c r="G18" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="52" customHeight="1">
+      <x:c r="A19" s="63" t="str">
+        <x:v>v1.13</x:v>
+      </x:c>
+      <x:c r="B19" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="C19" s="63" t="str">
+        <x:v>方形猫3D角色原型登记</x:v>
+      </x:c>
+      <x:c r="D19" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D及脚/眼/耳/短尾子资产</x:v>
+      </x:c>
+      <x:c r="E19" s="63" t="str">
+        <x:v>复用玩家根；登记Body/Head/Hand/Feet四主模块、双矩形眼、双三角耳、圆短尾、feet DIY及交替脚步</x:v>
+      </x:c>
+      <x:c r="F19" s="63" t="str">
+        <x:v>新增5个子AssetID；旧2D胶囊不变；3D旧Scarf隐藏兼容；玩法、碰撞、六态和灯光契约不变</x:v>
+      </x:c>
+      <x:c r="G19" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G2"/>
